--- a/out/Таймшит_AdTech_октябрь_2026_заполнен.xlsx
+++ b/out/Таймшит_AdTech_октябрь_2026_заполнен.xlsx
@@ -14476,29 +14476,29 @@
       </c>
       <c r="R139" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S139" s="8" t="inlineStr">
         <is>
-          <t>Интеграция ПО</t>
+          <t>Разработка (кодирование) ПО</t>
         </is>
       </c>
       <c r="T139" s="8" t="inlineStr">
         <is>
-          <t>Дедупликация событий показов и кликов: приемка функциональности и подготовка к запуску</t>
+          <t>Сопровождение промышленной эксплуатации показа рекламы: мониторинг, инциденты, обновления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U139" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-202</t>
+          <t>ADTHPL-221</t>
         </is>
       </c>
       <c r="V139" s="25" t="n">
         <v>46296</v>
       </c>
       <c r="W139" s="25" t="n">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="X139" s="8" t="n"/>
     </row>
@@ -21714,12 +21714,12 @@
       </c>
       <c r="T211" s="8" t="inlineStr">
         <is>
-          <t>Исправление дефектов промышленной эксплуатации показа рекламы (4 кв. 2026)</t>
+          <t>Миграция и перенос данных между хранилищами (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U211" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-222</t>
+          <t>ADTHPL-226</t>
         </is>
       </c>
       <c r="V211" s="25" t="n">
@@ -22110,12 +22110,12 @@
       </c>
       <c r="T215" s="8" t="inlineStr">
         <is>
-          <t>Управление портфелем разработки и бюджетом управления (4 кв. 2026)</t>
+          <t>Взаимодействие с бизнес-заказчиками и приоритизация бэклога (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U215" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-249</t>
+          <t>ADTHPL-250</t>
         </is>
       </c>
       <c r="V215" s="25" t="n">
@@ -25311,7 +25311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I243"/>
+  <dimension ref="A1:I240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -27575,13 +27575,13 @@
         <v>136</v>
       </c>
       <c r="E69" t="n">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0.706</v>
       </c>
       <c r="H69" t="n">
         <v>2</v>
@@ -30441,12 +30441,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ADTHPL-202</t>
+          <t>ADTHPL-203</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Дедупликация событий показов и кликов: приемка функциональности и подготовка к запуску</t>
+          <t>Управление согласиями пользователей на обработку данных: анализ данных и проектирование метрик</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -30456,28 +30456,28 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Менеджер продукта</t>
+          <t>Аналитик данных</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>40</v>
+        <v>96</v>
       </c>
       <c r="F161" t="n">
         <v>1</v>
       </c>
       <c r="G161" t="n">
-        <v>310</v>
+        <v>254</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ADTHPL-203</t>
+          <t>ADTHPL-204</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Управление согласиями пользователей на обработку данных: анализ данных и проектирование метрик</t>
+          <t>Управление согласиями пользователей на обработку данных: спецификация форматов обмена данными</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -30491,24 +30491,24 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>96</v>
+        <v>280</v>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G162" t="n">
-        <v>254</v>
+        <v>70</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ADTHPL-204</t>
+          <t>ADTHPL-205</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Управление согласиями пользователей на обработку данных: спецификация форматов обмена данными</t>
+          <t>Управление согласиями пользователей на обработку данных: проектирование модели данных</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -30518,28 +30518,28 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Аналитик данных</t>
+          <t>Ведущий аналитик данных</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="F163" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>70</v>
+        <v>230</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ADTHPL-205</t>
+          <t>ADTHPL-206</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Управление согласиями пользователей на обработку данных: проектирование модели данных</t>
+          <t>Управление согласиями пользователей на обработку данных: разработка требований и спецификации интеграций</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -30549,28 +30549,28 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Ведущий аналитик данных</t>
+          <t>Системный аналитик</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="F164" t="n">
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>230</v>
+        <v>262</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ADTHPL-206</t>
+          <t>ADTHPL-207</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Управление согласиями пользователей на обработку данных: разработка требований и спецификации интеграций</t>
+          <t>Управление согласиями пользователей на обработку данных: проектирование архитектуры решения</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -30596,12 +30596,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ADTHPL-207</t>
+          <t>ADTHPL-208</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Управление согласиями пользователей на обработку данных: проектирование архитектуры решения</t>
+          <t>Кабинет селлера для самостоятельного запуска продвижения: проектирование интерфейса и прототипирование</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -30611,28 +30611,28 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Системный аналитик</t>
+          <t>Дизайнер продукта</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>262</v>
+        <v>302</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ADTHPL-208</t>
+          <t>ADTHPL-209</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Кабинет селлера для самостоятельного запуска продвижения: проектирование интерфейса и прототипирование</t>
+          <t>Кабинет селлера для самостоятельного запуска продвижения: макеты экранов и дизайн-система</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -30646,24 +30646,24 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>48</v>
+        <v>128</v>
       </c>
       <c r="F167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G167" t="n">
-        <v>302</v>
+        <v>222</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ADTHPL-209</t>
+          <t>ADTHPL-210</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Кабинет селлера для самостоятельного запуска продвижения: макеты экранов и дизайн-система</t>
+          <t>Кабинет селлера для самостоятельного запуска продвижения: проектирование пользовательских сценариев</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -30677,24 +30677,24 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="F168" t="n">
         <v>2</v>
       </c>
       <c r="G168" t="n">
-        <v>222</v>
+        <v>238</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ADTHPL-210</t>
+          <t>ADTHPL-211</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Кабинет селлера для самостоятельного запуска продвижения: проектирование пользовательских сценариев</t>
+          <t>Кабинет селлера для самостоятельного запуска продвижения: адаптивные макеты для мобильных устройств</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -30720,12 +30720,12 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ADTHPL-211</t>
+          <t>ADTHPL-212</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Кабинет селлера для самостоятельного запуска продвижения: адаптивные макеты для мобильных устройств</t>
+          <t>Кабинет селлера для самостоятельного запуска продвижения: проектирование пользовательских сценариев, итерация 2</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -30739,24 +30739,24 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="F170" t="n">
         <v>2</v>
       </c>
       <c r="G170" t="n">
-        <v>238</v>
+        <v>222</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ADTHPL-212</t>
+          <t>ADTHPL-213</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Кабинет селлера для самостоятельного запуска продвижения: проектирование пользовательских сценариев, итерация 2</t>
+          <t>Кабинет селлера для самостоятельного запуска продвижения: юзабилити-тестирование интерфейса</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -30766,28 +30766,28 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Дизайнер продукта</t>
+          <t>Исследователь пользовательского опыта</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="F171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G171" t="n">
-        <v>222</v>
+        <v>270</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ADTHPL-213</t>
+          <t>ADTHPL-214</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Кабинет селлера для самостоятельного запуска продвижения: юзабилити-тестирование интерфейса</t>
+          <t>Отчет sales lift по рекламной кампании: анализ данных и проектирование метрик</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -30797,28 +30797,28 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Исследователь пользовательского опыта</t>
+          <t>Аналитик данных</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="F172" t="n">
         <v>1</v>
       </c>
       <c r="G172" t="n">
-        <v>270</v>
+        <v>230</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ADTHPL-214</t>
+          <t>ADTHPL-215</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Отчет sales lift по рекламной кампании: анализ данных и проектирование метрик</t>
+          <t>Отчет sales lift по рекламной кампании: анализ источников и качества данных</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -30844,12 +30844,12 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ADTHPL-215</t>
+          <t>ADTHPL-216</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Отчет sales lift по рекламной кампании: анализ источников и качества данных</t>
+          <t>Отчет sales lift по рекламной кампании: спецификация форматов обмена данными</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -30859,7 +30859,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Аналитик данных</t>
+          <t>Ведущий аналитик данных</t>
         </is>
       </c>
       <c r="E174" t="n">
@@ -30875,12 +30875,12 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ADTHPL-216</t>
+          <t>ADTHPL-217</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Отчет sales lift по рекламной кампании: спецификация форматов обмена данными</t>
+          <t>Кабинет партнера: ссылки, промокоды, статистика: функциональное и интеграционное тестирование</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -30890,28 +30890,28 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Ведущий аналитик данных</t>
+          <t>Ведущий специалист по тестированию</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="F175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G175" t="n">
-        <v>230</v>
+        <v>190</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ADTHPL-217</t>
+          <t>ADTHPL-218</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Кабинет партнера: ссылки, промокоды, статистика: функциональное и интеграционное тестирование</t>
+          <t>Кабинет партнера: ссылки, промокоды, статистика: нагрузочное тестирование</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -30925,24 +30925,24 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F176" t="n">
         <v>2</v>
       </c>
       <c r="G176" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ADTHPL-218</t>
+          <t>ADTHPL-219</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Кабинет партнера: ссылки, промокоды, статистика: нагрузочное тестирование</t>
+          <t>Кабинет партнера: ссылки, промокоды, статистика: автоматизация регрессионных тестов</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -30956,24 +30956,24 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>152</v>
+        <v>192</v>
       </c>
       <c r="F177" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G177" t="n">
-        <v>198</v>
+        <v>158</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ADTHPL-219</t>
+          <t>ADTHPL-220</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Кабинет партнера: ссылки, промокоды, статистика: автоматизация регрессионных тестов</t>
+          <t>Кабинет партнера: ссылки, промокоды, статистика: тестирование отказоустойчивости</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -30987,55 +30987,55 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="F178" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G178" t="n">
-        <v>158</v>
+        <v>238</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ADTHPL-220</t>
+          <t>ADTHPL-221</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Кабинет партнера: ссылки, промокоды, статистика: тестирование отказоустойчивости</t>
+          <t>Сопровождение промышленной эксплуатации показа рекламы: мониторинг, инциденты, обновления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Ведущий специалист по тестированию</t>
+          <t>Ведущий инженер сопровождения</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>112</v>
+        <v>342</v>
       </c>
       <c r="F179" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G179" t="n">
-        <v>238</v>
+        <v>8</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ADTHPL-221</t>
+          <t>ADTHPL-224</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Сопровождение промышленной эксплуатации показа рекламы: мониторинг, инциденты, обновления (4 кв. 2026)</t>
+          <t>Административное управление командой показа рекламы: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -31045,28 +31045,28 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Ведущий инженер сопровождения</t>
+          <t>Руководитель команды</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>302</v>
+        <v>350</v>
       </c>
       <c r="F180" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G180" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ADTHPL-222</t>
+          <t>ADTHPL-225</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Исправление дефектов промышленной эксплуатации показа рекламы (4 кв. 2026)</t>
+          <t>Сопровождение промышленной эксплуатации сбора событий: мониторинг, инциденты, обновления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -31076,28 +31076,28 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Ведущий инженер сопровождения</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>56</v>
+        <v>146</v>
       </c>
       <c r="F181" t="n">
         <v>1</v>
       </c>
       <c r="G181" t="n">
-        <v>294</v>
+        <v>204</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ADTHPL-224</t>
+          <t>ADTHPL-226</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Административное управление командой показа рекламы: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Миграция и перенос данных между хранилищами (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -31107,28 +31107,28 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Руководитель команды</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>350</v>
+        <v>56</v>
       </c>
       <c r="F182" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>294</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ADTHPL-225</t>
+          <t>ADTHPL-227</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Сопровождение промышленной эксплуатации сбора событий: мониторинг, инциденты, обновления (4 кв. 2026)</t>
+          <t>Административное управление командой сбора событий: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -31138,28 +31138,28 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Ведущий инженер сопровождения</t>
+          <t>Руководитель команды</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>146</v>
+        <v>246</v>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G183" t="n">
-        <v>204</v>
+        <v>104</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ADTHPL-226</t>
+          <t>ADTHPL-228</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Миграция и перенос данных между хранилищами (4 кв. 2026)</t>
+          <t>Сопровождение промышленной эксплуатации рекламного кабинета: мониторинг, инциденты, обновления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -31169,28 +31169,28 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Ведущий инженер сопровождения</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>350</v>
+        <v>286</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ADTHPL-227</t>
+          <t>ADTHPL-230</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Административное управление командой сбора событий: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Административное управление командой рекламного кабинета: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -31204,24 +31204,24 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>246</v>
+        <v>218</v>
       </c>
       <c r="F185" t="n">
         <v>2</v>
       </c>
       <c r="G185" t="n">
-        <v>104</v>
+        <v>132</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ADTHPL-228</t>
+          <t>ADTHPL-233</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Сопровождение промышленной эксплуатации рекламного кабинета: мониторинг, инциденты, обновления (4 кв. 2026)</t>
+          <t>Сопровождение промышленной эксплуатации аналитики: мониторинг, инциденты, обновления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -31235,24 +31235,24 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="F186" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G186" t="n">
-        <v>286</v>
+        <v>254</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ADTHPL-229</t>
+          <t>ADTHPL-234</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Снижение технического долга и обновление зависимостей (4 кв. 2026)</t>
+          <t>Административное управление командой аналитики: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -31262,28 +31262,28 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Главный разработчик</t>
+          <t>Руководитель команды</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="F187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G187" t="n">
-        <v>350</v>
+        <v>132</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ADTHPL-230</t>
+          <t>ADTHPL-235</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Административное управление командой рекламного кабинета: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Сопровождение промышленной эксплуатации партнерской платформы: мониторинг, инциденты, обновления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -31293,28 +31293,28 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Руководитель команды</t>
+          <t>Инженер сопровождения</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F188" t="n">
         <v>2</v>
       </c>
       <c r="G188" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ADTHPL-233</t>
+          <t>ADTHPL-236</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Сопровождение промышленной эксплуатации аналитики: мониторинг, инциденты, обновления (4 кв. 2026)</t>
+          <t>Административное управление командой партнерской платформы: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -31324,28 +31324,28 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Ведущий инженер сопровождения</t>
+          <t>Руководитель команды</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>96</v>
+        <v>210</v>
       </c>
       <c r="F189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G189" t="n">
-        <v>254</v>
+        <v>140</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ADTHPL-234</t>
+          <t>ADTHPL-237</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Административное управление командой аналитики: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Сопровождение промышленной эксплуатации интеграции с ОРД: мониторинг, инциденты, обновления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -31355,28 +31355,28 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Руководитель команды</t>
+          <t>Инженер сопровождения</t>
         </is>
       </c>
       <c r="E190" t="n">
-        <v>218</v>
+        <v>96</v>
       </c>
       <c r="F190" t="n">
         <v>2</v>
       </c>
       <c r="G190" t="n">
-        <v>132</v>
+        <v>254</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ADTHPL-235</t>
+          <t>ADTHPL-238</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Сопровождение промышленной эксплуатации партнерской платформы: мониторинг, инциденты, обновления (4 кв. 2026)</t>
+          <t>Административное управление командой интеграции с ОРД: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -31386,28 +31386,28 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Инженер сопровождения</t>
+          <t>Руководитель команды</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>216</v>
+        <v>123</v>
       </c>
       <c r="F191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>134</v>
+        <v>227</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ADTHPL-236</t>
+          <t>ADTHPL-239</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Административное управление командой партнерской платформы: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Сопровождение регулярной отчетности Эдтех: доработки и разбор обращений (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -31417,28 +31417,28 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Руководитель команды</t>
+          <t>Ведущий разработчик проекта Эдтех</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="F192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G192" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ADTHPL-237</t>
+          <t>ADTHPL-242</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Сопровождение промышленной эксплуатации интеграции с ОРД: мониторинг, инциденты, обновления (4 кв. 2026)</t>
+          <t>Стратегическое управление департаментом и бюджетирование (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -31448,28 +31448,28 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Инженер сопровождения</t>
+          <t>Директор департамента</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="F193" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G193" t="n">
-        <v>254</v>
+        <v>230</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ADTHPL-238</t>
+          <t>ADTHPL-243</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Административное управление командой интеграции с ОРД: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Исследование рынка и конкурентных рекламных решений (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -31479,28 +31479,28 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Руководитель команды</t>
+          <t>Менеджер продукта</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>123</v>
+        <v>210</v>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G194" t="n">
-        <v>227</v>
+        <v>140</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ADTHPL-239</t>
+          <t>ADTHPL-244</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Сопровождение регулярной отчетности Эдтех: доработки и разбор обращений (4 кв. 2026)</t>
+          <t>Управление графиком проектов платформы: сроки, риски, статус-отчетность (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -31510,28 +31510,28 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Ведущий разработчик проекта Эдтех</t>
+          <t>Менеджер проектов</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>120</v>
+        <v>125.3</v>
       </c>
       <c r="F195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G195" t="n">
-        <v>230</v>
+        <v>224.7</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ADTHPL-242</t>
+          <t>ADTHPL-245</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Стратегическое управление департаментом и бюджетирование (4 кв. 2026)</t>
+          <t>Участие в найме и онбординге сотрудников платформы (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -31541,28 +31541,28 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Директор департамента</t>
+          <t>Руководитель команды</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>120</v>
+        <v>27</v>
       </c>
       <c r="F196" t="n">
         <v>1</v>
       </c>
       <c r="G196" t="n">
-        <v>230</v>
+        <v>323</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ADTHPL-243</t>
+          <t>ADTHPL-246</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Исследование рынка и конкурентных рекламных решений (4 кв. 2026)</t>
+          <t>Планирование ресурсов и отчетность направления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -31572,28 +31572,28 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Менеджер продукта</t>
+          <t>Руководитель направления</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>210</v>
+        <v>176</v>
       </c>
       <c r="F197" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G197" t="n">
-        <v>140</v>
+        <v>174</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ADTHPL-244</t>
+          <t>ADTHPL-247</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Управление графиком проектов платформы: сроки, риски, статус-отчетность (4 кв. 2026)</t>
+          <t>Развитие компетенций и процессов направления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -31603,28 +31603,28 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Менеджер проектов</t>
+          <t>Руководитель направления</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>125.3</v>
+        <v>176</v>
       </c>
       <c r="F198" t="n">
         <v>2</v>
       </c>
       <c r="G198" t="n">
-        <v>224.7</v>
+        <v>174</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ADTHPL-245</t>
+          <t>ADTHPL-248</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Участие в найме и онбординге сотрудников платформы (4 кв. 2026)</t>
+          <t>Координация межкомандных проектов и коммуникация с заказчиками (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -31634,28 +31634,28 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Руководитель команды</t>
+          <t>Руководитель проектов</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>27</v>
+        <v>68.3</v>
       </c>
       <c r="F199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G199" t="n">
-        <v>323</v>
+        <v>281.7</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ADTHPL-246</t>
+          <t>ADTHPL-249</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Планирование ресурсов и отчетность направления (4 кв. 2026)</t>
+          <t>Управление портфелем разработки и бюджетом управления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -31665,28 +31665,28 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Руководитель направления</t>
+          <t>Руководитель управления</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>176</v>
+        <v>288</v>
       </c>
       <c r="F200" t="n">
         <v>2</v>
       </c>
       <c r="G200" t="n">
-        <v>174</v>
+        <v>62</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ADTHPL-247</t>
+          <t>ADTHPL-250</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Развитие компетенций и процессов направления (4 кв. 2026)</t>
+          <t>Взаимодействие с бизнес-заказчиками и приоритизация бэклога (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -31696,28 +31696,28 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Руководитель направления</t>
+          <t>Руководитель управления</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="F201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G201" t="n">
-        <v>174</v>
+        <v>166</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ADTHPL-248</t>
+          <t>ADTHPL-251</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Координация межкомандных проектов и коммуникация с заказчиками (4 кв. 2026)</t>
+          <t>Планирование численности и развитие команд управления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -31727,121 +31727,121 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Руководитель проектов</t>
+          <t>Руководитель управления</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>68.3</v>
+        <v>112</v>
       </c>
       <c r="F202" t="n">
         <v>2</v>
       </c>
       <c r="G202" t="n">
-        <v>281.7</v>
+        <v>238</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ADTHPL-249</t>
+          <t>ADTHPL-253</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Управление портфелем разработки и бюджетом управления (4 кв. 2026)</t>
+          <t>Геораспределенная отказоустойчивая инфраструктура выдачи: функциональное и интеграционное тестирование</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Руководитель управления</t>
+          <t>Ведущий специалист по тестированию</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>344</v>
+        <v>160</v>
       </c>
       <c r="F203" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>6</v>
+        <v>190</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ADTHPL-250</t>
+          <t>ADTHPL-254</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Взаимодействие с бизнес-заказчиками и приоритизация бэклога (4 кв. 2026)</t>
+          <t>Бюджет и биллинг рекламодателя в кабинете: функциональное и интеграционное тестирование</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Руководитель управления</t>
+          <t>Ведущий специалист по тестированию</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G204" t="n">
-        <v>222</v>
+        <v>230</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ADTHPL-251</t>
+          <t>ADTHPL-255</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Планирование численности и развитие команд управления (4 кв. 2026)</t>
+          <t>Модерация креативов в рекламном кабинете: разработка серверной части и API</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Руководитель управления</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="F205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G205" t="n">
-        <v>238</v>
+        <v>294</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ADTHPL-253</t>
+          <t>ADTHPL-256</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Геораспределенная отказоустойчивая инфраструктура выдачи: функциональное и интеграционное тестирование</t>
+          <t>Модерация креативов в рекламном кабинете: разработка пользовательского интерфейса</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -31851,90 +31851,90 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Ведущий специалист по тестированию</t>
+          <t>Разработчик</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>160</v>
+        <v>56</v>
       </c>
       <c r="F206" t="n">
         <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>190</v>
+        <v>294</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ADTHPL-254</t>
+          <t>ADTHPL-257</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Бюджет и биллинг рекламодателя в кабинете: функциональное и интеграционное тестирование</t>
+          <t>Аукцион первой цены с корректировкой ставок: исследование и формирование продуктовой гипотезы</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Ведущий специалист по тестированию</t>
+          <t>Ведущий менеджер продукта</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="F207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G207" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ADTHPL-255</t>
+          <t>ADTHPL-258</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Модерация креативов в рекламном кабинете: разработка серверной части и API</t>
+          <t>Аукцион первой цены с корректировкой ставок: оценка эффекта и подготовка бизнес-кейса</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Менеджер продукта</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>56</v>
+        <v>210</v>
       </c>
       <c r="F208" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G208" t="n">
-        <v>294</v>
+        <v>140</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ADTHPL-256</t>
+          <t>ADTHPL-259</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Модерация креативов в рекламном кабинете: разработка пользовательского интерфейса</t>
+          <t>Прогноз кликабельности для ранжирования ставок: функциональное и интеграционное тестирование</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -31944,90 +31944,90 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Разработчик</t>
+          <t>Ведущий специалист по тестированию</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="F209" t="n">
         <v>1</v>
       </c>
       <c r="G209" t="n">
-        <v>294</v>
+        <v>230</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ADTHPL-257</t>
+          <t>ADTHPL-260</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Аукцион первой цены с корректировкой ставок: исследование и формирование продуктовой гипотезы</t>
+          <t>Прогноз кликабельности для ранжирования ставок: нагрузочное тестирование</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Ведущий менеджер продукта</t>
+          <t>Ведущий специалист по тестированию</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="F210" t="n">
         <v>2</v>
       </c>
       <c r="G210" t="n">
-        <v>210</v>
+        <v>238</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ADTHPL-258</t>
+          <t>ADTHPL-261</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Аукцион первой цены с корректировкой ставок: оценка эффекта и подготовка бизнес-кейса</t>
+          <t>Прогноз кликабельности для ранжирования ставок: автоматизация регрессионных тестов</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Менеджер продукта</t>
+          <t>Ведущий специалист по тестированию</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="F211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G211" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>ADTHPL-259</t>
+          <t>ADTHPL-262</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: функциональное и интеграционное тестирование</t>
+          <t>Прогноз кликабельности для ранжирования ставок: тестирование отказоустойчивости</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -32037,7 +32037,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Ведущий специалист по тестированию</t>
+          <t>Главный специалист по тестированию</t>
         </is>
       </c>
       <c r="E212" t="n">
@@ -32053,12 +32053,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ADTHPL-260</t>
+          <t>ADTHPL-263</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: нагрузочное тестирование</t>
+          <t>Прогноз кликабельности для ранжирования ставок: тестирование безопасности</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -32068,28 +32068,28 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Ведущий специалист по тестированию</t>
+          <t>Главный специалист по тестированию</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="F213" t="n">
         <v>2</v>
       </c>
       <c r="G213" t="n">
-        <v>238</v>
+        <v>174</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ADTHPL-261</t>
+          <t>ADTHPL-264</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: автоматизация регрессионных тестов</t>
+          <t>Таргетинг по сегментам аудиторий в реальном времени: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -32099,28 +32099,28 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Ведущий специалист по тестированию</t>
+          <t>Главный разработчик</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="F214" t="n">
         <v>1</v>
       </c>
       <c r="G214" t="n">
-        <v>230</v>
+        <v>270</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ADTHPL-262</t>
+          <t>ADTHPL-265</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: тестирование отказоустойчивости</t>
+          <t>Мастер создания кампании в рекламном кабинете: функциональное и интеграционное тестирование</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -32130,28 +32130,28 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Главный специалист по тестированию</t>
+          <t>Ведущий специалист по тестированию</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="F215" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G215" t="n">
-        <v>230</v>
+        <v>198</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ADTHPL-263</t>
+          <t>ADTHPL-266</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: тестирование безопасности</t>
+          <t>Мастер создания кампании в рекламном кабинете: тестирование отказоустойчивости</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -32161,28 +32161,28 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Главный специалист по тестированию</t>
+          <t>Ведущий специалист по тестированию</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="F216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>174</v>
+        <v>262</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ADTHPL-264</t>
+          <t>ADTHPL-267</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Таргетинг по сегментам аудиторий в реальном времени: проектирование архитектуры и разработка ядра</t>
+          <t>Мастер создания кампании в рекламном кабинете: нагрузочное тестирование</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -32192,28 +32192,28 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Главный разработчик</t>
+          <t>Главный специалист по тестированию</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="F217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G217" t="n">
-        <v>270</v>
+        <v>150</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>ADTHPL-265</t>
+          <t>ADTHPL-268</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: функциональное и интеграционное тестирование</t>
+          <t>Мастер создания кампании в рекламном кабинете: тестирование безопасности</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -32223,7 +32223,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Ведущий специалист по тестированию</t>
+          <t>Главный специалист по тестированию</t>
         </is>
       </c>
       <c r="E218" t="n">
@@ -32239,12 +32239,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>ADTHPL-266</t>
+          <t>ADTHPL-269</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: тестирование отказоустойчивости</t>
+          <t>Мастер создания кампании в рекламном кабинете: автоматизация регрессионных тестов</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -32254,28 +32254,28 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Ведущий специалист по тестированию</t>
+          <t>Специалист по тестированию</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="F219" t="n">
         <v>1</v>
       </c>
       <c r="G219" t="n">
-        <v>262</v>
+        <v>230</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ADTHPL-267</t>
+          <t>ADTHPL-270</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: нагрузочное тестирование</t>
+          <t>Мастер создания кампании в рекламном кабинете: приемочное тестирование с бизнесом</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -32285,28 +32285,28 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Главный специалист по тестированию</t>
+          <t>Специалист по тестированию</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>200</v>
+        <v>56</v>
       </c>
       <c r="F220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G220" t="n">
-        <v>150</v>
+        <v>294</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ADTHPL-268</t>
+          <t>ADTHPL-271</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: тестирование безопасности</t>
+          <t>Автоматическая передача в ОРД данных о показах и актах: разработка серверной части и API</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -32316,28 +32316,28 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Главный специалист по тестированию</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>198</v>
+        <v>350</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ADTHPL-269</t>
+          <t>ADTHPL-272</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: автоматизация регрессионных тестов</t>
+          <t>Автоматическая передача в ОРД данных о показах и актах: мониторинг и логирование новой функциональности</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -32347,28 +32347,28 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Специалист по тестированию</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>230</v>
+        <v>350</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ADTHPL-270</t>
+          <t>ADTHPL-273</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: приемочное тестирование с бизнесом</t>
+          <t>Интеграция с внешними SSP по OpenRTB 2.6: разработка серверной части и API</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -32378,28 +32378,28 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Специалист по тестированию</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="F223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>294</v>
+        <v>350</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ADTHPL-271</t>
+          <t>ADTHPL-274</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Автоматическая передача в ОРД данных о показах и актах: разработка серверной части и API</t>
+          <t>Интеграция с внешними SSP по OpenRTB 2.6: разработка пользовательского интерфейса</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -32425,12 +32425,12 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ADTHPL-272</t>
+          <t>ADTHPL-275</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Автоматическая передача в ОРД данных о показах и актах: мониторинг и логирование новой функциональности</t>
+          <t>Интеграция с внешними SSP по OpenRTB 2.6: интеграция со смежными модулями платформы</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -32456,12 +32456,12 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ADTHPL-273</t>
+          <t>ADTHPL-276</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Интеграция с внешними SSP по OpenRTB 2.6: разработка серверной части и API</t>
+          <t>Интеграция с внешними SSP по OpenRTB 2.6: разработка хранения и обработки данных</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -32487,12 +32487,12 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ADTHPL-274</t>
+          <t>ADTHPL-277</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Интеграция с внешними SSP по OpenRTB 2.6: разработка пользовательского интерфейса</t>
+          <t>Интеграция с внешними SSP по OpenRTB 2.6: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -32502,28 +32502,28 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Главный разработчик</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="F227" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G227" t="n">
-        <v>350</v>
+        <v>286</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ADTHPL-275</t>
+          <t>ADTHPL-278</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Интеграция с внешними SSP по OpenRTB 2.6: интеграция со смежными модулями платформы</t>
+          <t>Интеграция с внешними SSP по OpenRTB 2.6: техническое руководство разработкой и код-ревью</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -32533,28 +32533,28 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Руководитель команды</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="F228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G228" t="n">
-        <v>350</v>
+        <v>297</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ADTHPL-276</t>
+          <t>ADTHPL-279</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Интеграция с внешними SSP по OpenRTB 2.6: разработка хранения и обработки данных</t>
+          <t>Управление согласиями пользователей на обработку данных: разработка конвейера загрузки и обработки данных</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -32564,28 +32564,28 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Инженер данных</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G229" t="n">
-        <v>350</v>
+        <v>294</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ADTHPL-277</t>
+          <t>ADTHPL-282</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Интеграция с внешними SSP по OpenRTB 2.6: проектирование архитектуры и разработка ядра</t>
+          <t>Управление согласиями пользователей на обработку данных: техническое руководство разработкой и код-ревью</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -32595,28 +32595,28 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Главный разработчик</t>
+          <t>Руководитель команды</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G230" t="n">
-        <v>286</v>
+        <v>297</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ADTHPL-278</t>
+          <t>ADTHPL-283</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Интеграция с внешними SSP по OpenRTB 2.6: техническое руководство разработкой и код-ревью</t>
+          <t>Кабинет селлера для самостоятельного запуска продвижения: интеграция со смежными модулями платформы</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -32626,28 +32626,28 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Руководитель команды</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="F231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G231" t="n">
-        <v>297</v>
+        <v>350</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ADTHPL-279</t>
+          <t>ADTHPL-284</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Управление согласиями пользователей на обработку данных: разработка конвейера загрузки и обработки данных</t>
+          <t>Кабинет селлера для самостоятельного запуска продвижения: разработка хранения и обработки данных</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -32657,28 +32657,28 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Инженер данных</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="F232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>294</v>
+        <v>350</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ADTHPL-282</t>
+          <t>ADTHPL-285</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Управление согласиями пользователей на обработку данных: техническое руководство разработкой и код-ревью</t>
+          <t>Кабинет селлера для самостоятельного запуска продвижения: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -32688,28 +32688,28 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Руководитель команды</t>
+          <t>Главный разработчик</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F233" t="n">
         <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ADTHPL-283</t>
+          <t>ADTHPL-286</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Кабинет селлера для самостоятельного запуска продвижения: интеграция со смежными модулями платформы</t>
+          <t>Кабинет селлера для самостоятельного запуска продвижения: разработка серверной части и API</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -32719,28 +32719,28 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Главный разработчик</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G234" t="n">
-        <v>350</v>
+        <v>294</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ADTHPL-284</t>
+          <t>ADTHPL-287</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Кабинет селлера для самостоятельного запуска продвижения: разработка хранения и обработки данных</t>
+          <t>Кабинет селлера для самостоятельного запуска продвижения: разработка пользовательского интерфейса</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -32750,28 +32750,28 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Главный разработчик</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="F235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G235" t="n">
-        <v>350</v>
+        <v>310</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ADTHPL-285</t>
+          <t>ADTHPL-290</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Кабинет селлера для самостоятельного запуска продвижения: проектирование архитектуры и разработка ядра</t>
+          <t>Отчет sales lift по рекламной кампании: обучение и валидация модели</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -32781,59 +32781,59 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Главный разработчик</t>
+          <t>Ведущий специалист ML</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>56</v>
+        <v>136</v>
       </c>
       <c r="F236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G236" t="n">
-        <v>294</v>
+        <v>214</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ADTHPL-286</t>
+          <t>ADTHPL-293</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Кабинет селлера для самостоятельного запуска продвижения: разработка серверной части и API</t>
+          <t>Сбор событий веб-витрины без сторонних cookies: исследование и формирование продуктовой гипотезы</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Главный разработчик</t>
+          <t>Ведущий менеджер продукта</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>56</v>
+        <v>140</v>
       </c>
       <c r="F237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G237" t="n">
-        <v>294</v>
+        <v>210</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ADTHPL-287</t>
+          <t>ADTHPL-295</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Кабинет селлера для самостоятельного запуска продвижения: разработка пользовательского интерфейса</t>
+          <t>Автоматическая передача в ОРД данных о показах и актах: анализ качества данных на тестовом контуре</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -32843,28 +32843,28 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Главный разработчик</t>
+          <t>Аналитик данных</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>310</v>
+        <v>350</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ADTHPL-290</t>
+          <t>ADTHPL-296</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Отчет sales lift по рекламной кампании: обучение и валидация модели</t>
+          <t>Автоматическая передача в ОРД данных о показах и актах: проверка расчета метрик</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -32874,140 +32874,47 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Ведущий специалист ML</t>
+          <t>Аналитик данных</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="F239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>214</v>
+        <v>350</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ADTHPL-293</t>
+          <t>ADTHPL-297</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Сбор событий веб-витрины без сторонних cookies: исследование и формирование продуктовой гипотезы</t>
+          <t>Автоматическая передача в ОРД данных о показах и актах: проектирование модели данных и витрин</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Ведущий менеджер продукта</t>
+          <t>Ведущий аналитик данных</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="F240" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>ADTHPL-295</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Автоматическая передача в ОРД данных о показах и актах: анализ качества данных на тестовом контуре</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>Аналитик данных</t>
-        </is>
-      </c>
-      <c r="E241" t="n">
-        <v>0</v>
-      </c>
-      <c r="F241" t="n">
-        <v>0</v>
-      </c>
-      <c r="G241" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>ADTHPL-296</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Автоматическая передача в ОРД данных о показах и актах: проверка расчета метрик</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>Аналитик данных</t>
-        </is>
-      </c>
-      <c r="E242" t="n">
-        <v>0</v>
-      </c>
-      <c r="F242" t="n">
-        <v>0</v>
-      </c>
-      <c r="G242" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>ADTHPL-297</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Автоматическая передача в ОРД данных о показах и актах: проектирование модели данных и витрин</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>Ведущий аналитик данных</t>
-        </is>
-      </c>
-      <c r="E243" t="n">
-        <v>0</v>
-      </c>
-      <c r="F243" t="n">
-        <v>0</v>
-      </c>
-      <c r="G243" t="n">
         <v>350</v>
       </c>
     </row>

--- a/out/Таймшит_AdTech_октябрь_2026_заполнен.xlsx
+++ b/out/Таймшит_AdTech_октябрь_2026_заполнен.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,12 +80,8 @@
     <font>
       <b val="1"/>
     </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -96,11 +92,6 @@
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -153,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -207,16 +198,6 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -958,8 +939,8 @@
         <v>96</v>
       </c>
       <c r="O2" s="8" t="n"/>
-      <c r="P2" s="31" t="n"/>
-      <c r="Q2" s="31" t="n"/>
+      <c r="P2" s="27" t="n"/>
+      <c r="Q2" s="27" t="n"/>
       <c r="R2" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -980,10 +961,10 @@
           <t>ADTHPL-194</t>
         </is>
       </c>
-      <c r="V2" s="32" t="n">
+      <c r="V2" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W2" s="32" t="n">
+      <c r="W2" s="28" t="n">
         <v>46311</v>
       </c>
       <c r="X2" s="8" t="n"/>
@@ -1052,8 +1033,8 @@
         <v>80</v>
       </c>
       <c r="O3" s="8" t="n"/>
-      <c r="P3" s="31" t="n"/>
-      <c r="Q3" s="31" t="n"/>
+      <c r="P3" s="27" t="n"/>
+      <c r="Q3" s="27" t="n"/>
       <c r="R3" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -1074,10 +1055,10 @@
           <t>ADTHPL-213</t>
         </is>
       </c>
-      <c r="V3" s="32" t="n">
+      <c r="V3" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W3" s="32" t="n">
+      <c r="W3" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X3" s="8" t="n"/>
@@ -1146,8 +1127,8 @@
         <v>64</v>
       </c>
       <c r="O4" s="8" t="n"/>
-      <c r="P4" s="31" t="n"/>
-      <c r="Q4" s="31" t="n"/>
+      <c r="P4" s="27" t="n"/>
+      <c r="Q4" s="27" t="n"/>
       <c r="R4" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -1168,10 +1149,10 @@
           <t>ADTHPL-209</t>
         </is>
       </c>
-      <c r="V4" s="32" t="n">
+      <c r="V4" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W4" s="32" t="n">
+      <c r="W4" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X4" s="8" t="n"/>
@@ -1240,8 +1221,8 @@
         <v>64</v>
       </c>
       <c r="O5" s="8" t="n"/>
-      <c r="P5" s="31" t="n"/>
-      <c r="Q5" s="31" t="n"/>
+      <c r="P5" s="27" t="n"/>
+      <c r="Q5" s="27" t="n"/>
       <c r="R5" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -1262,10 +1243,10 @@
           <t>ADTHPL-212</t>
         </is>
       </c>
-      <c r="V5" s="32" t="n">
+      <c r="V5" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W5" s="32" t="n">
+      <c r="W5" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X5" s="8" t="n"/>
@@ -1334,8 +1315,8 @@
         <v>48</v>
       </c>
       <c r="O6" s="8" t="n"/>
-      <c r="P6" s="31" t="n"/>
-      <c r="Q6" s="31" t="n"/>
+      <c r="P6" s="27" t="n"/>
+      <c r="Q6" s="27" t="n"/>
       <c r="R6" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -1356,10 +1337,10 @@
           <t>ADTHPL-208</t>
         </is>
       </c>
-      <c r="V6" s="32" t="n">
+      <c r="V6" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W6" s="32" t="n">
+      <c r="W6" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X6" s="8" t="n"/>
@@ -1428,8 +1409,8 @@
         <v>64</v>
       </c>
       <c r="O7" s="8" t="n"/>
-      <c r="P7" s="31" t="n"/>
-      <c r="Q7" s="31" t="n"/>
+      <c r="P7" s="27" t="n"/>
+      <c r="Q7" s="27" t="n"/>
       <c r="R7" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -1450,10 +1431,10 @@
           <t>ADTHPL-209</t>
         </is>
       </c>
-      <c r="V7" s="32" t="n">
+      <c r="V7" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W7" s="32" t="n">
+      <c r="W7" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X7" s="8" t="n"/>
@@ -1522,8 +1503,8 @@
         <v>64</v>
       </c>
       <c r="O8" s="8" t="n"/>
-      <c r="P8" s="31" t="n"/>
-      <c r="Q8" s="31" t="n"/>
+      <c r="P8" s="27" t="n"/>
+      <c r="Q8" s="27" t="n"/>
       <c r="R8" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -1544,10 +1525,10 @@
           <t>ADTHPL-210</t>
         </is>
       </c>
-      <c r="V8" s="32" t="n">
+      <c r="V8" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W8" s="32" t="n">
+      <c r="W8" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X8" s="8" t="n"/>
@@ -1616,8 +1597,8 @@
         <v>48</v>
       </c>
       <c r="O9" s="8" t="n"/>
-      <c r="P9" s="31" t="n"/>
-      <c r="Q9" s="31" t="n"/>
+      <c r="P9" s="27" t="n"/>
+      <c r="Q9" s="27" t="n"/>
       <c r="R9" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -1638,10 +1619,10 @@
           <t>ADTHPL-211</t>
         </is>
       </c>
-      <c r="V9" s="32" t="n">
+      <c r="V9" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W9" s="32" t="n">
+      <c r="W9" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X9" s="8" t="n"/>
@@ -1714,8 +1695,8 @@
         <v>176</v>
       </c>
       <c r="O10" s="8" t="n"/>
-      <c r="P10" s="31" t="n"/>
-      <c r="Q10" s="31" t="n"/>
+      <c r="P10" s="27" t="n"/>
+      <c r="Q10" s="27" t="n"/>
       <c r="R10" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -1736,10 +1717,10 @@
           <t>ADTHPL-244</t>
         </is>
       </c>
-      <c r="V10" s="32" t="n">
+      <c r="V10" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W10" s="32" t="n">
+      <c r="W10" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X10" s="8" t="n"/>
@@ -1808,8 +1789,8 @@
         <v>64</v>
       </c>
       <c r="O11" s="8" t="n"/>
-      <c r="P11" s="31" t="n"/>
-      <c r="Q11" s="31" t="n"/>
+      <c r="P11" s="27" t="n"/>
+      <c r="Q11" s="27" t="n"/>
       <c r="R11" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -1830,10 +1811,10 @@
           <t>ADTHPL-211</t>
         </is>
       </c>
-      <c r="V11" s="32" t="n">
+      <c r="V11" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W11" s="32" t="n">
+      <c r="W11" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X11" s="8" t="n"/>
@@ -1902,8 +1883,8 @@
         <v>64</v>
       </c>
       <c r="O12" s="8" t="n"/>
-      <c r="P12" s="31" t="n"/>
-      <c r="Q12" s="31" t="n"/>
+      <c r="P12" s="27" t="n"/>
+      <c r="Q12" s="27" t="n"/>
       <c r="R12" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -1924,10 +1905,10 @@
           <t>ADTHPL-212</t>
         </is>
       </c>
-      <c r="V12" s="32" t="n">
+      <c r="V12" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W12" s="32" t="n">
+      <c r="W12" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X12" s="8" t="n"/>
@@ -1996,8 +1977,8 @@
         <v>48</v>
       </c>
       <c r="O13" s="8" t="n"/>
-      <c r="P13" s="31" t="n"/>
-      <c r="Q13" s="31" t="n"/>
+      <c r="P13" s="27" t="n"/>
+      <c r="Q13" s="27" t="n"/>
       <c r="R13" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -2018,10 +1999,10 @@
           <t>ADTHPL-210</t>
         </is>
       </c>
-      <c r="V13" s="32" t="n">
+      <c r="V13" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W13" s="32" t="n">
+      <c r="W13" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X13" s="8" t="n"/>
@@ -2094,8 +2075,8 @@
         <v>74</v>
       </c>
       <c r="O14" s="8" t="n"/>
-      <c r="P14" s="31" t="n"/>
-      <c r="Q14" s="31" t="n"/>
+      <c r="P14" s="27" t="n"/>
+      <c r="Q14" s="27" t="n"/>
       <c r="R14" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -2116,10 +2097,10 @@
           <t>ADTHPL-148</t>
         </is>
       </c>
-      <c r="V14" s="32" t="n">
+      <c r="V14" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W14" s="32" t="n">
+      <c r="W14" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X14" s="8" t="n"/>
@@ -2192,8 +2173,8 @@
         <v>32</v>
       </c>
       <c r="O15" s="8" t="n"/>
-      <c r="P15" s="31" t="n"/>
-      <c r="Q15" s="31" t="n"/>
+      <c r="P15" s="27" t="n"/>
+      <c r="Q15" s="27" t="n"/>
       <c r="R15" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -2214,10 +2195,10 @@
           <t>ADTHPL-280</t>
         </is>
       </c>
-      <c r="V15" s="32" t="n">
+      <c r="V15" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W15" s="32" t="n">
+      <c r="W15" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X15" s="8" t="n"/>
@@ -2290,8 +2271,8 @@
         <v>70</v>
       </c>
       <c r="O16" s="8" t="n"/>
-      <c r="P16" s="31" t="n"/>
-      <c r="Q16" s="31" t="n"/>
+      <c r="P16" s="27" t="n"/>
+      <c r="Q16" s="27" t="n"/>
       <c r="R16" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -2312,10 +2293,10 @@
           <t>ADTHPL-258</t>
         </is>
       </c>
-      <c r="V16" s="32" t="n">
+      <c r="V16" s="28" t="n">
         <v>46300</v>
       </c>
-      <c r="W16" s="32" t="n">
+      <c r="W16" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X16" s="8" t="n"/>
@@ -2388,8 +2369,8 @@
         <v>74</v>
       </c>
       <c r="O17" s="8" t="n"/>
-      <c r="P17" s="31" t="n"/>
-      <c r="Q17" s="31" t="n"/>
+      <c r="P17" s="27" t="n"/>
+      <c r="Q17" s="27" t="n"/>
       <c r="R17" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -2410,10 +2391,10 @@
           <t>ADTHPL-148</t>
         </is>
       </c>
-      <c r="V17" s="32" t="n">
+      <c r="V17" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W17" s="32" t="n">
+      <c r="W17" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X17" s="8" t="n"/>
@@ -2486,8 +2467,8 @@
         <v>32</v>
       </c>
       <c r="O18" s="8" t="n"/>
-      <c r="P18" s="31" t="n"/>
-      <c r="Q18" s="31" t="n"/>
+      <c r="P18" s="27" t="n"/>
+      <c r="Q18" s="27" t="n"/>
       <c r="R18" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -2508,10 +2489,10 @@
           <t>ADTHPL-280</t>
         </is>
       </c>
-      <c r="V18" s="32" t="n">
+      <c r="V18" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W18" s="32" t="n">
+      <c r="W18" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X18" s="8" t="n"/>
@@ -2584,8 +2565,8 @@
         <v>70</v>
       </c>
       <c r="O19" s="8" t="n"/>
-      <c r="P19" s="31" t="n"/>
-      <c r="Q19" s="31" t="n"/>
+      <c r="P19" s="27" t="n"/>
+      <c r="Q19" s="27" t="n"/>
       <c r="R19" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -2606,10 +2587,10 @@
           <t>ADTHPL-258</t>
         </is>
       </c>
-      <c r="V19" s="32" t="n">
+      <c r="V19" s="28" t="n">
         <v>46300</v>
       </c>
-      <c r="W19" s="32" t="n">
+      <c r="W19" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X19" s="8" t="n"/>
@@ -2682,8 +2663,8 @@
         <v>74</v>
       </c>
       <c r="O20" s="8" t="n"/>
-      <c r="P20" s="31" t="n"/>
-      <c r="Q20" s="31" t="n"/>
+      <c r="P20" s="27" t="n"/>
+      <c r="Q20" s="27" t="n"/>
       <c r="R20" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -2704,10 +2685,10 @@
           <t>ADTHPL-178</t>
         </is>
       </c>
-      <c r="V20" s="32" t="n">
+      <c r="V20" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W20" s="32" t="n">
+      <c r="W20" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X20" s="8" t="n"/>
@@ -2780,8 +2761,8 @@
         <v>32</v>
       </c>
       <c r="O21" s="8" t="n"/>
-      <c r="P21" s="31" t="n"/>
-      <c r="Q21" s="31" t="n"/>
+      <c r="P21" s="27" t="n"/>
+      <c r="Q21" s="27" t="n"/>
       <c r="R21" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -2802,10 +2783,10 @@
           <t>ADTHPL-281</t>
         </is>
       </c>
-      <c r="V21" s="32" t="n">
+      <c r="V21" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W21" s="32" t="n">
+      <c r="W21" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X21" s="8" t="n"/>
@@ -2878,8 +2859,8 @@
         <v>70</v>
       </c>
       <c r="O22" s="8" t="n"/>
-      <c r="P22" s="31" t="n"/>
-      <c r="Q22" s="31" t="n"/>
+      <c r="P22" s="27" t="n"/>
+      <c r="Q22" s="27" t="n"/>
       <c r="R22" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -2900,10 +2881,10 @@
           <t>ADTHPL-243</t>
         </is>
       </c>
-      <c r="V22" s="32" t="n">
+      <c r="V22" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W22" s="32" t="n">
+      <c r="W22" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X22" s="8" t="n"/>
@@ -2976,8 +2957,8 @@
         <v>74</v>
       </c>
       <c r="O23" s="8" t="n"/>
-      <c r="P23" s="31" t="n"/>
-      <c r="Q23" s="31" t="n"/>
+      <c r="P23" s="27" t="n"/>
+      <c r="Q23" s="27" t="n"/>
       <c r="R23" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -2998,10 +2979,10 @@
           <t>ADTHPL-169</t>
         </is>
       </c>
-      <c r="V23" s="32" t="n">
+      <c r="V23" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W23" s="32" t="n">
+      <c r="W23" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X23" s="8" t="n"/>
@@ -3074,8 +3055,8 @@
         <v>32</v>
       </c>
       <c r="O24" s="8" t="n"/>
-      <c r="P24" s="31" t="n"/>
-      <c r="Q24" s="31" t="n"/>
+      <c r="P24" s="27" t="n"/>
+      <c r="Q24" s="27" t="n"/>
       <c r="R24" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -3096,10 +3077,10 @@
           <t>ADTHPL-291</t>
         </is>
       </c>
-      <c r="V24" s="32" t="n">
+      <c r="V24" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W24" s="32" t="n">
+      <c r="W24" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X24" s="8" t="n"/>
@@ -3172,8 +3153,8 @@
         <v>70</v>
       </c>
       <c r="O25" s="8" t="n"/>
-      <c r="P25" s="31" t="n"/>
-      <c r="Q25" s="31" t="n"/>
+      <c r="P25" s="27" t="n"/>
+      <c r="Q25" s="27" t="n"/>
       <c r="R25" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -3194,10 +3175,10 @@
           <t>ADTHPL-243</t>
         </is>
       </c>
-      <c r="V25" s="32" t="n">
+      <c r="V25" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W25" s="32" t="n">
+      <c r="W25" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X25" s="8" t="n"/>
@@ -3270,8 +3251,8 @@
         <v>74</v>
       </c>
       <c r="O26" s="8" t="n"/>
-      <c r="P26" s="31" t="n"/>
-      <c r="Q26" s="31" t="n"/>
+      <c r="P26" s="27" t="n"/>
+      <c r="Q26" s="27" t="n"/>
       <c r="R26" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -3292,10 +3273,10 @@
           <t>ADTHPL-145</t>
         </is>
       </c>
-      <c r="V26" s="32" t="n">
+      <c r="V26" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W26" s="32" t="n">
+      <c r="W26" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X26" s="8" t="n"/>
@@ -3368,8 +3349,8 @@
         <v>32</v>
       </c>
       <c r="O27" s="8" t="n"/>
-      <c r="P27" s="31" t="n"/>
-      <c r="Q27" s="31" t="n"/>
+      <c r="P27" s="27" t="n"/>
+      <c r="Q27" s="27" t="n"/>
       <c r="R27" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -3390,10 +3371,10 @@
           <t>ADTHPL-292</t>
         </is>
       </c>
-      <c r="V27" s="32" t="n">
+      <c r="V27" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W27" s="32" t="n">
+      <c r="W27" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X27" s="8" t="n"/>
@@ -3466,8 +3447,8 @@
         <v>70</v>
       </c>
       <c r="O28" s="8" t="n"/>
-      <c r="P28" s="31" t="n"/>
-      <c r="Q28" s="31" t="n"/>
+      <c r="P28" s="27" t="n"/>
+      <c r="Q28" s="27" t="n"/>
       <c r="R28" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -3488,10 +3469,10 @@
           <t>ADTHPL-243</t>
         </is>
       </c>
-      <c r="V28" s="32" t="n">
+      <c r="V28" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W28" s="32" t="n">
+      <c r="W28" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X28" s="8" t="n"/>
@@ -3564,8 +3545,8 @@
         <v>74</v>
       </c>
       <c r="O29" s="8" t="n"/>
-      <c r="P29" s="31" t="n"/>
-      <c r="Q29" s="31" t="n"/>
+      <c r="P29" s="27" t="n"/>
+      <c r="Q29" s="27" t="n"/>
       <c r="R29" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -3586,10 +3567,10 @@
           <t>ADTHPL-171</t>
         </is>
       </c>
-      <c r="V29" s="32" t="n">
+      <c r="V29" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W29" s="32" t="n">
+      <c r="W29" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X29" s="8" t="n"/>
@@ -3662,8 +3643,8 @@
         <v>32</v>
       </c>
       <c r="O30" s="8" t="n"/>
-      <c r="P30" s="31" t="n"/>
-      <c r="Q30" s="31" t="n"/>
+      <c r="P30" s="27" t="n"/>
+      <c r="Q30" s="27" t="n"/>
       <c r="R30" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -3684,10 +3665,10 @@
           <t>ADTHPL-288</t>
         </is>
       </c>
-      <c r="V30" s="32" t="n">
+      <c r="V30" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W30" s="32" t="n">
+      <c r="W30" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X30" s="8" t="n"/>
@@ -3760,8 +3741,8 @@
         <v>70</v>
       </c>
       <c r="O31" s="8" t="n"/>
-      <c r="P31" s="31" t="n"/>
-      <c r="Q31" s="31" t="n"/>
+      <c r="P31" s="27" t="n"/>
+      <c r="Q31" s="27" t="n"/>
       <c r="R31" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -3782,10 +3763,10 @@
           <t>ADTHPL-257</t>
         </is>
       </c>
-      <c r="V31" s="32" t="n">
+      <c r="V31" s="28" t="n">
         <v>46300</v>
       </c>
-      <c r="W31" s="32" t="n">
+      <c r="W31" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X31" s="8" t="n"/>
@@ -3858,8 +3839,8 @@
         <v>74</v>
       </c>
       <c r="O32" s="8" t="n"/>
-      <c r="P32" s="31" t="n"/>
-      <c r="Q32" s="31" t="n"/>
+      <c r="P32" s="27" t="n"/>
+      <c r="Q32" s="27" t="n"/>
       <c r="R32" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -3880,10 +3861,10 @@
           <t>ADTHPL-145</t>
         </is>
       </c>
-      <c r="V32" s="32" t="n">
+      <c r="V32" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W32" s="32" t="n">
+      <c r="W32" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X32" s="8" t="n"/>
@@ -3956,8 +3937,8 @@
         <v>32</v>
       </c>
       <c r="O33" s="8" t="n"/>
-      <c r="P33" s="31" t="n"/>
-      <c r="Q33" s="31" t="n"/>
+      <c r="P33" s="27" t="n"/>
+      <c r="Q33" s="27" t="n"/>
       <c r="R33" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -3978,10 +3959,10 @@
           <t>ADTHPL-202</t>
         </is>
       </c>
-      <c r="V33" s="32" t="n">
+      <c r="V33" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W33" s="32" t="n">
+      <c r="W33" s="28" t="n">
         <v>46311</v>
       </c>
       <c r="X33" s="8" t="n"/>
@@ -4054,8 +4035,8 @@
         <v>70</v>
       </c>
       <c r="O34" s="8" t="n"/>
-      <c r="P34" s="31" t="n"/>
-      <c r="Q34" s="31" t="n"/>
+      <c r="P34" s="27" t="n"/>
+      <c r="Q34" s="27" t="n"/>
       <c r="R34" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -4076,10 +4057,10 @@
           <t>ADTHPL-258</t>
         </is>
       </c>
-      <c r="V34" s="32" t="n">
+      <c r="V34" s="28" t="n">
         <v>46300</v>
       </c>
-      <c r="W34" s="32" t="n">
+      <c r="W34" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X34" s="8" t="n"/>
@@ -4152,8 +4133,8 @@
         <v>176</v>
       </c>
       <c r="O35" s="8" t="n"/>
-      <c r="P35" s="31" t="n"/>
-      <c r="Q35" s="31" t="n"/>
+      <c r="P35" s="27" t="n"/>
+      <c r="Q35" s="27" t="n"/>
       <c r="R35" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -4174,10 +4155,10 @@
           <t>ADTHPL-246</t>
         </is>
       </c>
-      <c r="V35" s="32" t="n">
+      <c r="V35" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W35" s="32" t="n">
+      <c r="W35" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X35" s="8" t="n"/>
@@ -4250,8 +4231,8 @@
         <v>74</v>
       </c>
       <c r="O36" s="8" t="n"/>
-      <c r="P36" s="31" t="n"/>
-      <c r="Q36" s="31" t="n"/>
+      <c r="P36" s="27" t="n"/>
+      <c r="Q36" s="27" t="n"/>
       <c r="R36" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -4272,10 +4253,10 @@
           <t>ADTHPL-171</t>
         </is>
       </c>
-      <c r="V36" s="32" t="n">
+      <c r="V36" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W36" s="32" t="n">
+      <c r="W36" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X36" s="8" t="n"/>
@@ -4348,8 +4329,8 @@
         <v>32</v>
       </c>
       <c r="O37" s="8" t="n"/>
-      <c r="P37" s="31" t="n"/>
-      <c r="Q37" s="31" t="n"/>
+      <c r="P37" s="27" t="n"/>
+      <c r="Q37" s="27" t="n"/>
       <c r="R37" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -4370,10 +4351,10 @@
           <t>ADTHPL-289</t>
         </is>
       </c>
-      <c r="V37" s="32" t="n">
+      <c r="V37" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W37" s="32" t="n">
+      <c r="W37" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X37" s="8" t="n"/>
@@ -4446,8 +4427,8 @@
         <v>70</v>
       </c>
       <c r="O38" s="8" t="n"/>
-      <c r="P38" s="31" t="n"/>
-      <c r="Q38" s="31" t="n"/>
+      <c r="P38" s="27" t="n"/>
+      <c r="Q38" s="27" t="n"/>
       <c r="R38" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -4468,10 +4449,10 @@
           <t>ADTHPL-257</t>
         </is>
       </c>
-      <c r="V38" s="32" t="n">
+      <c r="V38" s="28" t="n">
         <v>46300</v>
       </c>
-      <c r="W38" s="32" t="n">
+      <c r="W38" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X38" s="8" t="n"/>
@@ -4544,8 +4525,8 @@
         <v>74</v>
       </c>
       <c r="O39" s="8" t="n"/>
-      <c r="P39" s="31" t="n"/>
-      <c r="Q39" s="31" t="n"/>
+      <c r="P39" s="27" t="n"/>
+      <c r="Q39" s="27" t="n"/>
       <c r="R39" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -4566,10 +4547,10 @@
           <t>ADTHPL-158</t>
         </is>
       </c>
-      <c r="V39" s="32" t="n">
+      <c r="V39" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W39" s="32" t="n">
+      <c r="W39" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X39" s="8" t="n"/>
@@ -4642,8 +4623,8 @@
         <v>32</v>
       </c>
       <c r="O40" s="8" t="n"/>
-      <c r="P40" s="31" t="n"/>
-      <c r="Q40" s="31" t="n"/>
+      <c r="P40" s="27" t="n"/>
+      <c r="Q40" s="27" t="n"/>
       <c r="R40" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -4664,10 +4645,10 @@
           <t>ADTHPL-288</t>
         </is>
       </c>
-      <c r="V40" s="32" t="n">
+      <c r="V40" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W40" s="32" t="n">
+      <c r="W40" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X40" s="8" t="n"/>
@@ -4740,8 +4721,8 @@
         <v>70</v>
       </c>
       <c r="O41" s="8" t="n"/>
-      <c r="P41" s="31" t="n"/>
-      <c r="Q41" s="31" t="n"/>
+      <c r="P41" s="27" t="n"/>
+      <c r="Q41" s="27" t="n"/>
       <c r="R41" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -4762,10 +4743,10 @@
           <t>ADTHPL-257</t>
         </is>
       </c>
-      <c r="V41" s="32" t="n">
+      <c r="V41" s="28" t="n">
         <v>46300</v>
       </c>
-      <c r="W41" s="32" t="n">
+      <c r="W41" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X41" s="8" t="n"/>
@@ -4838,8 +4819,8 @@
         <v>74</v>
       </c>
       <c r="O42" s="8" t="n"/>
-      <c r="P42" s="31" t="n"/>
-      <c r="Q42" s="31" t="n"/>
+      <c r="P42" s="27" t="n"/>
+      <c r="Q42" s="27" t="n"/>
       <c r="R42" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -4860,10 +4841,10 @@
           <t>ADTHPL-143</t>
         </is>
       </c>
-      <c r="V42" s="32" t="n">
+      <c r="V42" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W42" s="32" t="n">
+      <c r="W42" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X42" s="8" t="n"/>
@@ -4936,8 +4917,8 @@
         <v>32</v>
       </c>
       <c r="O43" s="8" t="n"/>
-      <c r="P43" s="31" t="n"/>
-      <c r="Q43" s="31" t="n"/>
+      <c r="P43" s="27" t="n"/>
+      <c r="Q43" s="27" t="n"/>
       <c r="R43" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -4958,10 +4939,10 @@
           <t>ADTHPL-289</t>
         </is>
       </c>
-      <c r="V43" s="32" t="n">
+      <c r="V43" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W43" s="32" t="n">
+      <c r="W43" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X43" s="8" t="n"/>
@@ -5034,8 +5015,8 @@
         <v>70</v>
       </c>
       <c r="O44" s="8" t="n"/>
-      <c r="P44" s="31" t="n"/>
-      <c r="Q44" s="31" t="n"/>
+      <c r="P44" s="27" t="n"/>
+      <c r="Q44" s="27" t="n"/>
       <c r="R44" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -5056,10 +5037,10 @@
           <t>ADTHPL-257</t>
         </is>
       </c>
-      <c r="V44" s="32" t="n">
+      <c r="V44" s="28" t="n">
         <v>46300</v>
       </c>
-      <c r="W44" s="32" t="n">
+      <c r="W44" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X44" s="8" t="n"/>
@@ -5128,8 +5109,8 @@
         <v>17.6</v>
       </c>
       <c r="O45" s="8" t="n"/>
-      <c r="P45" s="31" t="n"/>
-      <c r="Q45" s="31" t="n"/>
+      <c r="P45" s="27" t="n"/>
+      <c r="Q45" s="27" t="n"/>
       <c r="R45" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -5150,10 +5131,10 @@
           <t>ADTHPL-248</t>
         </is>
       </c>
-      <c r="V45" s="32" t="n">
+      <c r="V45" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W45" s="32" t="n">
+      <c r="W45" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X45" s="8" t="n"/>
@@ -5222,8 +5203,8 @@
         <v>176</v>
       </c>
       <c r="O46" s="8" t="n"/>
-      <c r="P46" s="31" t="n"/>
-      <c r="Q46" s="31" t="n"/>
+      <c r="P46" s="27" t="n"/>
+      <c r="Q46" s="27" t="n"/>
       <c r="R46" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -5244,10 +5225,10 @@
           <t>ADTHPL-249</t>
         </is>
       </c>
-      <c r="V46" s="32" t="n">
+      <c r="V46" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W46" s="32" t="n">
+      <c r="W46" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X46" s="8" t="n"/>
@@ -5320,8 +5301,8 @@
         <v>120</v>
       </c>
       <c r="O47" s="8" t="n"/>
-      <c r="P47" s="31" t="n"/>
-      <c r="Q47" s="31" t="n"/>
+      <c r="P47" s="27" t="n"/>
+      <c r="Q47" s="27" t="n"/>
       <c r="R47" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -5342,10 +5323,10 @@
           <t>ADTHPL-144</t>
         </is>
       </c>
-      <c r="V47" s="32" t="n">
+      <c r="V47" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W47" s="32" t="n">
+      <c r="W47" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X47" s="8" t="n"/>
@@ -5418,8 +5399,8 @@
         <v>56</v>
       </c>
       <c r="O48" s="8" t="n"/>
-      <c r="P48" s="31" t="n"/>
-      <c r="Q48" s="31" t="n"/>
+      <c r="P48" s="27" t="n"/>
+      <c r="Q48" s="27" t="n"/>
       <c r="R48" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -5440,10 +5421,10 @@
           <t>ADTHPL-279</t>
         </is>
       </c>
-      <c r="V48" s="32" t="n">
+      <c r="V48" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W48" s="32" t="n">
+      <c r="W48" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X48" s="8" t="n"/>
@@ -5516,8 +5497,8 @@
         <v>120</v>
       </c>
       <c r="O49" s="8" t="n"/>
-      <c r="P49" s="31" t="n"/>
-      <c r="Q49" s="31" t="n"/>
+      <c r="P49" s="27" t="n"/>
+      <c r="Q49" s="27" t="n"/>
       <c r="R49" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -5538,10 +5519,10 @@
           <t>ADTHPL-204</t>
         </is>
       </c>
-      <c r="V49" s="32" t="n">
+      <c r="V49" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W49" s="32" t="n">
+      <c r="W49" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X49" s="8" t="n"/>
@@ -5614,8 +5595,8 @@
         <v>56</v>
       </c>
       <c r="O50" s="8" t="n"/>
-      <c r="P50" s="31" t="n"/>
-      <c r="Q50" s="31" t="n"/>
+      <c r="P50" s="27" t="n"/>
+      <c r="Q50" s="27" t="n"/>
       <c r="R50" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -5636,10 +5617,10 @@
           <t>ADTHPL-182</t>
         </is>
       </c>
-      <c r="V50" s="32" t="n">
+      <c r="V50" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W50" s="32" t="n">
+      <c r="W50" s="28" t="n">
         <v>46304</v>
       </c>
       <c r="X50" s="8" t="n"/>
@@ -5712,8 +5693,8 @@
         <v>120</v>
       </c>
       <c r="O51" s="8" t="n"/>
-      <c r="P51" s="31" t="n"/>
-      <c r="Q51" s="31" t="n"/>
+      <c r="P51" s="27" t="n"/>
+      <c r="Q51" s="27" t="n"/>
       <c r="R51" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -5734,10 +5715,10 @@
           <t>ADTHPL-214</t>
         </is>
       </c>
-      <c r="V51" s="32" t="n">
+      <c r="V51" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W51" s="32" t="n">
+      <c r="W51" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X51" s="8" t="n"/>
@@ -5810,8 +5791,8 @@
         <v>56</v>
       </c>
       <c r="O52" s="8" t="n"/>
-      <c r="P52" s="31" t="n"/>
-      <c r="Q52" s="31" t="n"/>
+      <c r="P52" s="27" t="n"/>
+      <c r="Q52" s="27" t="n"/>
       <c r="R52" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -5832,10 +5813,10 @@
           <t>ADTHPL-182</t>
         </is>
       </c>
-      <c r="V52" s="32" t="n">
+      <c r="V52" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W52" s="32" t="n">
+      <c r="W52" s="28" t="n">
         <v>46304</v>
       </c>
       <c r="X52" s="8" t="n"/>
@@ -5908,8 +5889,8 @@
         <v>120</v>
       </c>
       <c r="O53" s="8" t="n"/>
-      <c r="P53" s="31" t="n"/>
-      <c r="Q53" s="31" t="n"/>
+      <c r="P53" s="27" t="n"/>
+      <c r="Q53" s="27" t="n"/>
       <c r="R53" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -5930,10 +5911,10 @@
           <t>ADTHPL-215</t>
         </is>
       </c>
-      <c r="V53" s="32" t="n">
+      <c r="V53" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W53" s="32" t="n">
+      <c r="W53" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X53" s="8" t="n"/>
@@ -6006,8 +5987,8 @@
         <v>56</v>
       </c>
       <c r="O54" s="8" t="n"/>
-      <c r="P54" s="31" t="n"/>
-      <c r="Q54" s="31" t="n"/>
+      <c r="P54" s="27" t="n"/>
+      <c r="Q54" s="27" t="n"/>
       <c r="R54" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -6028,10 +6009,10 @@
           <t>ADTHPL-184</t>
         </is>
       </c>
-      <c r="V54" s="32" t="n">
+      <c r="V54" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W54" s="32" t="n">
+      <c r="W54" s="28" t="n">
         <v>46304</v>
       </c>
       <c r="X54" s="8" t="n"/>
@@ -6104,8 +6085,8 @@
         <v>74</v>
       </c>
       <c r="O55" s="8" t="n"/>
-      <c r="P55" s="31" t="n"/>
-      <c r="Q55" s="31" t="n"/>
+      <c r="P55" s="27" t="n"/>
+      <c r="Q55" s="27" t="n"/>
       <c r="R55" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -6126,10 +6107,10 @@
           <t>ADTHPL-195</t>
         </is>
       </c>
-      <c r="V55" s="32" t="n">
+      <c r="V55" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W55" s="32" t="n">
+      <c r="W55" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X55" s="8" t="n"/>
@@ -6202,8 +6183,8 @@
         <v>56</v>
       </c>
       <c r="O56" s="8" t="n"/>
-      <c r="P56" s="31" t="n"/>
-      <c r="Q56" s="31" t="n"/>
+      <c r="P56" s="27" t="n"/>
+      <c r="Q56" s="27" t="n"/>
       <c r="R56" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -6224,10 +6205,10 @@
           <t>ADTHPL-180</t>
         </is>
       </c>
-      <c r="V56" s="32" t="n">
+      <c r="V56" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W56" s="32" t="n">
+      <c r="W56" s="28" t="n">
         <v>46304</v>
       </c>
       <c r="X56" s="8" t="n"/>
@@ -6300,8 +6281,8 @@
         <v>46</v>
       </c>
       <c r="O57" s="8" t="n"/>
-      <c r="P57" s="31" t="n"/>
-      <c r="Q57" s="31" t="n"/>
+      <c r="P57" s="27" t="n"/>
+      <c r="Q57" s="27" t="n"/>
       <c r="R57" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -6322,10 +6303,10 @@
           <t>ADTHPL-203</t>
         </is>
       </c>
-      <c r="V57" s="32" t="n">
+      <c r="V57" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W57" s="32" t="n">
+      <c r="W57" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X57" s="8" t="n"/>
@@ -6398,8 +6379,8 @@
         <v>120</v>
       </c>
       <c r="O58" s="8" t="n"/>
-      <c r="P58" s="31" t="n"/>
-      <c r="Q58" s="31" t="n"/>
+      <c r="P58" s="27" t="n"/>
+      <c r="Q58" s="27" t="n"/>
       <c r="R58" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -6420,10 +6401,10 @@
           <t>ADTHPL-203</t>
         </is>
       </c>
-      <c r="V58" s="32" t="n">
+      <c r="V58" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W58" s="32" t="n">
+      <c r="W58" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X58" s="8" t="n"/>
@@ -6496,8 +6477,8 @@
         <v>56</v>
       </c>
       <c r="O59" s="8" t="n"/>
-      <c r="P59" s="31" t="n"/>
-      <c r="Q59" s="31" t="n"/>
+      <c r="P59" s="27" t="n"/>
+      <c r="Q59" s="27" t="n"/>
       <c r="R59" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -6518,10 +6499,10 @@
           <t>ADTHPL-180</t>
         </is>
       </c>
-      <c r="V59" s="32" t="n">
+      <c r="V59" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W59" s="32" t="n">
+      <c r="W59" s="28" t="n">
         <v>46304</v>
       </c>
       <c r="X59" s="8" t="n"/>
@@ -6594,8 +6575,8 @@
         <v>104</v>
       </c>
       <c r="O60" s="8" t="n"/>
-      <c r="P60" s="31" t="n"/>
-      <c r="Q60" s="31" t="n"/>
+      <c r="P60" s="27" t="n"/>
+      <c r="Q60" s="27" t="n"/>
       <c r="R60" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -6616,10 +6597,10 @@
           <t>ADTHPL-195</t>
         </is>
       </c>
-      <c r="V60" s="32" t="n">
+      <c r="V60" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W60" s="32" t="n">
+      <c r="W60" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X60" s="8" t="n"/>
@@ -6692,8 +6673,8 @@
         <v>40</v>
       </c>
       <c r="O61" s="8" t="n"/>
-      <c r="P61" s="31" t="n"/>
-      <c r="Q61" s="31" t="n"/>
+      <c r="P61" s="27" t="n"/>
+      <c r="Q61" s="27" t="n"/>
       <c r="R61" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -6714,10 +6695,10 @@
           <t>ADTHPL-203</t>
         </is>
       </c>
-      <c r="V61" s="32" t="n">
+      <c r="V61" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W61" s="32" t="n">
+      <c r="W61" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X61" s="8" t="n"/>
@@ -6790,8 +6771,8 @@
         <v>32</v>
       </c>
       <c r="O62" s="8" t="n"/>
-      <c r="P62" s="31" t="n"/>
-      <c r="Q62" s="31" t="n"/>
+      <c r="P62" s="27" t="n"/>
+      <c r="Q62" s="27" t="n"/>
       <c r="R62" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -6812,10 +6793,10 @@
           <t>ADTHPL-180</t>
         </is>
       </c>
-      <c r="V62" s="32" t="n">
+      <c r="V62" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W62" s="32" t="n">
+      <c r="W62" s="28" t="n">
         <v>46304</v>
       </c>
       <c r="X62" s="8" t="n"/>
@@ -6888,8 +6869,8 @@
         <v>120</v>
       </c>
       <c r="O63" s="8" t="n"/>
-      <c r="P63" s="31" t="n"/>
-      <c r="Q63" s="31" t="n"/>
+      <c r="P63" s="27" t="n"/>
+      <c r="Q63" s="27" t="n"/>
       <c r="R63" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -6910,10 +6891,10 @@
           <t>ADTHPL-205</t>
         </is>
       </c>
-      <c r="V63" s="32" t="n">
+      <c r="V63" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W63" s="32" t="n">
+      <c r="W63" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X63" s="8" t="n"/>
@@ -6986,8 +6967,8 @@
         <v>56</v>
       </c>
       <c r="O64" s="8" t="n"/>
-      <c r="P64" s="31" t="n"/>
-      <c r="Q64" s="31" t="n"/>
+      <c r="P64" s="27" t="n"/>
+      <c r="Q64" s="27" t="n"/>
       <c r="R64" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -7008,10 +6989,10 @@
           <t>ADTHPL-181</t>
         </is>
       </c>
-      <c r="V64" s="32" t="n">
+      <c r="V64" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W64" s="32" t="n">
+      <c r="W64" s="28" t="n">
         <v>46304</v>
       </c>
       <c r="X64" s="8" t="n"/>
@@ -7084,8 +7065,8 @@
         <v>104</v>
       </c>
       <c r="O65" s="8" t="n"/>
-      <c r="P65" s="31" t="n"/>
-      <c r="Q65" s="31" t="n"/>
+      <c r="P65" s="27" t="n"/>
+      <c r="Q65" s="27" t="n"/>
       <c r="R65" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -7106,10 +7087,10 @@
           <t>ADTHPL-197</t>
         </is>
       </c>
-      <c r="V65" s="32" t="n">
+      <c r="V65" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W65" s="32" t="n">
+      <c r="W65" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X65" s="8" t="n"/>
@@ -7182,8 +7163,8 @@
         <v>40</v>
       </c>
       <c r="O66" s="8" t="n"/>
-      <c r="P66" s="31" t="n"/>
-      <c r="Q66" s="31" t="n"/>
+      <c r="P66" s="27" t="n"/>
+      <c r="Q66" s="27" t="n"/>
       <c r="R66" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -7204,10 +7185,10 @@
           <t>ADTHPL-297</t>
         </is>
       </c>
-      <c r="V66" s="32" t="n">
+      <c r="V66" s="28" t="n">
         <v>46321</v>
       </c>
-      <c r="W66" s="32" t="n">
+      <c r="W66" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X66" s="8" t="n"/>
@@ -7280,8 +7261,8 @@
         <v>32</v>
       </c>
       <c r="O67" s="8" t="n"/>
-      <c r="P67" s="31" t="n"/>
-      <c r="Q67" s="31" t="n"/>
+      <c r="P67" s="27" t="n"/>
+      <c r="Q67" s="27" t="n"/>
       <c r="R67" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -7302,10 +7283,10 @@
           <t>ADTHPL-183</t>
         </is>
       </c>
-      <c r="V67" s="32" t="n">
+      <c r="V67" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W67" s="32" t="n">
+      <c r="W67" s="28" t="n">
         <v>46304</v>
       </c>
       <c r="X67" s="8" t="n"/>
@@ -7378,8 +7359,8 @@
         <v>104</v>
       </c>
       <c r="O68" s="8" t="n"/>
-      <c r="P68" s="31" t="n"/>
-      <c r="Q68" s="31" t="n"/>
+      <c r="P68" s="27" t="n"/>
+      <c r="Q68" s="27" t="n"/>
       <c r="R68" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -7400,10 +7381,10 @@
           <t>ADTHPL-196</t>
         </is>
       </c>
-      <c r="V68" s="32" t="n">
+      <c r="V68" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W68" s="32" t="n">
+      <c r="W68" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X68" s="8" t="n"/>
@@ -7476,8 +7457,8 @@
         <v>40</v>
       </c>
       <c r="O69" s="8" t="n"/>
-      <c r="P69" s="31" t="n"/>
-      <c r="Q69" s="31" t="n"/>
+      <c r="P69" s="27" t="n"/>
+      <c r="Q69" s="27" t="n"/>
       <c r="R69" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -7498,10 +7479,10 @@
           <t>ADTHPL-295</t>
         </is>
       </c>
-      <c r="V69" s="32" t="n">
+      <c r="V69" s="28" t="n">
         <v>46321</v>
       </c>
-      <c r="W69" s="32" t="n">
+      <c r="W69" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X69" s="8" t="n"/>
@@ -7574,8 +7555,8 @@
         <v>32</v>
       </c>
       <c r="O70" s="8" t="n"/>
-      <c r="P70" s="31" t="n"/>
-      <c r="Q70" s="31" t="n"/>
+      <c r="P70" s="27" t="n"/>
+      <c r="Q70" s="27" t="n"/>
       <c r="R70" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -7596,10 +7577,10 @@
           <t>ADTHPL-184</t>
         </is>
       </c>
-      <c r="V70" s="32" t="n">
+      <c r="V70" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W70" s="32" t="n">
+      <c r="W70" s="28" t="n">
         <v>46304</v>
       </c>
       <c r="X70" s="8" t="n"/>
@@ -7674,10 +7655,10 @@
       <c r="O71" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="P71" s="31" t="n">
+      <c r="P71" s="27" t="n">
         <v>46303</v>
       </c>
-      <c r="Q71" s="31" t="n">
+      <c r="Q71" s="27" t="n">
         <v>46304</v>
       </c>
       <c r="R71" s="8" t="inlineStr">
@@ -7700,10 +7681,10 @@
           <t>ADTHPL-221</t>
         </is>
       </c>
-      <c r="V71" s="32" t="n">
+      <c r="V71" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W71" s="32" t="n">
+      <c r="W71" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X71" s="8" t="n"/>
@@ -7776,8 +7757,8 @@
         <v>120</v>
       </c>
       <c r="O72" s="8" t="n"/>
-      <c r="P72" s="31" t="n"/>
-      <c r="Q72" s="31" t="n"/>
+      <c r="P72" s="27" t="n"/>
+      <c r="Q72" s="27" t="n"/>
       <c r="R72" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -7798,10 +7779,10 @@
           <t>ADTHPL-165</t>
         </is>
       </c>
-      <c r="V72" s="32" t="n">
+      <c r="V72" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W72" s="32" t="n">
+      <c r="W72" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X72" s="8" t="n"/>
@@ -7874,8 +7855,8 @@
         <v>56</v>
       </c>
       <c r="O73" s="8" t="n"/>
-      <c r="P73" s="31" t="n"/>
-      <c r="Q73" s="31" t="n"/>
+      <c r="P73" s="27" t="n"/>
+      <c r="Q73" s="27" t="n"/>
       <c r="R73" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -7896,10 +7877,10 @@
           <t>ADTHPL-290</t>
         </is>
       </c>
-      <c r="V73" s="32" t="n">
+      <c r="V73" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W73" s="32" t="n">
+      <c r="W73" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X73" s="8" t="n"/>
@@ -7972,8 +7953,8 @@
         <v>120</v>
       </c>
       <c r="O74" s="8" t="n"/>
-      <c r="P74" s="31" t="n"/>
-      <c r="Q74" s="31" t="n"/>
+      <c r="P74" s="27" t="n"/>
+      <c r="Q74" s="27" t="n"/>
       <c r="R74" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -7994,10 +7975,10 @@
           <t>ADTHPL-147</t>
         </is>
       </c>
-      <c r="V74" s="32" t="n">
+      <c r="V74" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W74" s="32" t="n">
+      <c r="W74" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X74" s="8" t="n"/>
@@ -8070,8 +8051,8 @@
         <v>56</v>
       </c>
       <c r="O75" s="8" t="n"/>
-      <c r="P75" s="31" t="n"/>
-      <c r="Q75" s="31" t="n"/>
+      <c r="P75" s="27" t="n"/>
+      <c r="Q75" s="27" t="n"/>
       <c r="R75" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -8092,10 +8073,10 @@
           <t>ADTHPL-290</t>
         </is>
       </c>
-      <c r="V75" s="32" t="n">
+      <c r="V75" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W75" s="32" t="n">
+      <c r="W75" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X75" s="8" t="n"/>
@@ -8168,8 +8149,8 @@
         <v>120</v>
       </c>
       <c r="O76" s="8" t="n"/>
-      <c r="P76" s="31" t="n"/>
-      <c r="Q76" s="31" t="n"/>
+      <c r="P76" s="27" t="n"/>
+      <c r="Q76" s="27" t="n"/>
       <c r="R76" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -8190,10 +8171,10 @@
           <t>ADTHPL-216</t>
         </is>
       </c>
-      <c r="V76" s="32" t="n">
+      <c r="V76" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W76" s="32" t="n">
+      <c r="W76" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X76" s="8" t="n"/>
@@ -8266,8 +8247,8 @@
         <v>56</v>
       </c>
       <c r="O77" s="8" t="n"/>
-      <c r="P77" s="31" t="n"/>
-      <c r="Q77" s="31" t="n"/>
+      <c r="P77" s="27" t="n"/>
+      <c r="Q77" s="27" t="n"/>
       <c r="R77" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -8288,10 +8269,10 @@
           <t>ADTHPL-183</t>
         </is>
       </c>
-      <c r="V77" s="32" t="n">
+      <c r="V77" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W77" s="32" t="n">
+      <c r="W77" s="28" t="n">
         <v>46304</v>
       </c>
       <c r="X77" s="8" t="n"/>
@@ -8364,8 +8345,8 @@
         <v>120</v>
       </c>
       <c r="O78" s="8" t="n"/>
-      <c r="P78" s="31" t="n"/>
-      <c r="Q78" s="31" t="n"/>
+      <c r="P78" s="27" t="n"/>
+      <c r="Q78" s="27" t="n"/>
       <c r="R78" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -8386,10 +8367,10 @@
           <t>ADTHPL-167</t>
         </is>
       </c>
-      <c r="V78" s="32" t="n">
+      <c r="V78" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W78" s="32" t="n">
+      <c r="W78" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X78" s="8" t="n"/>
@@ -8462,8 +8443,8 @@
         <v>56</v>
       </c>
       <c r="O79" s="8" t="n"/>
-      <c r="P79" s="31" t="n"/>
-      <c r="Q79" s="31" t="n"/>
+      <c r="P79" s="27" t="n"/>
+      <c r="Q79" s="27" t="n"/>
       <c r="R79" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -8484,10 +8465,10 @@
           <t>ADTHPL-168</t>
         </is>
       </c>
-      <c r="V79" s="32" t="n">
+      <c r="V79" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W79" s="32" t="n">
+      <c r="W79" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X79" s="8" t="n"/>
@@ -8560,8 +8541,8 @@
         <v>88</v>
       </c>
       <c r="O80" s="8" t="n"/>
-      <c r="P80" s="31" t="n"/>
-      <c r="Q80" s="31" t="n"/>
+      <c r="P80" s="27" t="n"/>
+      <c r="Q80" s="27" t="n"/>
       <c r="R80" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -8582,10 +8563,10 @@
           <t>ADTHPL-200</t>
         </is>
       </c>
-      <c r="V80" s="32" t="n">
+      <c r="V80" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W80" s="32" t="n">
+      <c r="W80" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X80" s="8" t="n"/>
@@ -8658,8 +8639,8 @@
         <v>88</v>
       </c>
       <c r="O81" s="8" t="n"/>
-      <c r="P81" s="31" t="n"/>
-      <c r="Q81" s="31" t="n"/>
+      <c r="P81" s="27" t="n"/>
+      <c r="Q81" s="27" t="n"/>
       <c r="R81" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -8680,10 +8661,10 @@
           <t>ADTHPL-201</t>
         </is>
       </c>
-      <c r="V81" s="32" t="n">
+      <c r="V81" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W81" s="32" t="n">
+      <c r="W81" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X81" s="8" t="n"/>
@@ -8756,8 +8737,8 @@
         <v>37</v>
       </c>
       <c r="O82" s="8" t="n"/>
-      <c r="P82" s="31" t="n"/>
-      <c r="Q82" s="31" t="n"/>
+      <c r="P82" s="27" t="n"/>
+      <c r="Q82" s="27" t="n"/>
       <c r="R82" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -8778,10 +8759,10 @@
           <t>ADTHPL-149</t>
         </is>
       </c>
-      <c r="V82" s="32" t="n">
+      <c r="V82" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W82" s="32" t="n">
+      <c r="W82" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X82" s="8" t="n"/>
@@ -8854,8 +8835,8 @@
         <v>16</v>
       </c>
       <c r="O83" s="8" t="n"/>
-      <c r="P83" s="31" t="n"/>
-      <c r="Q83" s="31" t="n"/>
+      <c r="P83" s="27" t="n"/>
+      <c r="Q83" s="27" t="n"/>
       <c r="R83" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -8876,10 +8857,10 @@
           <t>ADTHPL-278</t>
         </is>
       </c>
-      <c r="V83" s="32" t="n">
+      <c r="V83" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W83" s="32" t="n">
+      <c r="W83" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X83" s="8" t="n"/>
@@ -8952,8 +8933,8 @@
         <v>123</v>
       </c>
       <c r="O84" s="8" t="n"/>
-      <c r="P84" s="31" t="n"/>
-      <c r="Q84" s="31" t="n"/>
+      <c r="P84" s="27" t="n"/>
+      <c r="Q84" s="27" t="n"/>
       <c r="R84" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -8974,10 +8955,10 @@
           <t>ADTHPL-234</t>
         </is>
       </c>
-      <c r="V84" s="32" t="n">
+      <c r="V84" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W84" s="32" t="n">
+      <c r="W84" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X84" s="8" t="n"/>
@@ -9050,8 +9031,8 @@
         <v>37</v>
       </c>
       <c r="O85" s="8" t="n"/>
-      <c r="P85" s="31" t="n"/>
-      <c r="Q85" s="31" t="n"/>
+      <c r="P85" s="27" t="n"/>
+      <c r="Q85" s="27" t="n"/>
       <c r="R85" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -9072,10 +9053,10 @@
           <t>ADTHPL-154</t>
         </is>
       </c>
-      <c r="V85" s="32" t="n">
+      <c r="V85" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W85" s="32" t="n">
+      <c r="W85" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X85" s="8" t="n"/>
@@ -9148,8 +9129,8 @@
         <v>16</v>
       </c>
       <c r="O86" s="8" t="n"/>
-      <c r="P86" s="31" t="n"/>
-      <c r="Q86" s="31" t="n"/>
+      <c r="P86" s="27" t="n"/>
+      <c r="Q86" s="27" t="n"/>
       <c r="R86" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -9170,10 +9151,10 @@
           <t>ADTHPL-282</t>
         </is>
       </c>
-      <c r="V86" s="32" t="n">
+      <c r="V86" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W86" s="32" t="n">
+      <c r="W86" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X86" s="8" t="n"/>
@@ -9246,8 +9227,8 @@
         <v>123</v>
       </c>
       <c r="O87" s="8" t="n"/>
-      <c r="P87" s="31" t="n"/>
-      <c r="Q87" s="31" t="n"/>
+      <c r="P87" s="27" t="n"/>
+      <c r="Q87" s="27" t="n"/>
       <c r="R87" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -9268,10 +9249,10 @@
           <t>ADTHPL-227</t>
         </is>
       </c>
-      <c r="V87" s="32" t="n">
+      <c r="V87" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W87" s="32" t="n">
+      <c r="W87" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X87" s="8" t="n"/>
@@ -9344,8 +9325,8 @@
         <v>37</v>
       </c>
       <c r="O88" s="8" t="n"/>
-      <c r="P88" s="31" t="n"/>
-      <c r="Q88" s="31" t="n"/>
+      <c r="P88" s="27" t="n"/>
+      <c r="Q88" s="27" t="n"/>
       <c r="R88" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -9366,10 +9347,10 @@
           <t>ADTHPL-170</t>
         </is>
       </c>
-      <c r="V88" s="32" t="n">
+      <c r="V88" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W88" s="32" t="n">
+      <c r="W88" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X88" s="8" t="n"/>
@@ -9442,8 +9423,8 @@
         <v>16</v>
       </c>
       <c r="O89" s="8" t="n"/>
-      <c r="P89" s="31" t="n"/>
-      <c r="Q89" s="31" t="n"/>
+      <c r="P89" s="27" t="n"/>
+      <c r="Q89" s="27" t="n"/>
       <c r="R89" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -9464,10 +9445,10 @@
           <t>ADTHPL-278</t>
         </is>
       </c>
-      <c r="V89" s="32" t="n">
+      <c r="V89" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W89" s="32" t="n">
+      <c r="W89" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X89" s="8" t="n"/>
@@ -9540,8 +9521,8 @@
         <v>123</v>
       </c>
       <c r="O90" s="8" t="n"/>
-      <c r="P90" s="31" t="n"/>
-      <c r="Q90" s="31" t="n"/>
+      <c r="P90" s="27" t="n"/>
+      <c r="Q90" s="27" t="n"/>
       <c r="R90" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -9562,10 +9543,10 @@
           <t>ADTHPL-227</t>
         </is>
       </c>
-      <c r="V90" s="32" t="n">
+      <c r="V90" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W90" s="32" t="n">
+      <c r="W90" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X90" s="8" t="n"/>
@@ -9638,8 +9619,8 @@
         <v>176</v>
       </c>
       <c r="O91" s="8" t="n"/>
-      <c r="P91" s="31" t="n"/>
-      <c r="Q91" s="31" t="n"/>
+      <c r="P91" s="27" t="n"/>
+      <c r="Q91" s="27" t="n"/>
       <c r="R91" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -9660,10 +9641,10 @@
           <t>ADTHPL-247</t>
         </is>
       </c>
-      <c r="V91" s="32" t="n">
+      <c r="V91" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W91" s="32" t="n">
+      <c r="W91" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X91" s="8" t="n"/>
@@ -9736,8 +9717,8 @@
         <v>176</v>
       </c>
       <c r="O92" s="8" t="n"/>
-      <c r="P92" s="31" t="n"/>
-      <c r="Q92" s="31" t="n"/>
+      <c r="P92" s="27" t="n"/>
+      <c r="Q92" s="27" t="n"/>
       <c r="R92" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -9758,10 +9739,10 @@
           <t>ADTHPL-250</t>
         </is>
       </c>
-      <c r="V92" s="32" t="n">
+      <c r="V92" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W92" s="32" t="n">
+      <c r="W92" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X92" s="8" t="n"/>
@@ -9834,8 +9815,8 @@
         <v>120</v>
       </c>
       <c r="O93" s="8" t="n"/>
-      <c r="P93" s="31" t="n"/>
-      <c r="Q93" s="31" t="n"/>
+      <c r="P93" s="27" t="n"/>
+      <c r="Q93" s="27" t="n"/>
       <c r="R93" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -9856,10 +9837,10 @@
           <t>ADTHPL-269</t>
         </is>
       </c>
-      <c r="V93" s="32" t="n">
+      <c r="V93" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="W93" s="32" t="n">
+      <c r="W93" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X93" s="8" t="n"/>
@@ -9932,8 +9913,8 @@
         <v>56</v>
       </c>
       <c r="O94" s="8" t="n"/>
-      <c r="P94" s="31" t="n"/>
-      <c r="Q94" s="31" t="n"/>
+      <c r="P94" s="27" t="n"/>
+      <c r="Q94" s="27" t="n"/>
       <c r="R94" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -9954,10 +9935,10 @@
           <t>ADTHPL-220</t>
         </is>
       </c>
-      <c r="V94" s="32" t="n">
+      <c r="V94" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W94" s="32" t="n">
+      <c r="W94" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X94" s="8" t="n"/>
@@ -10032,10 +10013,10 @@
       <c r="O95" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="P95" s="31" t="n">
+      <c r="P95" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="Q95" s="31" t="n">
+      <c r="Q95" s="27" t="n">
         <v>46304</v>
       </c>
       <c r="R95" s="8" t="inlineStr">
@@ -10058,10 +10039,10 @@
           <t>ADTHPL-175</t>
         </is>
       </c>
-      <c r="V95" s="32" t="n">
+      <c r="V95" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="W95" s="32" t="n">
+      <c r="W95" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X95" s="8" t="n"/>
@@ -10136,10 +10117,10 @@
       <c r="O96" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="P96" s="31" t="n">
+      <c r="P96" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="Q96" s="31" t="n">
+      <c r="Q96" s="27" t="n">
         <v>46304</v>
       </c>
       <c r="R96" s="8" t="inlineStr">
@@ -10162,10 +10143,10 @@
           <t>ADTHPL-177</t>
         </is>
       </c>
-      <c r="V96" s="32" t="n">
+      <c r="V96" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="W96" s="32" t="n">
+      <c r="W96" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X96" s="8" t="n"/>
@@ -10238,8 +10219,8 @@
         <v>88</v>
       </c>
       <c r="O97" s="8" t="n"/>
-      <c r="P97" s="31" t="n"/>
-      <c r="Q97" s="31" t="n"/>
+      <c r="P97" s="27" t="n"/>
+      <c r="Q97" s="27" t="n"/>
       <c r="R97" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -10260,10 +10241,10 @@
           <t>ADTHPL-206</t>
         </is>
       </c>
-      <c r="V97" s="32" t="n">
+      <c r="V97" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W97" s="32" t="n">
+      <c r="W97" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X97" s="8" t="n"/>
@@ -10336,8 +10317,8 @@
         <v>88</v>
       </c>
       <c r="O98" s="8" t="n"/>
-      <c r="P98" s="31" t="n"/>
-      <c r="Q98" s="31" t="n"/>
+      <c r="P98" s="27" t="n"/>
+      <c r="Q98" s="27" t="n"/>
       <c r="R98" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -10358,10 +10339,10 @@
           <t>ADTHPL-207</t>
         </is>
       </c>
-      <c r="V98" s="32" t="n">
+      <c r="V98" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W98" s="32" t="n">
+      <c r="W98" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X98" s="8" t="n"/>
@@ -10434,8 +10415,8 @@
         <v>88</v>
       </c>
       <c r="O99" s="8" t="n"/>
-      <c r="P99" s="31" t="n"/>
-      <c r="Q99" s="31" t="n"/>
+      <c r="P99" s="27" t="n"/>
+      <c r="Q99" s="27" t="n"/>
       <c r="R99" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -10456,10 +10437,10 @@
           <t>ADTHPL-198</t>
         </is>
       </c>
-      <c r="V99" s="32" t="n">
+      <c r="V99" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W99" s="32" t="n">
+      <c r="W99" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X99" s="8" t="n"/>
@@ -10532,8 +10513,8 @@
         <v>88</v>
       </c>
       <c r="O100" s="8" t="n"/>
-      <c r="P100" s="31" t="n"/>
-      <c r="Q100" s="31" t="n"/>
+      <c r="P100" s="27" t="n"/>
+      <c r="Q100" s="27" t="n"/>
       <c r="R100" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -10554,10 +10535,10 @@
           <t>ADTHPL-199</t>
         </is>
       </c>
-      <c r="V100" s="32" t="n">
+      <c r="V100" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W100" s="32" t="n">
+      <c r="W100" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X100" s="8" t="n"/>
@@ -10632,12 +10613,12 @@
       <c r="O101" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P101" s="31" t="inlineStr">
+      <c r="P101" s="27" t="inlineStr">
         <is>
           <t>15.10.2026/19.10.2026</t>
         </is>
       </c>
-      <c r="Q101" s="31" t="inlineStr">
+      <c r="Q101" s="27" t="inlineStr">
         <is>
           <t>16.10.2026/21.10.2026</t>
         </is>
@@ -10662,10 +10643,10 @@
           <t>ADTHPL-253</t>
         </is>
       </c>
-      <c r="V101" s="32" t="n">
+      <c r="V101" s="28" t="n">
         <v>46300</v>
       </c>
-      <c r="W101" s="32" t="n">
+      <c r="W101" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X101" s="8" t="n"/>
@@ -10740,12 +10721,12 @@
       <c r="O102" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P102" s="31" t="inlineStr">
+      <c r="P102" s="27" t="inlineStr">
         <is>
           <t>15.10.2026/19.10.2026</t>
         </is>
       </c>
-      <c r="Q102" s="31" t="inlineStr">
+      <c r="Q102" s="27" t="inlineStr">
         <is>
           <t>16.10.2026/21.10.2026</t>
         </is>
@@ -10770,10 +10751,10 @@
           <t>ADTHPL-220</t>
         </is>
       </c>
-      <c r="V102" s="32" t="n">
+      <c r="V102" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W102" s="32" t="n">
+      <c r="W102" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X102" s="8" t="n"/>
@@ -10846,8 +10827,8 @@
         <v>120</v>
       </c>
       <c r="O103" s="8" t="n"/>
-      <c r="P103" s="31" t="n"/>
-      <c r="Q103" s="31" t="n"/>
+      <c r="P103" s="27" t="n"/>
+      <c r="Q103" s="27" t="n"/>
       <c r="R103" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -10868,10 +10849,10 @@
           <t>ADTHPL-220</t>
         </is>
       </c>
-      <c r="V103" s="32" t="n">
+      <c r="V103" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W103" s="32" t="n">
+      <c r="W103" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X103" s="8" t="n"/>
@@ -10944,8 +10925,8 @@
         <v>56</v>
       </c>
       <c r="O104" s="8" t="n"/>
-      <c r="P104" s="31" t="n"/>
-      <c r="Q104" s="31" t="n"/>
+      <c r="P104" s="27" t="n"/>
+      <c r="Q104" s="27" t="n"/>
       <c r="R104" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -10966,10 +10947,10 @@
           <t>ADTHPL-218</t>
         </is>
       </c>
-      <c r="V104" s="32" t="n">
+      <c r="V104" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W104" s="32" t="n">
+      <c r="W104" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X104" s="8" t="n"/>
@@ -11042,8 +11023,8 @@
         <v>120</v>
       </c>
       <c r="O105" s="8" t="n"/>
-      <c r="P105" s="31" t="n"/>
-      <c r="Q105" s="31" t="n"/>
+      <c r="P105" s="27" t="n"/>
+      <c r="Q105" s="27" t="n"/>
       <c r="R105" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -11064,10 +11045,10 @@
           <t>ADTHPL-179</t>
         </is>
       </c>
-      <c r="V105" s="32" t="n">
+      <c r="V105" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W105" s="32" t="n">
+      <c r="W105" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X105" s="8" t="n"/>
@@ -11140,8 +11121,8 @@
         <v>56</v>
       </c>
       <c r="O106" s="8" t="n"/>
-      <c r="P106" s="31" t="n"/>
-      <c r="Q106" s="31" t="n"/>
+      <c r="P106" s="27" t="n"/>
+      <c r="Q106" s="27" t="n"/>
       <c r="R106" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -11162,10 +11143,10 @@
           <t>ADTHPL-256</t>
         </is>
       </c>
-      <c r="V106" s="32" t="n">
+      <c r="V106" s="28" t="n">
         <v>46300</v>
       </c>
-      <c r="W106" s="32" t="n">
+      <c r="W106" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X106" s="8" t="n"/>
@@ -11240,10 +11221,10 @@
       <c r="O107" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P107" s="31" t="n">
+      <c r="P107" s="27" t="n">
         <v>46321</v>
       </c>
-      <c r="Q107" s="31" t="n">
+      <c r="Q107" s="27" t="n">
         <v>46325</v>
       </c>
       <c r="R107" s="8" t="inlineStr">
@@ -11266,10 +11247,10 @@
           <t>ADTHPL-263</t>
         </is>
       </c>
-      <c r="V107" s="32" t="n">
+      <c r="V107" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="W107" s="32" t="n">
+      <c r="W107" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X107" s="8" t="n"/>
@@ -11344,10 +11325,10 @@
       <c r="O108" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P108" s="31" t="n">
+      <c r="P108" s="27" t="n">
         <v>46321</v>
       </c>
-      <c r="Q108" s="31" t="n">
+      <c r="Q108" s="27" t="n">
         <v>46325</v>
       </c>
       <c r="R108" s="8" t="inlineStr">
@@ -11370,10 +11351,10 @@
           <t>ADTHPL-219</t>
         </is>
       </c>
-      <c r="V108" s="32" t="n">
+      <c r="V108" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W108" s="32" t="n">
+      <c r="W108" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X108" s="8" t="n"/>
@@ -11446,8 +11427,8 @@
         <v>120</v>
       </c>
       <c r="O109" s="8" t="n"/>
-      <c r="P109" s="31" t="n"/>
-      <c r="Q109" s="31" t="n"/>
+      <c r="P109" s="27" t="n"/>
+      <c r="Q109" s="27" t="n"/>
       <c r="R109" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -11468,10 +11449,10 @@
           <t>ADTHPL-268</t>
         </is>
       </c>
-      <c r="V109" s="32" t="n">
+      <c r="V109" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="W109" s="32" t="n">
+      <c r="W109" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X109" s="8" t="n"/>
@@ -11544,8 +11525,8 @@
         <v>56</v>
       </c>
       <c r="O110" s="8" t="n"/>
-      <c r="P110" s="31" t="n"/>
-      <c r="Q110" s="31" t="n"/>
+      <c r="P110" s="27" t="n"/>
+      <c r="Q110" s="27" t="n"/>
       <c r="R110" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -11566,10 +11547,10 @@
           <t>ADTHPL-217</t>
         </is>
       </c>
-      <c r="V110" s="32" t="n">
+      <c r="V110" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W110" s="32" t="n">
+      <c r="W110" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X110" s="8" t="n"/>
@@ -11644,10 +11625,10 @@
       <c r="O111" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="P111" s="31" t="n">
+      <c r="P111" s="27" t="n">
         <v>46300</v>
       </c>
-      <c r="Q111" s="31" t="n">
+      <c r="Q111" s="27" t="n">
         <v>46302</v>
       </c>
       <c r="R111" s="8" t="inlineStr">
@@ -11670,10 +11651,10 @@
           <t>ADTHPL-173</t>
         </is>
       </c>
-      <c r="V111" s="32" t="n">
+      <c r="V111" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W111" s="32" t="n">
+      <c r="W111" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X111" s="8" t="n"/>
@@ -11748,10 +11729,10 @@
       <c r="O112" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="P112" s="31" t="n">
+      <c r="P112" s="27" t="n">
         <v>46300</v>
       </c>
-      <c r="Q112" s="31" t="n">
+      <c r="Q112" s="27" t="n">
         <v>46302</v>
       </c>
       <c r="R112" s="8" t="inlineStr">
@@ -11774,10 +11755,10 @@
           <t>ADTHPL-172</t>
         </is>
       </c>
-      <c r="V112" s="32" t="n">
+      <c r="V112" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W112" s="32" t="n">
+      <c r="W112" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X112" s="8" t="n"/>
@@ -11850,8 +11831,8 @@
         <v>176</v>
       </c>
       <c r="O113" s="8" t="n"/>
-      <c r="P113" s="31" t="n"/>
-      <c r="Q113" s="31" t="n"/>
+      <c r="P113" s="27" t="n"/>
+      <c r="Q113" s="27" t="n"/>
       <c r="R113" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -11872,10 +11853,10 @@
           <t>ADTHPL-225</t>
         </is>
       </c>
-      <c r="V113" s="32" t="n">
+      <c r="V113" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W113" s="32" t="n">
+      <c r="W113" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X113" s="8" t="n"/>
@@ -11950,10 +11931,10 @@
       <c r="O114" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="P114" s="31" t="n">
+      <c r="P114" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="Q114" s="31" t="n">
+      <c r="Q114" s="27" t="n">
         <v>46301</v>
       </c>
       <c r="R114" s="8" t="inlineStr">
@@ -11976,10 +11957,10 @@
           <t>ADTHPL-254</t>
         </is>
       </c>
-      <c r="V114" s="32" t="n">
+      <c r="V114" s="28" t="n">
         <v>46302</v>
       </c>
-      <c r="W114" s="32" t="n">
+      <c r="W114" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X114" s="8" t="n"/>
@@ -12054,10 +12035,10 @@
       <c r="O115" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="P115" s="31" t="n">
+      <c r="P115" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="Q115" s="31" t="n">
+      <c r="Q115" s="27" t="n">
         <v>46301</v>
       </c>
       <c r="R115" s="8" t="inlineStr">
@@ -12080,10 +12061,10 @@
           <t>ADTHPL-259</t>
         </is>
       </c>
-      <c r="V115" s="32" t="n">
+      <c r="V115" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="W115" s="32" t="n">
+      <c r="W115" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X115" s="8" t="n"/>
@@ -12158,10 +12139,10 @@
       <c r="O116" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="P116" s="31" t="n">
+      <c r="P116" s="27" t="n">
         <v>46300</v>
       </c>
-      <c r="Q116" s="31" t="n">
+      <c r="Q116" s="27" t="n">
         <v>46313</v>
       </c>
       <c r="R116" s="8" t="inlineStr">
@@ -12184,10 +12165,10 @@
           <t>ADTHPL-174</t>
         </is>
       </c>
-      <c r="V116" s="32" t="n">
+      <c r="V116" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W116" s="32" t="n">
+      <c r="W116" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X116" s="8" t="n"/>
@@ -12262,10 +12243,10 @@
       <c r="O117" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="P117" s="31" t="n">
+      <c r="P117" s="27" t="n">
         <v>46300</v>
       </c>
-      <c r="Q117" s="31" t="n">
+      <c r="Q117" s="27" t="n">
         <v>46313</v>
       </c>
       <c r="R117" s="8" t="inlineStr">
@@ -12288,10 +12269,10 @@
           <t>ADTHPL-173</t>
         </is>
       </c>
-      <c r="V117" s="32" t="n">
+      <c r="V117" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W117" s="32" t="n">
+      <c r="W117" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X117" s="8" t="n"/>
@@ -12366,10 +12347,10 @@
       <c r="O118" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="P118" s="31" t="n">
+      <c r="P118" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="Q118" s="31" t="n">
+      <c r="Q118" s="27" t="n">
         <v>46297</v>
       </c>
       <c r="R118" s="8" t="inlineStr">
@@ -12392,10 +12373,10 @@
           <t>ADTHPL-267</t>
         </is>
       </c>
-      <c r="V118" s="32" t="n">
+      <c r="V118" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="W118" s="32" t="n">
+      <c r="W118" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X118" s="8" t="n"/>
@@ -12470,10 +12451,10 @@
       <c r="O119" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="P119" s="31" t="n">
+      <c r="P119" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="Q119" s="31" t="n">
+      <c r="Q119" s="27" t="n">
         <v>46297</v>
       </c>
       <c r="R119" s="8" t="inlineStr">
@@ -12496,10 +12477,10 @@
           <t>ADTHPL-253</t>
         </is>
       </c>
-      <c r="V119" s="32" t="n">
+      <c r="V119" s="28" t="n">
         <v>46300</v>
       </c>
-      <c r="W119" s="32" t="n">
+      <c r="W119" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X119" s="8" t="n"/>
@@ -12574,10 +12555,10 @@
       <c r="O120" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="P120" s="31" t="n">
+      <c r="P120" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="Q120" s="31" t="n">
+      <c r="Q120" s="27" t="n">
         <v>46297</v>
       </c>
       <c r="R120" s="8" t="inlineStr">
@@ -12600,10 +12581,10 @@
           <t>ADTHPL-268</t>
         </is>
       </c>
-      <c r="V120" s="32" t="n">
+      <c r="V120" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="W120" s="32" t="n">
+      <c r="W120" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X120" s="8" t="n"/>
@@ -12676,8 +12657,8 @@
         <v>176</v>
       </c>
       <c r="O121" s="8" t="n"/>
-      <c r="P121" s="31" t="n"/>
-      <c r="Q121" s="31" t="n"/>
+      <c r="P121" s="27" t="n"/>
+      <c r="Q121" s="27" t="n"/>
       <c r="R121" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -12698,10 +12679,10 @@
           <t>ADTHPL-221</t>
         </is>
       </c>
-      <c r="V121" s="32" t="n">
+      <c r="V121" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W121" s="32" t="n">
+      <c r="W121" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X121" s="8" t="n"/>
@@ -12774,8 +12755,8 @@
         <v>160</v>
       </c>
       <c r="O122" s="8" t="n"/>
-      <c r="P122" s="31" t="n"/>
-      <c r="Q122" s="31" t="n"/>
+      <c r="P122" s="27" t="n"/>
+      <c r="Q122" s="27" t="n"/>
       <c r="R122" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -12796,10 +12777,10 @@
           <t>ADTHPL-217</t>
         </is>
       </c>
-      <c r="V122" s="32" t="n">
+      <c r="V122" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W122" s="32" t="n">
+      <c r="W122" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X122" s="8" t="n"/>
@@ -12872,8 +12853,8 @@
         <v>16</v>
       </c>
       <c r="O123" s="8" t="n"/>
-      <c r="P123" s="31" t="n"/>
-      <c r="Q123" s="31" t="n"/>
+      <c r="P123" s="27" t="n"/>
+      <c r="Q123" s="27" t="n"/>
       <c r="R123" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -12894,10 +12875,10 @@
           <t>ADTHPL-150</t>
         </is>
       </c>
-      <c r="V123" s="32" t="n">
+      <c r="V123" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W123" s="32" t="n">
+      <c r="W123" s="28" t="n">
         <v>46297</v>
       </c>
       <c r="X123" s="8" t="n"/>
@@ -12970,8 +12951,8 @@
         <v>120</v>
       </c>
       <c r="O124" s="8" t="n"/>
-      <c r="P124" s="31" t="n"/>
-      <c r="Q124" s="31" t="n"/>
+      <c r="P124" s="27" t="n"/>
+      <c r="Q124" s="27" t="n"/>
       <c r="R124" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -12992,10 +12973,10 @@
           <t>ADTHPL-262</t>
         </is>
       </c>
-      <c r="V124" s="32" t="n">
+      <c r="V124" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="W124" s="32" t="n">
+      <c r="W124" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X124" s="8" t="n"/>
@@ -13068,8 +13049,8 @@
         <v>56</v>
       </c>
       <c r="O125" s="8" t="n"/>
-      <c r="P125" s="31" t="n"/>
-      <c r="Q125" s="31" t="n"/>
+      <c r="P125" s="27" t="n"/>
+      <c r="Q125" s="27" t="n"/>
       <c r="R125" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -13090,10 +13071,10 @@
           <t>ADTHPL-218</t>
         </is>
       </c>
-      <c r="V125" s="32" t="n">
+      <c r="V125" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W125" s="32" t="n">
+      <c r="W125" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X125" s="8" t="n"/>
@@ -13166,8 +13147,8 @@
         <v>120</v>
       </c>
       <c r="O126" s="8" t="n"/>
-      <c r="P126" s="31" t="n"/>
-      <c r="Q126" s="31" t="n"/>
+      <c r="P126" s="27" t="n"/>
+      <c r="Q126" s="27" t="n"/>
       <c r="R126" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -13188,10 +13169,10 @@
           <t>ADTHPL-261</t>
         </is>
       </c>
-      <c r="V126" s="32" t="n">
+      <c r="V126" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="W126" s="32" t="n">
+      <c r="W126" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X126" s="8" t="n"/>
@@ -13264,8 +13245,8 @@
         <v>56</v>
       </c>
       <c r="O127" s="8" t="n"/>
-      <c r="P127" s="31" t="n"/>
-      <c r="Q127" s="31" t="n"/>
+      <c r="P127" s="27" t="n"/>
+      <c r="Q127" s="27" t="n"/>
       <c r="R127" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -13286,10 +13267,10 @@
           <t>ADTHPL-217</t>
         </is>
       </c>
-      <c r="V127" s="32" t="n">
+      <c r="V127" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W127" s="32" t="n">
+      <c r="W127" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X127" s="8" t="n"/>
@@ -13364,10 +13345,10 @@
       <c r="O128" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="P128" s="31" t="n">
+      <c r="P128" s="27" t="n">
         <v>46307</v>
       </c>
-      <c r="Q128" s="31" t="n">
+      <c r="Q128" s="27" t="n">
         <v>46318</v>
       </c>
       <c r="R128" s="8" t="inlineStr">
@@ -13390,10 +13371,10 @@
           <t>ADTHPL-228</t>
         </is>
       </c>
-      <c r="V128" s="32" t="n">
+      <c r="V128" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W128" s="32" t="n">
+      <c r="W128" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X128" s="8" t="n"/>
@@ -13468,10 +13449,10 @@
       <c r="O129" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="P129" s="31" t="n">
+      <c r="P129" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="Q129" s="31" t="n">
+      <c r="Q129" s="27" t="n">
         <v>46297</v>
       </c>
       <c r="R129" s="8" t="inlineStr">
@@ -13494,10 +13475,10 @@
           <t>ADTHPL-260</t>
         </is>
       </c>
-      <c r="V129" s="32" t="n">
+      <c r="V129" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="W129" s="32" t="n">
+      <c r="W129" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X129" s="8" t="n"/>
@@ -13572,10 +13553,10 @@
       <c r="O130" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="P130" s="31" t="n">
+      <c r="P130" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="Q130" s="31" t="n">
+      <c r="Q130" s="27" t="n">
         <v>46297</v>
       </c>
       <c r="R130" s="8" t="inlineStr">
@@ -13598,10 +13579,10 @@
           <t>ADTHPL-253</t>
         </is>
       </c>
-      <c r="V130" s="32" t="n">
+      <c r="V130" s="28" t="n">
         <v>46300</v>
       </c>
-      <c r="W130" s="32" t="n">
+      <c r="W130" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X130" s="8" t="n"/>
@@ -13674,8 +13655,8 @@
         <v>120</v>
       </c>
       <c r="O131" s="8" t="n"/>
-      <c r="P131" s="31" t="n"/>
-      <c r="Q131" s="31" t="n"/>
+      <c r="P131" s="27" t="n"/>
+      <c r="Q131" s="27" t="n"/>
       <c r="R131" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -13696,10 +13677,10 @@
           <t>ADTHPL-153</t>
         </is>
       </c>
-      <c r="V131" s="32" t="n">
+      <c r="V131" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W131" s="32" t="n">
+      <c r="W131" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X131" s="8" t="n"/>
@@ -13772,8 +13753,8 @@
         <v>56</v>
       </c>
       <c r="O132" s="8" t="n"/>
-      <c r="P132" s="31" t="n"/>
-      <c r="Q132" s="31" t="n"/>
+      <c r="P132" s="27" t="n"/>
+      <c r="Q132" s="27" t="n"/>
       <c r="R132" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -13794,10 +13775,10 @@
           <t>ADTHPL-152</t>
         </is>
       </c>
-      <c r="V132" s="32" t="n">
+      <c r="V132" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W132" s="32" t="n">
+      <c r="W132" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X132" s="8" t="n"/>
@@ -13872,10 +13853,10 @@
       <c r="O133" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="P133" s="31" t="n">
+      <c r="P133" s="27" t="n">
         <v>46314</v>
       </c>
-      <c r="Q133" s="31" t="n">
+      <c r="Q133" s="27" t="n">
         <v>46325</v>
       </c>
       <c r="R133" s="8" t="inlineStr">
@@ -13898,10 +13879,10 @@
           <t>ADTHPL-172</t>
         </is>
       </c>
-      <c r="V133" s="32" t="n">
+      <c r="V133" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W133" s="32" t="n">
+      <c r="W133" s="28" t="n">
         <v>46311</v>
       </c>
       <c r="X133" s="8" t="n"/>
@@ -13976,10 +13957,10 @@
       <c r="O134" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="P134" s="31" t="n">
+      <c r="P134" s="27" t="n">
         <v>46314</v>
       </c>
-      <c r="Q134" s="31" t="n">
+      <c r="Q134" s="27" t="n">
         <v>46325</v>
       </c>
       <c r="R134" s="8" t="inlineStr">
@@ -14002,10 +13983,10 @@
           <t>ADTHPL-173</t>
         </is>
       </c>
-      <c r="V134" s="32" t="n">
+      <c r="V134" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W134" s="32" t="n">
+      <c r="W134" s="28" t="n">
         <v>46311</v>
       </c>
       <c r="X134" s="8" t="n"/>
@@ -14078,8 +14059,8 @@
         <v>120</v>
       </c>
       <c r="O135" s="8" t="n"/>
-      <c r="P135" s="31" t="n"/>
-      <c r="Q135" s="31" t="n"/>
+      <c r="P135" s="27" t="n"/>
+      <c r="Q135" s="27" t="n"/>
       <c r="R135" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -14100,10 +14081,10 @@
           <t>ADTHPL-155</t>
         </is>
       </c>
-      <c r="V135" s="32" t="n">
+      <c r="V135" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W135" s="32" t="n">
+      <c r="W135" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X135" s="8" t="n"/>
@@ -14176,8 +14157,8 @@
         <v>56</v>
       </c>
       <c r="O136" s="8" t="n"/>
-      <c r="P136" s="31" t="n"/>
-      <c r="Q136" s="31" t="n"/>
+      <c r="P136" s="27" t="n"/>
+      <c r="Q136" s="27" t="n"/>
       <c r="R136" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -14198,10 +14179,10 @@
           <t>ADTHPL-255</t>
         </is>
       </c>
-      <c r="V136" s="32" t="n">
+      <c r="V136" s="28" t="n">
         <v>46300</v>
       </c>
-      <c r="W136" s="32" t="n">
+      <c r="W136" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X136" s="8" t="n"/>
@@ -14274,8 +14255,8 @@
         <v>120</v>
       </c>
       <c r="O137" s="8" t="n"/>
-      <c r="P137" s="31" t="n"/>
-      <c r="Q137" s="31" t="n"/>
+      <c r="P137" s="27" t="n"/>
+      <c r="Q137" s="27" t="n"/>
       <c r="R137" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -14296,10 +14277,10 @@
           <t>ADTHPL-160</t>
         </is>
       </c>
-      <c r="V137" s="32" t="n">
+      <c r="V137" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W137" s="32" t="n">
+      <c r="W137" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X137" s="8" t="n"/>
@@ -14372,8 +14353,8 @@
         <v>56</v>
       </c>
       <c r="O138" s="8" t="n"/>
-      <c r="P138" s="31" t="n"/>
-      <c r="Q138" s="31" t="n"/>
+      <c r="P138" s="27" t="n"/>
+      <c r="Q138" s="27" t="n"/>
       <c r="R138" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -14394,10 +14375,10 @@
           <t>ADTHPL-161</t>
         </is>
       </c>
-      <c r="V138" s="32" t="n">
+      <c r="V138" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W138" s="32" t="n">
+      <c r="W138" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X138" s="8" t="n"/>
@@ -14472,10 +14453,10 @@
       <c r="O139" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P139" s="31" t="n">
+      <c r="P139" s="27" t="n">
         <v>46321</v>
       </c>
-      <c r="Q139" s="31" t="n">
+      <c r="Q139" s="27" t="n">
         <v>46325</v>
       </c>
       <c r="R139" s="8" t="inlineStr">
@@ -14498,10 +14479,10 @@
           <t>ADTHPL-157</t>
         </is>
       </c>
-      <c r="V139" s="32" t="n">
+      <c r="V139" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W139" s="32" t="n">
+      <c r="W139" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X139" s="8" t="n"/>
@@ -14576,10 +14557,10 @@
       <c r="O140" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P140" s="31" t="n">
+      <c r="P140" s="27" t="n">
         <v>46321</v>
       </c>
-      <c r="Q140" s="31" t="n">
+      <c r="Q140" s="27" t="n">
         <v>46325</v>
       </c>
       <c r="R140" s="8" t="inlineStr">
@@ -14602,10 +14583,10 @@
           <t>ADTHPL-282</t>
         </is>
       </c>
-      <c r="V140" s="32" t="n">
+      <c r="V140" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W140" s="32" t="n">
+      <c r="W140" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X140" s="8" t="n"/>
@@ -14680,10 +14661,10 @@
       <c r="O141" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P141" s="31" t="n">
+      <c r="P141" s="27" t="n">
         <v>46321</v>
       </c>
-      <c r="Q141" s="31" t="n">
+      <c r="Q141" s="27" t="n">
         <v>46325</v>
       </c>
       <c r="R141" s="8" t="inlineStr">
@@ -14706,10 +14687,10 @@
           <t>ADTHPL-234</t>
         </is>
       </c>
-      <c r="V141" s="32" t="n">
+      <c r="V141" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W141" s="32" t="n">
+      <c r="W141" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X141" s="8" t="n"/>
@@ -14782,8 +14763,8 @@
         <v>120</v>
       </c>
       <c r="O142" s="8" t="n"/>
-      <c r="P142" s="31" t="n"/>
-      <c r="Q142" s="31" t="n"/>
+      <c r="P142" s="27" t="n"/>
+      <c r="Q142" s="27" t="n"/>
       <c r="R142" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -14804,10 +14785,10 @@
           <t>ADTHPL-161</t>
         </is>
       </c>
-      <c r="V142" s="32" t="n">
+      <c r="V142" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W142" s="32" t="n">
+      <c r="W142" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X142" s="8" t="n"/>
@@ -14880,8 +14861,8 @@
         <v>56</v>
       </c>
       <c r="O143" s="8" t="n"/>
-      <c r="P143" s="31" t="n"/>
-      <c r="Q143" s="31" t="n"/>
+      <c r="P143" s="27" t="n"/>
+      <c r="Q143" s="27" t="n"/>
       <c r="R143" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -14902,10 +14883,10 @@
           <t>ADTHPL-159</t>
         </is>
       </c>
-      <c r="V143" s="32" t="n">
+      <c r="V143" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W143" s="32" t="n">
+      <c r="W143" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X143" s="8" t="n"/>
@@ -14978,8 +14959,8 @@
         <v>160</v>
       </c>
       <c r="O144" s="8" t="n"/>
-      <c r="P144" s="31" t="n"/>
-      <c r="Q144" s="31" t="n"/>
+      <c r="P144" s="27" t="n"/>
+      <c r="Q144" s="27" t="n"/>
       <c r="R144" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -15000,10 +14981,10 @@
           <t>ADTHPL-219</t>
         </is>
       </c>
-      <c r="V144" s="32" t="n">
+      <c r="V144" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W144" s="32" t="n">
+      <c r="W144" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X144" s="8" t="n"/>
@@ -15076,8 +15057,8 @@
         <v>16</v>
       </c>
       <c r="O145" s="8" t="n"/>
-      <c r="P145" s="31" t="n"/>
-      <c r="Q145" s="31" t="n"/>
+      <c r="P145" s="27" t="n"/>
+      <c r="Q145" s="27" t="n"/>
       <c r="R145" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -15098,10 +15079,10 @@
           <t>ADTHPL-150</t>
         </is>
       </c>
-      <c r="V145" s="32" t="n">
+      <c r="V145" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W145" s="32" t="n">
+      <c r="W145" s="28" t="n">
         <v>46297</v>
       </c>
       <c r="X145" s="8" t="n"/>
@@ -15176,10 +15157,10 @@
       <c r="O146" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P146" s="31" t="n">
+      <c r="P146" s="27" t="n">
         <v>46321</v>
       </c>
-      <c r="Q146" s="31" t="n">
+      <c r="Q146" s="27" t="n">
         <v>46325</v>
       </c>
       <c r="R146" s="8" t="inlineStr">
@@ -15202,10 +15183,10 @@
           <t>ADTHPL-166</t>
         </is>
       </c>
-      <c r="V146" s="32" t="n">
+      <c r="V146" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W146" s="32" t="n">
+      <c r="W146" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X146" s="8" t="n"/>
@@ -15280,10 +15261,10 @@
       <c r="O147" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P147" s="31" t="n">
+      <c r="P147" s="27" t="n">
         <v>46321</v>
       </c>
-      <c r="Q147" s="31" t="n">
+      <c r="Q147" s="27" t="n">
         <v>46325</v>
       </c>
       <c r="R147" s="8" t="inlineStr">
@@ -15306,10 +15287,10 @@
           <t>ADTHPL-202</t>
         </is>
       </c>
-      <c r="V147" s="32" t="n">
+      <c r="V147" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W147" s="32" t="n">
+      <c r="W147" s="28" t="n">
         <v>46311</v>
       </c>
       <c r="X147" s="8" t="n"/>
@@ -15382,8 +15363,8 @@
         <v>120</v>
       </c>
       <c r="O148" s="8" t="n"/>
-      <c r="P148" s="31" t="n"/>
-      <c r="Q148" s="31" t="n"/>
+      <c r="P148" s="27" t="n"/>
+      <c r="Q148" s="27" t="n"/>
       <c r="R148" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -15404,10 +15385,10 @@
           <t>ADTHPL-163</t>
         </is>
       </c>
-      <c r="V148" s="32" t="n">
+      <c r="V148" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W148" s="32" t="n">
+      <c r="W148" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X148" s="8" t="n"/>
@@ -15480,8 +15461,8 @@
         <v>56</v>
       </c>
       <c r="O149" s="8" t="n"/>
-      <c r="P149" s="31" t="n"/>
-      <c r="Q149" s="31" t="n"/>
+      <c r="P149" s="27" t="n"/>
+      <c r="Q149" s="27" t="n"/>
       <c r="R149" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -15502,10 +15483,10 @@
           <t>ADTHPL-159</t>
         </is>
       </c>
-      <c r="V149" s="32" t="n">
+      <c r="V149" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W149" s="32" t="n">
+      <c r="W149" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X149" s="8" t="n"/>
@@ -15578,8 +15559,8 @@
         <v>120</v>
       </c>
       <c r="O150" s="8" t="n"/>
-      <c r="P150" s="31" t="n"/>
-      <c r="Q150" s="31" t="n"/>
+      <c r="P150" s="27" t="n"/>
+      <c r="Q150" s="27" t="n"/>
       <c r="R150" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -15600,10 +15581,10 @@
           <t>ADTHPL-142</t>
         </is>
       </c>
-      <c r="V150" s="32" t="n">
+      <c r="V150" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W150" s="32" t="n">
+      <c r="W150" s="28" t="n">
         <v>46325</v>
       </c>
       <c r="X150" s="8" t="n"/>
@@ -15676,8 +15657,8 @@
         <v>56</v>
       </c>
       <c r="O151" s="8" t="n"/>
-      <c r="P151" s="31" t="n"/>
-      <c r="Q151" s="31" t="n"/>
+      <c r="P151" s="27" t="n"/>
+      <c r="Q151" s="27" t="n"/>
       <c r="R151" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -15698,10 +15679,10 @@
           <t>ADTHPL-168</t>
         </is>
       </c>
-      <c r="V151" s="32" t="n">
+      <c r="V151" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W151" s="32" t="n">
+      <c r="W151" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X151" s="8" t="n"/>
@@ -15774,8 +15755,8 @@
         <v>120</v>
       </c>
       <c r="O152" s="8" t="n"/>
-      <c r="P152" s="31" t="n"/>
-      <c r="Q152" s="31" t="n"/>
+      <c r="P152" s="27" t="n"/>
+      <c r="Q152" s="27" t="n"/>
       <c r="R152" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -15796,10 +15777,10 @@
           <t>ADTHPL-162</t>
         </is>
       </c>
-      <c r="V152" s="32" t="n">
+      <c r="V152" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W152" s="32" t="n">
+      <c r="W152" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X152" s="8" t="n"/>
@@ -15872,8 +15853,8 @@
         <v>56</v>
       </c>
       <c r="O153" s="8" t="n"/>
-      <c r="P153" s="31" t="n"/>
-      <c r="Q153" s="31" t="n"/>
+      <c r="P153" s="27" t="n"/>
+      <c r="Q153" s="27" t="n"/>
       <c r="R153" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -15894,10 +15875,10 @@
           <t>ADTHPL-163</t>
         </is>
       </c>
-      <c r="V153" s="32" t="n">
+      <c r="V153" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W153" s="32" t="n">
+      <c r="W153" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X153" s="8" t="n"/>
@@ -15972,10 +15953,10 @@
       <c r="O154" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P154" s="31" t="n">
+      <c r="P154" s="27" t="n">
         <v>46300</v>
       </c>
-      <c r="Q154" s="31" t="n">
+      <c r="Q154" s="27" t="n">
         <v>46304</v>
       </c>
       <c r="R154" s="8" t="inlineStr">
@@ -15998,10 +15979,10 @@
           <t>ADTHPL-218</t>
         </is>
       </c>
-      <c r="V154" s="32" t="n">
+      <c r="V154" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W154" s="32" t="n">
+      <c r="W154" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X154" s="8" t="n"/>
@@ -16076,10 +16057,10 @@
       <c r="O155" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P155" s="31" t="n">
+      <c r="P155" s="27" t="n">
         <v>46300</v>
       </c>
-      <c r="Q155" s="31" t="n">
+      <c r="Q155" s="27" t="n">
         <v>46304</v>
       </c>
       <c r="R155" s="8" t="inlineStr">
@@ -16102,10 +16083,10 @@
           <t>ADTHPL-151</t>
         </is>
       </c>
-      <c r="V155" s="32" t="n">
+      <c r="V155" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W155" s="32" t="n">
+      <c r="W155" s="28" t="n">
         <v>46297</v>
       </c>
       <c r="X155" s="8" t="n"/>
@@ -16180,10 +16161,10 @@
       <c r="O156" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P156" s="31" t="n">
+      <c r="P156" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="Q156" s="31" t="n">
+      <c r="Q156" s="27" t="n">
         <v>46302</v>
       </c>
       <c r="R156" s="8" t="inlineStr">
@@ -16206,10 +16187,10 @@
           <t>ADTHPL-196</t>
         </is>
       </c>
-      <c r="V156" s="32" t="n">
+      <c r="V156" s="28" t="n">
         <v>46303</v>
       </c>
-      <c r="W156" s="32" t="n">
+      <c r="W156" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X156" s="8" t="inlineStr">
@@ -16288,10 +16269,10 @@
       <c r="O157" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P157" s="31" t="n">
+      <c r="P157" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="Q157" s="31" t="n">
+      <c r="Q157" s="27" t="n">
         <v>46302</v>
       </c>
       <c r="R157" s="8" t="inlineStr">
@@ -16314,10 +16295,10 @@
           <t>ADTHPL-296</t>
         </is>
       </c>
-      <c r="V157" s="32" t="n">
+      <c r="V157" s="28" t="n">
         <v>46321</v>
       </c>
-      <c r="W157" s="32" t="n">
+      <c r="W157" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X157" s="8" t="inlineStr">
@@ -16394,8 +16375,8 @@
         <v>120</v>
       </c>
       <c r="O158" s="8" t="n"/>
-      <c r="P158" s="31" t="n"/>
-      <c r="Q158" s="31" t="n"/>
+      <c r="P158" s="27" t="n"/>
+      <c r="Q158" s="27" t="n"/>
       <c r="R158" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -16416,10 +16397,10 @@
           <t>ADTHPL-152</t>
         </is>
       </c>
-      <c r="V158" s="32" t="n">
+      <c r="V158" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W158" s="32" t="n">
+      <c r="W158" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X158" s="8" t="n"/>
@@ -16492,8 +16473,8 @@
         <v>56</v>
       </c>
       <c r="O159" s="8" t="n"/>
-      <c r="P159" s="31" t="n"/>
-      <c r="Q159" s="31" t="n"/>
+      <c r="P159" s="27" t="n"/>
+      <c r="Q159" s="27" t="n"/>
       <c r="R159" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -16514,10 +16495,10 @@
           <t>ADTHPL-153</t>
         </is>
       </c>
-      <c r="V159" s="32" t="n">
+      <c r="V159" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W159" s="32" t="n">
+      <c r="W159" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X159" s="8" t="n"/>
@@ -16590,8 +16571,8 @@
         <v>120</v>
       </c>
       <c r="O160" s="8" t="n"/>
-      <c r="P160" s="31" t="n"/>
-      <c r="Q160" s="31" t="n"/>
+      <c r="P160" s="27" t="n"/>
+      <c r="Q160" s="27" t="n"/>
       <c r="R160" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -16612,10 +16593,10 @@
           <t>ADTHPL-172</t>
         </is>
       </c>
-      <c r="V160" s="32" t="n">
+      <c r="V160" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W160" s="32" t="n">
+      <c r="W160" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X160" s="8" t="n"/>
@@ -16688,8 +16669,8 @@
         <v>56</v>
       </c>
       <c r="O161" s="8" t="n"/>
-      <c r="P161" s="31" t="n"/>
-      <c r="Q161" s="31" t="n"/>
+      <c r="P161" s="27" t="n"/>
+      <c r="Q161" s="27" t="n"/>
       <c r="R161" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -16710,10 +16691,10 @@
           <t>ADTHPL-173</t>
         </is>
       </c>
-      <c r="V161" s="32" t="n">
+      <c r="V161" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W161" s="32" t="n">
+      <c r="W161" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X161" s="8" t="n"/>
@@ -16788,10 +16769,10 @@
       <c r="O162" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P162" s="31" t="n">
+      <c r="P162" s="27" t="n">
         <v>46321</v>
       </c>
-      <c r="Q162" s="31" t="n">
+      <c r="Q162" s="27" t="n">
         <v>46325</v>
       </c>
       <c r="R162" s="8" t="inlineStr">
@@ -16814,10 +16795,10 @@
           <t>ADTHPL-157</t>
         </is>
       </c>
-      <c r="V162" s="32" t="n">
+      <c r="V162" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W162" s="32" t="n">
+      <c r="W162" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X162" s="8" t="n"/>
@@ -16892,10 +16873,10 @@
       <c r="O163" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P163" s="31" t="n">
+      <c r="P163" s="27" t="n">
         <v>46321</v>
       </c>
-      <c r="Q163" s="31" t="n">
+      <c r="Q163" s="27" t="n">
         <v>46325</v>
       </c>
       <c r="R163" s="8" t="inlineStr">
@@ -16918,10 +16899,10 @@
           <t>ADTHPL-154</t>
         </is>
       </c>
-      <c r="V163" s="32" t="n">
+      <c r="V163" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W163" s="32" t="n">
+      <c r="W163" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X163" s="8" t="n"/>
@@ -16996,10 +16977,10 @@
       <c r="O164" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P164" s="31" t="n">
+      <c r="P164" s="27" t="n">
         <v>46321</v>
       </c>
-      <c r="Q164" s="31" t="n">
+      <c r="Q164" s="27" t="n">
         <v>46325</v>
       </c>
       <c r="R164" s="8" t="inlineStr">
@@ -17022,10 +17003,10 @@
           <t>ADTHPL-230</t>
         </is>
       </c>
-      <c r="V164" s="32" t="n">
+      <c r="V164" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W164" s="32" t="n">
+      <c r="W164" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X164" s="8" t="n"/>
@@ -17100,12 +17081,12 @@
       <c r="O165" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="P165" s="31" t="inlineStr">
+      <c r="P165" s="27" t="inlineStr">
         <is>
           <t>01.10.2026/08.10.2026</t>
         </is>
       </c>
-      <c r="Q165" s="31" t="inlineStr">
+      <c r="Q165" s="27" t="inlineStr">
         <is>
           <t>02.10.2026/09.10.2026</t>
         </is>
@@ -17130,10 +17111,10 @@
           <t>ADTHPL-153</t>
         </is>
       </c>
-      <c r="V165" s="32" t="n">
+      <c r="V165" s="28" t="n">
         <v>46300</v>
       </c>
-      <c r="W165" s="32" t="n">
+      <c r="W165" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X165" s="8" t="n"/>
@@ -17208,12 +17189,12 @@
       <c r="O166" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="P166" s="31" t="inlineStr">
+      <c r="P166" s="27" t="inlineStr">
         <is>
           <t>01.10.2026/08.10.2026</t>
         </is>
       </c>
-      <c r="Q166" s="31" t="inlineStr">
+      <c r="Q166" s="27" t="inlineStr">
         <is>
           <t>02.10.2026/09.10.2026</t>
         </is>
@@ -17238,10 +17219,10 @@
           <t>ADTHPL-152</t>
         </is>
       </c>
-      <c r="V166" s="32" t="n">
+      <c r="V166" s="28" t="n">
         <v>46300</v>
       </c>
-      <c r="W166" s="32" t="n">
+      <c r="W166" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X166" s="8" t="n"/>
@@ -17314,8 +17295,8 @@
         <v>120</v>
       </c>
       <c r="O167" s="8" t="n"/>
-      <c r="P167" s="31" t="n"/>
-      <c r="Q167" s="31" t="n"/>
+      <c r="P167" s="27" t="n"/>
+      <c r="Q167" s="27" t="n"/>
       <c r="R167" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -17336,10 +17317,10 @@
           <t>ADTHPL-174</t>
         </is>
       </c>
-      <c r="V167" s="32" t="n">
+      <c r="V167" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W167" s="32" t="n">
+      <c r="W167" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X167" s="8" t="n"/>
@@ -17412,8 +17393,8 @@
         <v>56</v>
       </c>
       <c r="O168" s="8" t="n"/>
-      <c r="P168" s="31" t="n"/>
-      <c r="Q168" s="31" t="n"/>
+      <c r="P168" s="27" t="n"/>
+      <c r="Q168" s="27" t="n"/>
       <c r="R168" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -17434,10 +17415,10 @@
           <t>ADTHPL-173</t>
         </is>
       </c>
-      <c r="V168" s="32" t="n">
+      <c r="V168" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W168" s="32" t="n">
+      <c r="W168" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X168" s="8" t="n"/>
@@ -17510,8 +17491,8 @@
         <v>120</v>
       </c>
       <c r="O169" s="8" t="n"/>
-      <c r="P169" s="31" t="n"/>
-      <c r="Q169" s="31" t="n"/>
+      <c r="P169" s="27" t="n"/>
+      <c r="Q169" s="27" t="n"/>
       <c r="R169" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -17532,10 +17513,10 @@
           <t>ADTHPL-177</t>
         </is>
       </c>
-      <c r="V169" s="32" t="n">
+      <c r="V169" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W169" s="32" t="n">
+      <c r="W169" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X169" s="8" t="n"/>
@@ -17608,8 +17589,8 @@
         <v>56</v>
       </c>
       <c r="O170" s="8" t="n"/>
-      <c r="P170" s="31" t="n"/>
-      <c r="Q170" s="31" t="n"/>
+      <c r="P170" s="27" t="n"/>
+      <c r="Q170" s="27" t="n"/>
       <c r="R170" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -17630,10 +17611,10 @@
           <t>ADTHPL-175</t>
         </is>
       </c>
-      <c r="V170" s="32" t="n">
+      <c r="V170" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W170" s="32" t="n">
+      <c r="W170" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X170" s="8" t="n"/>
@@ -17706,8 +17687,8 @@
         <v>120</v>
       </c>
       <c r="O171" s="8" t="n"/>
-      <c r="P171" s="31" t="n"/>
-      <c r="Q171" s="31" t="n"/>
+      <c r="P171" s="27" t="n"/>
+      <c r="Q171" s="27" t="n"/>
       <c r="R171" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -17728,10 +17709,10 @@
           <t>ADTHPL-159</t>
         </is>
       </c>
-      <c r="V171" s="32" t="n">
+      <c r="V171" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W171" s="32" t="n">
+      <c r="W171" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X171" s="8" t="n"/>
@@ -17804,8 +17785,8 @@
         <v>56</v>
       </c>
       <c r="O172" s="8" t="n"/>
-      <c r="P172" s="31" t="n"/>
-      <c r="Q172" s="31" t="n"/>
+      <c r="P172" s="27" t="n"/>
+      <c r="Q172" s="27" t="n"/>
       <c r="R172" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -17826,10 +17807,10 @@
           <t>ADTHPL-161</t>
         </is>
       </c>
-      <c r="V172" s="32" t="n">
+      <c r="V172" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W172" s="32" t="n">
+      <c r="W172" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X172" s="8" t="n"/>
@@ -17902,8 +17883,8 @@
         <v>120</v>
       </c>
       <c r="O173" s="8" t="n"/>
-      <c r="P173" s="31" t="n"/>
-      <c r="Q173" s="31" t="n"/>
+      <c r="P173" s="27" t="n"/>
+      <c r="Q173" s="27" t="n"/>
       <c r="R173" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -17924,10 +17905,10 @@
           <t>ADTHPL-156</t>
         </is>
       </c>
-      <c r="V173" s="32" t="n">
+      <c r="V173" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W173" s="32" t="n">
+      <c r="W173" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X173" s="8" t="n"/>
@@ -18000,8 +17981,8 @@
         <v>56</v>
       </c>
       <c r="O174" s="8" t="n"/>
-      <c r="P174" s="31" t="n"/>
-      <c r="Q174" s="31" t="n"/>
+      <c r="P174" s="27" t="n"/>
+      <c r="Q174" s="27" t="n"/>
       <c r="R174" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -18022,10 +18003,10 @@
           <t>ADTHPL-264</t>
         </is>
       </c>
-      <c r="V174" s="32" t="n">
+      <c r="V174" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="W174" s="32" t="n">
+      <c r="W174" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X174" s="8" t="n"/>
@@ -18098,8 +18079,8 @@
         <v>120</v>
       </c>
       <c r="O175" s="8" t="n"/>
-      <c r="P175" s="31" t="n"/>
-      <c r="Q175" s="31" t="n"/>
+      <c r="P175" s="27" t="n"/>
+      <c r="Q175" s="27" t="n"/>
       <c r="R175" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -18120,10 +18101,10 @@
           <t>ADTHPL-176</t>
         </is>
       </c>
-      <c r="V175" s="32" t="n">
+      <c r="V175" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W175" s="32" t="n">
+      <c r="W175" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X175" s="8" t="n"/>
@@ -18196,8 +18177,8 @@
         <v>56</v>
       </c>
       <c r="O176" s="8" t="n"/>
-      <c r="P176" s="31" t="n"/>
-      <c r="Q176" s="31" t="n"/>
+      <c r="P176" s="27" t="n"/>
+      <c r="Q176" s="27" t="n"/>
       <c r="R176" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -18218,10 +18199,10 @@
           <t>ADTHPL-177</t>
         </is>
       </c>
-      <c r="V176" s="32" t="n">
+      <c r="V176" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W176" s="32" t="n">
+      <c r="W176" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X176" s="8" t="n"/>
@@ -18296,12 +18277,12 @@
       <c r="O177" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="P177" s="31" t="inlineStr">
+      <c r="P177" s="27" t="inlineStr">
         <is>
           <t>23.10.2026/30.10.2026</t>
         </is>
       </c>
-      <c r="Q177" s="31" t="inlineStr">
+      <c r="Q177" s="27" t="inlineStr">
         <is>
           <t>23.10.2026/30.10.2026</t>
         </is>
@@ -18326,10 +18307,10 @@
           <t>ADTHPL-160</t>
         </is>
       </c>
-      <c r="V177" s="32" t="n">
+      <c r="V177" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W177" s="32" t="n">
+      <c r="W177" s="28" t="n">
         <v>46324</v>
       </c>
       <c r="X177" s="8" t="n"/>
@@ -18404,12 +18385,12 @@
       <c r="O178" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="P178" s="31" t="inlineStr">
+      <c r="P178" s="27" t="inlineStr">
         <is>
           <t>23.10.2026/30.10.2026</t>
         </is>
       </c>
-      <c r="Q178" s="31" t="inlineStr">
+      <c r="Q178" s="27" t="inlineStr">
         <is>
           <t>23.10.2026/30.10.2026</t>
         </is>
@@ -18434,10 +18415,10 @@
           <t>ADTHPL-163</t>
         </is>
       </c>
-      <c r="V178" s="32" t="n">
+      <c r="V178" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W178" s="32" t="n">
+      <c r="W178" s="28" t="n">
         <v>46324</v>
       </c>
       <c r="X178" s="8" t="n"/>
@@ -18512,10 +18493,10 @@
       <c r="O179" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P179" s="31" t="n">
+      <c r="P179" s="27" t="n">
         <v>46307</v>
       </c>
-      <c r="Q179" s="31" t="n">
+      <c r="Q179" s="27" t="n">
         <v>46311</v>
       </c>
       <c r="R179" s="8" t="inlineStr">
@@ -18538,10 +18519,10 @@
           <t>ADTHPL-146</t>
         </is>
       </c>
-      <c r="V179" s="32" t="n">
+      <c r="V179" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W179" s="32" t="n">
+      <c r="W179" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X179" s="8" t="n"/>
@@ -18616,10 +18597,10 @@
       <c r="O180" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P180" s="31" t="n">
+      <c r="P180" s="27" t="n">
         <v>46307</v>
       </c>
-      <c r="Q180" s="31" t="n">
+      <c r="Q180" s="27" t="n">
         <v>46311</v>
       </c>
       <c r="R180" s="8" t="inlineStr">
@@ -18642,10 +18623,10 @@
           <t>ADTHPL-277</t>
         </is>
       </c>
-      <c r="V180" s="32" t="n">
+      <c r="V180" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W180" s="32" t="n">
+      <c r="W180" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X180" s="8" t="n"/>
@@ -18720,12 +18701,12 @@
       <c r="O181" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="P181" s="31" t="inlineStr">
+      <c r="P181" s="27" t="inlineStr">
         <is>
           <t>09.10.2026/12.10.2026</t>
         </is>
       </c>
-      <c r="Q181" s="31" t="inlineStr">
+      <c r="Q181" s="27" t="inlineStr">
         <is>
           <t>09.10.2026/12.10.2026</t>
         </is>
@@ -18750,10 +18731,10 @@
           <t>ADTHPL-162</t>
         </is>
       </c>
-      <c r="V181" s="32" t="n">
+      <c r="V181" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W181" s="32" t="n">
+      <c r="W181" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X181" s="8" t="n"/>
@@ -18828,12 +18809,12 @@
       <c r="O182" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="P182" s="31" t="inlineStr">
+      <c r="P182" s="27" t="inlineStr">
         <is>
           <t>09.10.2026/12.10.2026</t>
         </is>
       </c>
-      <c r="Q182" s="31" t="inlineStr">
+      <c r="Q182" s="27" t="inlineStr">
         <is>
           <t>09.10.2026/12.10.2026</t>
         </is>
@@ -18858,10 +18839,10 @@
           <t>ADTHPL-163</t>
         </is>
       </c>
-      <c r="V182" s="32" t="n">
+      <c r="V182" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W182" s="32" t="n">
+      <c r="W182" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X182" s="8" t="n"/>
@@ -18934,8 +18915,8 @@
         <v>120</v>
       </c>
       <c r="O183" s="8" t="n"/>
-      <c r="P183" s="31" t="n"/>
-      <c r="Q183" s="31" t="n"/>
+      <c r="P183" s="27" t="n"/>
+      <c r="Q183" s="27" t="n"/>
       <c r="R183" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -18956,10 +18937,10 @@
           <t>ADTHPL-156</t>
         </is>
       </c>
-      <c r="V183" s="32" t="n">
+      <c r="V183" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W183" s="32" t="n">
+      <c r="W183" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X183" s="8" t="n"/>
@@ -19032,8 +19013,8 @@
         <v>56</v>
       </c>
       <c r="O184" s="8" t="n"/>
-      <c r="P184" s="31" t="n"/>
-      <c r="Q184" s="31" t="n"/>
+      <c r="P184" s="27" t="n"/>
+      <c r="Q184" s="27" t="n"/>
       <c r="R184" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -19054,10 +19035,10 @@
           <t>ADTHPL-167</t>
         </is>
       </c>
-      <c r="V184" s="32" t="n">
+      <c r="V184" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W184" s="32" t="n">
+      <c r="W184" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X184" s="8" t="n"/>
@@ -19130,8 +19111,8 @@
         <v>120</v>
       </c>
       <c r="O185" s="8" t="n"/>
-      <c r="P185" s="31" t="n"/>
-      <c r="Q185" s="31" t="n"/>
+      <c r="P185" s="27" t="n"/>
+      <c r="Q185" s="27" t="n"/>
       <c r="R185" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -19152,10 +19133,10 @@
           <t>ADTHPL-146</t>
         </is>
       </c>
-      <c r="V185" s="32" t="n">
+      <c r="V185" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W185" s="32" t="n">
+      <c r="W185" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X185" s="8" t="n"/>
@@ -19228,8 +19209,8 @@
         <v>56</v>
       </c>
       <c r="O186" s="8" t="n"/>
-      <c r="P186" s="31" t="n"/>
-      <c r="Q186" s="31" t="n"/>
+      <c r="P186" s="27" t="n"/>
+      <c r="Q186" s="27" t="n"/>
       <c r="R186" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -19250,10 +19231,10 @@
           <t>ADTHPL-285</t>
         </is>
       </c>
-      <c r="V186" s="32" t="n">
+      <c r="V186" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W186" s="32" t="n">
+      <c r="W186" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X186" s="8" t="n"/>
@@ -19328,10 +19309,10 @@
       <c r="O187" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P187" s="31" t="n">
+      <c r="P187" s="27" t="n">
         <v>46307</v>
       </c>
-      <c r="Q187" s="31" t="n">
+      <c r="Q187" s="27" t="n">
         <v>46312</v>
       </c>
       <c r="R187" s="8" t="inlineStr">
@@ -19354,10 +19335,10 @@
           <t>ADTHPL-154</t>
         </is>
       </c>
-      <c r="V187" s="32" t="n">
+      <c r="V187" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W187" s="32" t="n">
+      <c r="W187" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X187" s="8" t="n"/>
@@ -19432,10 +19413,10 @@
       <c r="O188" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P188" s="31" t="n">
+      <c r="P188" s="27" t="n">
         <v>46307</v>
       </c>
-      <c r="Q188" s="31" t="n">
+      <c r="Q188" s="27" t="n">
         <v>46312</v>
       </c>
       <c r="R188" s="8" t="inlineStr">
@@ -19458,10 +19439,10 @@
           <t>ADTHPL-282</t>
         </is>
       </c>
-      <c r="V188" s="32" t="n">
+      <c r="V188" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W188" s="32" t="n">
+      <c r="W188" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X188" s="8" t="n"/>
@@ -19536,10 +19517,10 @@
       <c r="O189" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P189" s="31" t="n">
+      <c r="P189" s="27" t="n">
         <v>46307</v>
       </c>
-      <c r="Q189" s="31" t="n">
+      <c r="Q189" s="27" t="n">
         <v>46312</v>
       </c>
       <c r="R189" s="8" t="inlineStr">
@@ -19562,10 +19543,10 @@
           <t>ADTHPL-236</t>
         </is>
       </c>
-      <c r="V189" s="32" t="n">
+      <c r="V189" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W189" s="32" t="n">
+      <c r="W189" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X189" s="8" t="n"/>
@@ -19638,8 +19619,8 @@
         <v>37</v>
       </c>
       <c r="O190" s="8" t="n"/>
-      <c r="P190" s="31" t="n"/>
-      <c r="Q190" s="31" t="n"/>
+      <c r="P190" s="27" t="n"/>
+      <c r="Q190" s="27" t="n"/>
       <c r="R190" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -19660,10 +19641,10 @@
           <t>ADTHPL-154</t>
         </is>
       </c>
-      <c r="V190" s="32" t="n">
+      <c r="V190" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W190" s="32" t="n">
+      <c r="W190" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X190" s="8" t="n"/>
@@ -19736,8 +19717,8 @@
         <v>16</v>
       </c>
       <c r="O191" s="8" t="n"/>
-      <c r="P191" s="31" t="n"/>
-      <c r="Q191" s="31" t="n"/>
+      <c r="P191" s="27" t="n"/>
+      <c r="Q191" s="27" t="n"/>
       <c r="R191" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -19758,10 +19739,10 @@
           <t>ADTHPL-282</t>
         </is>
       </c>
-      <c r="V191" s="32" t="n">
+      <c r="V191" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W191" s="32" t="n">
+      <c r="W191" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X191" s="8" t="n"/>
@@ -19834,8 +19815,8 @@
         <v>123</v>
       </c>
       <c r="O192" s="8" t="n"/>
-      <c r="P192" s="31" t="n"/>
-      <c r="Q192" s="31" t="n"/>
+      <c r="P192" s="27" t="n"/>
+      <c r="Q192" s="27" t="n"/>
       <c r="R192" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -19856,10 +19837,10 @@
           <t>ADTHPL-245</t>
         </is>
       </c>
-      <c r="V192" s="32" t="n">
+      <c r="V192" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W192" s="32" t="n">
+      <c r="W192" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X192" s="8" t="n"/>
@@ -19932,8 +19913,8 @@
         <v>120</v>
       </c>
       <c r="O193" s="8" t="n"/>
-      <c r="P193" s="31" t="n"/>
-      <c r="Q193" s="31" t="n"/>
+      <c r="P193" s="27" t="n"/>
+      <c r="Q193" s="27" t="n"/>
       <c r="R193" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -19954,10 +19935,10 @@
           <t>ADTHPL-167</t>
         </is>
       </c>
-      <c r="V193" s="32" t="n">
+      <c r="V193" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W193" s="32" t="n">
+      <c r="W193" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X193" s="8" t="n"/>
@@ -20030,8 +20011,8 @@
         <v>56</v>
       </c>
       <c r="O194" s="8" t="n"/>
-      <c r="P194" s="31" t="n"/>
-      <c r="Q194" s="31" t="n"/>
+      <c r="P194" s="27" t="n"/>
+      <c r="Q194" s="27" t="n"/>
       <c r="R194" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -20052,10 +20033,10 @@
           <t>ADTHPL-168</t>
         </is>
       </c>
-      <c r="V194" s="32" t="n">
+      <c r="V194" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W194" s="32" t="n">
+      <c r="W194" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X194" s="8" t="n"/>
@@ -20130,10 +20111,10 @@
       <c r="O195" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P195" s="31" t="n">
+      <c r="P195" s="27" t="n">
         <v>46321</v>
       </c>
-      <c r="Q195" s="31" t="n">
+      <c r="Q195" s="27" t="n">
         <v>46325</v>
       </c>
       <c r="R195" s="8" t="inlineStr">
@@ -20156,10 +20137,10 @@
           <t>ADTHPL-142</t>
         </is>
       </c>
-      <c r="V195" s="32" t="n">
+      <c r="V195" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W195" s="32" t="n">
+      <c r="W195" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X195" s="8" t="n"/>
@@ -20234,10 +20215,10 @@
       <c r="O196" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P196" s="31" t="n">
+      <c r="P196" s="27" t="n">
         <v>46321</v>
       </c>
-      <c r="Q196" s="31" t="n">
+      <c r="Q196" s="27" t="n">
         <v>46325</v>
       </c>
       <c r="R196" s="8" t="inlineStr">
@@ -20260,10 +20241,10 @@
           <t>ADTHPL-286</t>
         </is>
       </c>
-      <c r="V196" s="32" t="n">
+      <c r="V196" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W196" s="32" t="n">
+      <c r="W196" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X196" s="8" t="n"/>
@@ -20336,8 +20317,8 @@
         <v>37</v>
       </c>
       <c r="O197" s="8" t="n"/>
-      <c r="P197" s="31" t="n"/>
-      <c r="Q197" s="31" t="n"/>
+      <c r="P197" s="27" t="n"/>
+      <c r="Q197" s="27" t="n"/>
       <c r="R197" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -20358,10 +20339,10 @@
           <t>ADTHPL-157</t>
         </is>
       </c>
-      <c r="V197" s="32" t="n">
+      <c r="V197" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W197" s="32" t="n">
+      <c r="W197" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X197" s="8" t="n"/>
@@ -20434,8 +20415,8 @@
         <v>16</v>
       </c>
       <c r="O198" s="8" t="n"/>
-      <c r="P198" s="31" t="n"/>
-      <c r="Q198" s="31" t="n"/>
+      <c r="P198" s="27" t="n"/>
+      <c r="Q198" s="27" t="n"/>
       <c r="R198" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -20456,10 +20437,10 @@
           <t>ADTHPL-282</t>
         </is>
       </c>
-      <c r="V198" s="32" t="n">
+      <c r="V198" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W198" s="32" t="n">
+      <c r="W198" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X198" s="8" t="n"/>
@@ -20532,8 +20513,8 @@
         <v>123</v>
       </c>
       <c r="O199" s="8" t="n"/>
-      <c r="P199" s="31" t="n"/>
-      <c r="Q199" s="31" t="n"/>
+      <c r="P199" s="27" t="n"/>
+      <c r="Q199" s="27" t="n"/>
       <c r="R199" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -20554,10 +20535,10 @@
           <t>ADTHPL-230</t>
         </is>
       </c>
-      <c r="V199" s="32" t="n">
+      <c r="V199" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W199" s="32" t="n">
+      <c r="W199" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X199" s="8" t="n"/>
@@ -20632,10 +20613,10 @@
       <c r="O200" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="P200" s="31" t="n">
+      <c r="P200" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="Q200" s="31" t="n">
+      <c r="Q200" s="27" t="n">
         <v>46304</v>
       </c>
       <c r="R200" s="8" t="inlineStr">
@@ -20658,10 +20639,10 @@
           <t>ADTHPL-265</t>
         </is>
       </c>
-      <c r="V200" s="32" t="n">
+      <c r="V200" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="W200" s="32" t="n">
+      <c r="W200" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X200" s="8" t="n"/>
@@ -20736,10 +20717,10 @@
       <c r="O201" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="P201" s="31" t="n">
+      <c r="P201" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="Q201" s="31" t="n">
+      <c r="Q201" s="27" t="n">
         <v>46304</v>
       </c>
       <c r="R201" s="8" t="inlineStr">
@@ -20762,10 +20743,10 @@
           <t>ADTHPL-266</t>
         </is>
       </c>
-      <c r="V201" s="32" t="n">
+      <c r="V201" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="W201" s="32" t="n">
+      <c r="W201" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X201" s="8" t="n"/>
@@ -20838,8 +20819,8 @@
         <v>120</v>
       </c>
       <c r="O202" s="8" t="n"/>
-      <c r="P202" s="31" t="n"/>
-      <c r="Q202" s="31" t="n"/>
+      <c r="P202" s="27" t="n"/>
+      <c r="Q202" s="27" t="n"/>
       <c r="R202" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -20860,10 +20841,10 @@
           <t>ADTHPL-176</t>
         </is>
       </c>
-      <c r="V202" s="32" t="n">
+      <c r="V202" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W202" s="32" t="n">
+      <c r="W202" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X202" s="8" t="n"/>
@@ -20936,8 +20917,8 @@
         <v>56</v>
       </c>
       <c r="O203" s="8" t="n"/>
-      <c r="P203" s="31" t="n"/>
-      <c r="Q203" s="31" t="n"/>
+      <c r="P203" s="27" t="n"/>
+      <c r="Q203" s="27" t="n"/>
       <c r="R203" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -20958,10 +20939,10 @@
           <t>ADTHPL-175</t>
         </is>
       </c>
-      <c r="V203" s="32" t="n">
+      <c r="V203" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W203" s="32" t="n">
+      <c r="W203" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X203" s="8" t="n"/>
@@ -21034,8 +21015,8 @@
         <v>37</v>
       </c>
       <c r="O204" s="8" t="n"/>
-      <c r="P204" s="31" t="n"/>
-      <c r="Q204" s="31" t="n"/>
+      <c r="P204" s="27" t="n"/>
+      <c r="Q204" s="27" t="n"/>
       <c r="R204" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -21056,10 +21037,10 @@
           <t>ADTHPL-170</t>
         </is>
       </c>
-      <c r="V204" s="32" t="n">
+      <c r="V204" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W204" s="32" t="n">
+      <c r="W204" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X204" s="8" t="n"/>
@@ -21132,8 +21113,8 @@
         <v>16</v>
       </c>
       <c r="O205" s="8" t="n"/>
-      <c r="P205" s="31" t="n"/>
-      <c r="Q205" s="31" t="n"/>
+      <c r="P205" s="27" t="n"/>
+      <c r="Q205" s="27" t="n"/>
       <c r="R205" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -21154,10 +21135,10 @@
           <t>ADTHPL-149</t>
         </is>
       </c>
-      <c r="V205" s="32" t="n">
+      <c r="V205" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W205" s="32" t="n">
+      <c r="W205" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X205" s="8" t="n"/>
@@ -21230,8 +21211,8 @@
         <v>123</v>
       </c>
       <c r="O206" s="8" t="n"/>
-      <c r="P206" s="31" t="n"/>
-      <c r="Q206" s="31" t="n"/>
+      <c r="P206" s="27" t="n"/>
+      <c r="Q206" s="27" t="n"/>
       <c r="R206" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -21252,10 +21233,10 @@
           <t>ADTHPL-236</t>
         </is>
       </c>
-      <c r="V206" s="32" t="n">
+      <c r="V206" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W206" s="32" t="n">
+      <c r="W206" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X206" s="8" t="n"/>
@@ -21328,8 +21309,8 @@
         <v>37</v>
       </c>
       <c r="O207" s="8" t="n"/>
-      <c r="P207" s="31" t="n"/>
-      <c r="Q207" s="31" t="n"/>
+      <c r="P207" s="27" t="n"/>
+      <c r="Q207" s="27" t="n"/>
       <c r="R207" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -21350,10 +21331,10 @@
           <t>ADTHPL-278</t>
         </is>
       </c>
-      <c r="V207" s="32" t="n">
+      <c r="V207" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W207" s="32" t="n">
+      <c r="W207" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X207" s="8" t="n"/>
@@ -21426,8 +21407,8 @@
         <v>16</v>
       </c>
       <c r="O208" s="8" t="n"/>
-      <c r="P208" s="31" t="n"/>
-      <c r="Q208" s="31" t="n"/>
+      <c r="P208" s="27" t="n"/>
+      <c r="Q208" s="27" t="n"/>
       <c r="R208" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -21448,10 +21429,10 @@
           <t>ADTHPL-282</t>
         </is>
       </c>
-      <c r="V208" s="32" t="n">
+      <c r="V208" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W208" s="32" t="n">
+      <c r="W208" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X208" s="8" t="n"/>
@@ -21524,8 +21505,8 @@
         <v>123</v>
       </c>
       <c r="O209" s="8" t="n"/>
-      <c r="P209" s="31" t="n"/>
-      <c r="Q209" s="31" t="n"/>
+      <c r="P209" s="27" t="n"/>
+      <c r="Q209" s="27" t="n"/>
       <c r="R209" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -21546,10 +21527,10 @@
           <t>ADTHPL-224</t>
         </is>
       </c>
-      <c r="V209" s="32" t="n">
+      <c r="V209" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W209" s="32" t="n">
+      <c r="W209" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X209" s="8" t="n"/>
@@ -21622,8 +21603,8 @@
         <v>120</v>
       </c>
       <c r="O210" s="8" t="n"/>
-      <c r="P210" s="31" t="n"/>
-      <c r="Q210" s="31" t="n"/>
+      <c r="P210" s="27" t="n"/>
+      <c r="Q210" s="27" t="n"/>
       <c r="R210" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -21644,10 +21625,10 @@
           <t>ADTHPL-175</t>
         </is>
       </c>
-      <c r="V210" s="32" t="n">
+      <c r="V210" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W210" s="32" t="n">
+      <c r="W210" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X210" s="8" t="n"/>
@@ -21720,8 +21701,8 @@
         <v>56</v>
       </c>
       <c r="O211" s="8" t="n"/>
-      <c r="P211" s="31" t="n"/>
-      <c r="Q211" s="31" t="n"/>
+      <c r="P211" s="27" t="n"/>
+      <c r="Q211" s="27" t="n"/>
       <c r="R211" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -21742,10 +21723,10 @@
           <t>ADTHPL-177</t>
         </is>
       </c>
-      <c r="V211" s="32" t="n">
+      <c r="V211" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W211" s="32" t="n">
+      <c r="W211" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X211" s="8" t="n"/>
@@ -21820,10 +21801,10 @@
       <c r="O212" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P212" s="31" t="n">
+      <c r="P212" s="27" t="n">
         <v>46321</v>
       </c>
-      <c r="Q212" s="31" t="n">
+      <c r="Q212" s="27" t="n">
         <v>46325</v>
       </c>
       <c r="R212" s="8" t="inlineStr">
@@ -21846,10 +21827,10 @@
           <t>ADTHPL-235</t>
         </is>
       </c>
-      <c r="V212" s="32" t="n">
+      <c r="V212" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W212" s="32" t="n">
+      <c r="W212" s="28" t="n">
         <v>46318</v>
       </c>
       <c r="X212" s="8" t="n"/>
@@ -21922,8 +21903,8 @@
         <v>37</v>
       </c>
       <c r="O213" s="8" t="n"/>
-      <c r="P213" s="31" t="n"/>
-      <c r="Q213" s="31" t="n"/>
+      <c r="P213" s="27" t="n"/>
+      <c r="Q213" s="27" t="n"/>
       <c r="R213" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -21944,10 +21925,10 @@
           <t>ADTHPL-149</t>
         </is>
       </c>
-      <c r="V213" s="32" t="n">
+      <c r="V213" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W213" s="32" t="n">
+      <c r="W213" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X213" s="8" t="n"/>
@@ -22020,8 +22001,8 @@
         <v>16</v>
       </c>
       <c r="O214" s="8" t="n"/>
-      <c r="P214" s="31" t="n"/>
-      <c r="Q214" s="31" t="n"/>
+      <c r="P214" s="27" t="n"/>
+      <c r="Q214" s="27" t="n"/>
       <c r="R214" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -22042,10 +22023,10 @@
           <t>ADTHPL-278</t>
         </is>
       </c>
-      <c r="V214" s="32" t="n">
+      <c r="V214" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W214" s="32" t="n">
+      <c r="W214" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X214" s="8" t="n"/>
@@ -22118,8 +22099,8 @@
         <v>123</v>
       </c>
       <c r="O215" s="8" t="n"/>
-      <c r="P215" s="31" t="n"/>
-      <c r="Q215" s="31" t="n"/>
+      <c r="P215" s="27" t="n"/>
+      <c r="Q215" s="27" t="n"/>
       <c r="R215" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -22140,10 +22121,10 @@
           <t>ADTHPL-224</t>
         </is>
       </c>
-      <c r="V215" s="32" t="n">
+      <c r="V215" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W215" s="32" t="n">
+      <c r="W215" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X215" s="8" t="n"/>
@@ -22216,8 +22197,8 @@
         <v>37</v>
       </c>
       <c r="O216" s="8" t="n"/>
-      <c r="P216" s="31" t="n"/>
-      <c r="Q216" s="31" t="n"/>
+      <c r="P216" s="27" t="n"/>
+      <c r="Q216" s="27" t="n"/>
       <c r="R216" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -22238,10 +22219,10 @@
           <t>ADTHPL-157</t>
         </is>
       </c>
-      <c r="V216" s="32" t="n">
+      <c r="V216" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W216" s="32" t="n">
+      <c r="W216" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X216" s="8" t="n"/>
@@ -22314,8 +22295,8 @@
         <v>16</v>
       </c>
       <c r="O217" s="8" t="n"/>
-      <c r="P217" s="31" t="n"/>
-      <c r="Q217" s="31" t="n"/>
+      <c r="P217" s="27" t="n"/>
+      <c r="Q217" s="27" t="n"/>
       <c r="R217" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -22336,10 +22317,10 @@
           <t>ADTHPL-170</t>
         </is>
       </c>
-      <c r="V217" s="32" t="n">
+      <c r="V217" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W217" s="32" t="n">
+      <c r="W217" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X217" s="8" t="n"/>
@@ -22412,8 +22393,8 @@
         <v>104</v>
       </c>
       <c r="O218" s="8" t="n"/>
-      <c r="P218" s="31" t="n"/>
-      <c r="Q218" s="31" t="n"/>
+      <c r="P218" s="27" t="n"/>
+      <c r="Q218" s="27" t="n"/>
       <c r="R218" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -22434,10 +22415,10 @@
           <t>ADTHPL-224</t>
         </is>
       </c>
-      <c r="V218" s="32" t="n">
+      <c r="V218" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W218" s="32" t="n">
+      <c r="W218" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X218" s="8" t="n"/>
@@ -22510,8 +22491,8 @@
         <v>19</v>
       </c>
       <c r="O219" s="8" t="n"/>
-      <c r="P219" s="31" t="n"/>
-      <c r="Q219" s="31" t="n"/>
+      <c r="P219" s="27" t="n"/>
+      <c r="Q219" s="27" t="n"/>
       <c r="R219" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -22532,10 +22513,10 @@
           <t>ADTHPL-238</t>
         </is>
       </c>
-      <c r="V219" s="32" t="n">
+      <c r="V219" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W219" s="32" t="n">
+      <c r="W219" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X219" s="8" t="n"/>
@@ -22610,10 +22591,10 @@
       <c r="O220" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P220" s="31" t="n">
+      <c r="P220" s="27" t="n">
         <v>46307</v>
       </c>
-      <c r="Q220" s="31" t="n">
+      <c r="Q220" s="27" t="n">
         <v>46313</v>
       </c>
       <c r="R220" s="8" t="inlineStr">
@@ -22636,10 +22617,10 @@
           <t>ADTHPL-254</t>
         </is>
       </c>
-      <c r="V220" s="32" t="n">
+      <c r="V220" s="28" t="n">
         <v>46300</v>
       </c>
-      <c r="W220" s="32" t="n">
+      <c r="W220" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X220" s="8" t="n"/>
@@ -22714,10 +22695,10 @@
       <c r="O221" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="P221" s="31" t="n">
+      <c r="P221" s="27" t="n">
         <v>46307</v>
       </c>
-      <c r="Q221" s="31" t="n">
+      <c r="Q221" s="27" t="n">
         <v>46313</v>
       </c>
       <c r="R221" s="8" t="inlineStr">
@@ -22740,10 +22721,10 @@
           <t>ADTHPL-219</t>
         </is>
       </c>
-      <c r="V221" s="32" t="n">
+      <c r="V221" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W221" s="32" t="n">
+      <c r="W221" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X221" s="8" t="n"/>
@@ -22816,8 +22797,8 @@
         <v>168</v>
       </c>
       <c r="O222" s="8" t="n"/>
-      <c r="P222" s="31" t="n"/>
-      <c r="Q222" s="31" t="n"/>
+      <c r="P222" s="27" t="n"/>
+      <c r="Q222" s="27" t="n"/>
       <c r="R222" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -22838,10 +22819,10 @@
           <t>ADTHPL-249</t>
         </is>
       </c>
-      <c r="V222" s="32" t="n">
+      <c r="V222" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W222" s="32" t="n">
+      <c r="W222" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X222" s="8" t="n"/>
@@ -22914,8 +22895,8 @@
         <v>8</v>
       </c>
       <c r="O223" s="8" t="n"/>
-      <c r="P223" s="31" t="n"/>
-      <c r="Q223" s="31" t="n"/>
+      <c r="P223" s="27" t="n"/>
+      <c r="Q223" s="27" t="n"/>
       <c r="R223" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -22936,10 +22917,10 @@
           <t>ADTHPL-251</t>
         </is>
       </c>
-      <c r="V223" s="32" t="n">
+      <c r="V223" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W223" s="32" t="n">
+      <c r="W223" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X223" s="8" t="n"/>
@@ -23008,8 +22989,8 @@
         <v>176</v>
       </c>
       <c r="O224" s="8" t="n"/>
-      <c r="P224" s="31" t="n"/>
-      <c r="Q224" s="31" t="n"/>
+      <c r="P224" s="27" t="n"/>
+      <c r="Q224" s="27" t="n"/>
       <c r="R224" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -23030,17 +23011,13 @@
           <t>ADTHPL-239</t>
         </is>
       </c>
-      <c r="V224" s="32" t="n">
+      <c r="V224" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W224" s="32" t="n">
+      <c r="W224" s="28" t="n">
         <v>46326</v>
       </c>
-      <c r="X224" s="8" t="inlineStr">
-        <is>
-          <t>нет в Jira</t>
-        </is>
-      </c>
+      <c r="X224" s="8" t="n"/>
     </row>
     <row r="225">
       <c r="A225" s="8" t="inlineStr">
@@ -23110,8 +23087,8 @@
         <v>176</v>
       </c>
       <c r="O225" s="8" t="n"/>
-      <c r="P225" s="31" t="n"/>
-      <c r="Q225" s="31" t="n"/>
+      <c r="P225" s="27" t="n"/>
+      <c r="Q225" s="27" t="n"/>
       <c r="R225" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -23132,10 +23109,10 @@
           <t>ADTHPL-235</t>
         </is>
       </c>
-      <c r="V225" s="32" t="n">
+      <c r="V225" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W225" s="32" t="n">
+      <c r="W225" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X225" s="8" t="n"/>
@@ -23208,8 +23185,8 @@
         <v>176</v>
       </c>
       <c r="O226" s="8" t="n"/>
-      <c r="P226" s="31" t="n"/>
-      <c r="Q226" s="31" t="n"/>
+      <c r="P226" s="27" t="n"/>
+      <c r="Q226" s="27" t="n"/>
       <c r="R226" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -23230,10 +23207,10 @@
           <t>ADTHPL-242</t>
         </is>
       </c>
-      <c r="V226" s="32" t="n">
+      <c r="V226" s="28" t="n">
         <v>46296</v>
       </c>
-      <c r="W226" s="32" t="n">
+      <c r="W226" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X226" s="8" t="n"/>
@@ -23308,10 +23285,10 @@
       <c r="O227" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="P227" s="31" t="n">
+      <c r="P227" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="Q227" s="31" t="n">
+      <c r="Q227" s="27" t="n">
         <v>46306</v>
       </c>
       <c r="R227" s="8" t="inlineStr">
@@ -23334,10 +23311,10 @@
           <t>ADTHPL-147</t>
         </is>
       </c>
-      <c r="V227" s="32" t="n">
+      <c r="V227" s="28" t="n">
         <v>46307</v>
       </c>
-      <c r="W227" s="32" t="n">
+      <c r="W227" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X227" s="8" t="inlineStr">
@@ -23416,10 +23393,10 @@
       <c r="O228" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="P228" s="31" t="n">
+      <c r="P228" s="27" t="n">
         <v>46296</v>
       </c>
-      <c r="Q228" s="31" t="n">
+      <c r="Q228" s="27" t="n">
         <v>46306</v>
       </c>
       <c r="R228" s="8" t="inlineStr">
@@ -23442,10 +23419,10 @@
           <t>ADTHPL-290</t>
         </is>
       </c>
-      <c r="V228" s="32" t="n">
+      <c r="V228" s="28" t="n">
         <v>46314</v>
       </c>
-      <c r="W228" s="32" t="n">
+      <c r="W228" s="28" t="n">
         <v>46326</v>
       </c>
       <c r="X228" s="8" t="inlineStr">

--- a/out/Таймшит_AdTech_октябрь_2026_заполнен.xlsx
+++ b/out/Таймшит_AdTech_октябрь_2026_заполнен.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Были в сентябре" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист1'!$A$1:$X$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист1'!$A$1:$X$229</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Были в сентябре'!$A$1:$L$37</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -735,7 +735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X228"/>
+  <dimension ref="A1:X229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="7"/>
@@ -22986,14 +22986,14 @@
         <v>1</v>
       </c>
       <c r="N224" s="23" t="n">
-        <v>176</v>
+        <v>120</v>
       </c>
       <c r="O224" s="8" t="n"/>
       <c r="P224" s="27" t="n"/>
       <c r="Q224" s="27" t="n"/>
       <c r="R224" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S224" s="8" t="inlineStr">
@@ -23003,12 +23003,12 @@
       </c>
       <c r="T224" s="8" t="inlineStr">
         <is>
-          <t>Сопровождение регулярной отчетности Эдтех: доработки и разбор обращений (4 кв. 2026)</t>
+          <t>Прогноз кликабельности для ранжирования ставок: мониторинг и логирование новой функциональности</t>
         </is>
       </c>
       <c r="U224" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-239</t>
+          <t>ADTHPL-164</t>
         </is>
       </c>
       <c r="V224" s="28" t="n">
@@ -23032,47 +23032,43 @@
       </c>
       <c r="C225" s="8" t="inlineStr">
         <is>
-          <t>CN-0981142</t>
+          <t>GK-0002680</t>
         </is>
       </c>
       <c r="D225" s="8" t="inlineStr">
         <is>
-          <t>Лошманов Александр Борисович</t>
+          <t>Гряда Игорь Леонидович</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>Инженер сопровождения</t>
+          <t>Ведущий разработчик проекта Эдтех</t>
         </is>
       </c>
       <c r="F225" s="8" t="inlineStr">
         <is>
-          <t>0f507677-229f-11f1-93e2-c4cbe1a36811</t>
+          <t>401c7277-4316-11e8-8109-5cf3fc374db0</t>
         </is>
       </c>
       <c r="G225" s="8" t="inlineStr">
         <is>
-          <t>c0029a41-22a0-11f1-93e2-c4cbe1a36811</t>
+          <t>512cec66-1cb6-11ef-ab4e-f8f21e64b171</t>
         </is>
       </c>
       <c r="H225" s="8" t="inlineStr">
         <is>
-          <t>loshmanov_ab@magnit.ru</t>
-        </is>
-      </c>
-      <c r="I225" s="8" t="inlineStr">
-        <is>
-          <t>Департамент по развитию и разработке онлайн платформ</t>
-        </is>
-      </c>
+          <t>gryada_il@magnit.ru</t>
+        </is>
+      </c>
+      <c r="I225" s="8" t="n"/>
       <c r="J225" s="8" t="inlineStr">
         <is>
-          <t>Науменко Андрей Викторович</t>
+          <t>Моисеенко Ярослав Александрович</t>
         </is>
       </c>
       <c r="K225" s="8" t="inlineStr">
         <is>
-          <t>Команда развития медиаконтента</t>
+          <t>Сектор разработки регулярной отчётности</t>
         </is>
       </c>
       <c r="L225" s="23" t="inlineStr">
@@ -23084,14 +23080,14 @@
         <v>1</v>
       </c>
       <c r="N225" s="23" t="n">
-        <v>176</v>
+        <v>56</v>
       </c>
       <c r="O225" s="8" t="n"/>
       <c r="P225" s="27" t="n"/>
       <c r="Q225" s="27" t="n"/>
       <c r="R225" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S225" s="8" t="inlineStr">
@@ -23101,12 +23097,12 @@
       </c>
       <c r="T225" s="8" t="inlineStr">
         <is>
-          <t>Сопровождение промышленной эксплуатации партнерской платформы: мониторинг, инциденты, обновления (4 кв. 2026)</t>
+          <t>Прогноз кликабельности для ранжирования ставок: разработка серверной части и API</t>
         </is>
       </c>
       <c r="U225" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-235</t>
+          <t>ADTHPL-168</t>
         </is>
       </c>
       <c r="V225" s="28" t="n">
@@ -23130,47 +23126,47 @@
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>CN-0744573</t>
+          <t>CN-0981142</t>
         </is>
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>Ардаширов Денис Тимурович</t>
+          <t>Лошманов Александр Борисович</t>
         </is>
       </c>
       <c r="E226" s="8" t="inlineStr">
         <is>
-          <t>Директор департамента</t>
+          <t>Инженер сопровождения</t>
         </is>
       </c>
       <c r="F226" s="8" t="inlineStr">
         <is>
-          <t>8b6edcd4-c45f-11ef-ab50-f8f21e64b170</t>
+          <t>0f507677-229f-11f1-93e2-c4cbe1a36811</t>
         </is>
       </c>
       <c r="G226" s="8" t="inlineStr">
         <is>
-          <t>8b6edd55-c45f-11ef-ab50-f8f21e64b170</t>
+          <t>c0029a41-22a0-11f1-93e2-c4cbe1a36811</t>
         </is>
       </c>
       <c r="H226" s="8" t="inlineStr">
         <is>
-          <t>ardashirov@magnit.ru</t>
+          <t>loshmanov_ab@magnit.ru</t>
         </is>
       </c>
       <c r="I226" s="8" t="inlineStr">
         <is>
-          <t>Департамент продуктов коммерции и механики рекламных технологий</t>
+          <t>Департамент по развитию и разработке онлайн платформ</t>
         </is>
       </c>
       <c r="J226" s="8" t="inlineStr">
         <is>
-          <t>Марлье Людмила Анатольевна</t>
+          <t>Науменко Андрей Викторович</t>
         </is>
       </c>
       <c r="K226" s="8" t="inlineStr">
         <is>
-          <t>Бизнес-формат Рекламные технологии</t>
+          <t>Команда развития медиаконтента</t>
         </is>
       </c>
       <c r="L226" s="23" t="inlineStr">
@@ -23194,17 +23190,17 @@
       </c>
       <c r="S226" s="8" t="inlineStr">
         <is>
-          <t>Менеджмент/ Административные задачи</t>
+          <t>Разработка (кодирование) ПО</t>
         </is>
       </c>
       <c r="T226" s="8" t="inlineStr">
         <is>
-          <t>Стратегическое управление департаментом и бюджетирование (4 кв. 2026)</t>
+          <t>Сопровождение промышленной эксплуатации партнерской платформы: мониторинг, инциденты, обновления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U226" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-242</t>
+          <t>ADTHPL-235</t>
         </is>
       </c>
       <c r="V226" s="28" t="n">
@@ -23218,7 +23214,7 @@
     <row r="227">
       <c r="A227" s="8" t="inlineStr">
         <is>
-          <t>Аналитика</t>
+          <t>Бизнес</t>
         </is>
       </c>
       <c r="B227" s="8" t="inlineStr">
@@ -23228,100 +23224,90 @@
       </c>
       <c r="C227" s="8" t="inlineStr">
         <is>
-          <t>CN-1090167</t>
+          <t>CN-0744573</t>
         </is>
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>Чижиков Никита Игоревич</t>
+          <t>Ардаширов Денис Тимурович</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>Специалист ML</t>
+          <t>Директор департамента</t>
         </is>
       </c>
       <c r="F227" s="8" t="inlineStr">
         <is>
-          <t>664a7fef-c2e6-11f1-86a6-3a68dd8b748f</t>
+          <t>8b6edcd4-c45f-11ef-ab50-f8f21e64b170</t>
         </is>
       </c>
       <c r="G227" s="8" t="inlineStr">
         <is>
-          <t>fd95a41a-c2e6-11f1-86a6-3a68dd8b748f</t>
+          <t>8b6edd55-c45f-11ef-ab50-f8f21e64b170</t>
         </is>
       </c>
       <c r="H227" s="8" t="inlineStr">
         <is>
-          <t>chizhikov_ni@magnit.ru</t>
+          <t>ardashirov@magnit.ru</t>
         </is>
       </c>
       <c r="I227" s="8" t="inlineStr">
         <is>
-          <t>Департамент по управлению данными и операционной аналитике цифровых платформ</t>
+          <t>Департамент продуктов коммерции и механики рекламных технологий</t>
         </is>
       </c>
       <c r="J227" s="8" t="inlineStr">
         <is>
-          <t>Соловьев Никита Александрович</t>
+          <t>Марлье Людмила Анатольевна</t>
         </is>
       </c>
       <c r="K227" s="8" t="inlineStr">
         <is>
-          <t>Команда машинного обучения в рекламных технологиях</t>
+          <t>Бизнес-формат Рекламные технологии</t>
         </is>
       </c>
       <c r="L227" s="23" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="M227" s="23" t="n">
         <v>1</v>
       </c>
       <c r="N227" s="23" t="n">
-        <v>88</v>
-      </c>
-      <c r="O227" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="P227" s="27" t="n">
+        <v>176</v>
+      </c>
+      <c r="O227" s="8" t="n"/>
+      <c r="P227" s="27" t="n"/>
+      <c r="Q227" s="27" t="n"/>
+      <c r="R227" s="8" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="S227" s="8" t="inlineStr">
+        <is>
+          <t>Менеджмент/ Административные задачи</t>
+        </is>
+      </c>
+      <c r="T227" s="8" t="inlineStr">
+        <is>
+          <t>Стратегическое управление департаментом и бюджетирование (4 кв. 2026)</t>
+        </is>
+      </c>
+      <c r="U227" s="8" t="inlineStr">
+        <is>
+          <t>ADTHPL-242</t>
+        </is>
+      </c>
+      <c r="V227" s="28" t="n">
         <v>46296</v>
-      </c>
-      <c r="Q227" s="27" t="n">
-        <v>46306</v>
-      </c>
-      <c r="R227" s="8" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="S227" s="8" t="inlineStr">
-        <is>
-          <t>Разработка (кодирование) ПО</t>
-        </is>
-      </c>
-      <c r="T227" s="8" t="inlineStr">
-        <is>
-          <t>Дашборд эффективности кампаний в реальном времени: обучение и валидация модели</t>
-        </is>
-      </c>
-      <c r="U227" s="8" t="inlineStr">
-        <is>
-          <t>ADTHPL-147</t>
-        </is>
-      </c>
-      <c r="V227" s="28" t="n">
-        <v>46307</v>
       </c>
       <c r="W227" s="28" t="n">
         <v>46326</v>
       </c>
-      <c r="X227" s="8" t="inlineStr">
-        <is>
-          <t>приступили к работе в октябре</t>
-        </is>
-      </c>
+      <c r="X227" s="8" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="8" t="inlineStr">
@@ -23388,7 +23374,7 @@
         <v>1</v>
       </c>
       <c r="N228" s="23" t="n">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="O228" s="8" t="n">
         <v>7</v>
@@ -23411,16 +23397,16 @@
       </c>
       <c r="T228" s="8" t="inlineStr">
         <is>
-          <t>Отчет sales lift по рекламной кампании: обучение и валидация модели</t>
+          <t>Дашборд эффективности кампаний в реальном времени: обучение и валидация модели</t>
         </is>
       </c>
       <c r="U228" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-290</t>
+          <t>ADTHPL-147</t>
         </is>
       </c>
       <c r="V228" s="28" t="n">
-        <v>46314</v>
+        <v>46307</v>
       </c>
       <c r="W228" s="28" t="n">
         <v>46326</v>
@@ -23431,8 +23417,116 @@
         </is>
       </c>
     </row>
+    <row r="229">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>Аналитика</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
+        <is>
+          <t>AdTech</t>
+        </is>
+      </c>
+      <c r="C229" s="8" t="inlineStr">
+        <is>
+          <t>CN-1090167</t>
+        </is>
+      </c>
+      <c r="D229" s="8" t="inlineStr">
+        <is>
+          <t>Чижиков Никита Игоревич</t>
+        </is>
+      </c>
+      <c r="E229" s="8" t="inlineStr">
+        <is>
+          <t>Специалист ML</t>
+        </is>
+      </c>
+      <c r="F229" s="8" t="inlineStr">
+        <is>
+          <t>664a7fef-c2e6-11f1-86a6-3a68dd8b748f</t>
+        </is>
+      </c>
+      <c r="G229" s="8" t="inlineStr">
+        <is>
+          <t>fd95a41a-c2e6-11f1-86a6-3a68dd8b748f</t>
+        </is>
+      </c>
+      <c r="H229" s="8" t="inlineStr">
+        <is>
+          <t>chizhikov_ni@magnit.ru</t>
+        </is>
+      </c>
+      <c r="I229" s="8" t="inlineStr">
+        <is>
+          <t>Департамент по управлению данными и операционной аналитике цифровых платформ</t>
+        </is>
+      </c>
+      <c r="J229" s="8" t="inlineStr">
+        <is>
+          <t>Соловьев Никита Александрович</t>
+        </is>
+      </c>
+      <c r="K229" s="8" t="inlineStr">
+        <is>
+          <t>Команда машинного обучения в рекламных технологиях</t>
+        </is>
+      </c>
+      <c r="L229" s="23" t="inlineStr">
+        <is>
+          <t>нет</t>
+        </is>
+      </c>
+      <c r="M229" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="N229" s="23" t="n">
+        <v>32</v>
+      </c>
+      <c r="O229" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P229" s="27" t="n">
+        <v>46296</v>
+      </c>
+      <c r="Q229" s="27" t="n">
+        <v>46306</v>
+      </c>
+      <c r="R229" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="S229" s="8" t="inlineStr">
+        <is>
+          <t>Разработка (кодирование) ПО</t>
+        </is>
+      </c>
+      <c r="T229" s="8" t="inlineStr">
+        <is>
+          <t>Отчет sales lift по рекламной кампании: обучение и валидация модели</t>
+        </is>
+      </c>
+      <c r="U229" s="8" t="inlineStr">
+        <is>
+          <t>ADTHPL-290</t>
+        </is>
+      </c>
+      <c r="V229" s="28" t="n">
+        <v>46314</v>
+      </c>
+      <c r="W229" s="28" t="n">
+        <v>46326</v>
+      </c>
+      <c r="X229" s="8" t="inlineStr">
+        <is>
+          <t>приступили к работе в октябре</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:X228"/>
+  <autoFilter ref="A1:X229"/>
   <conditionalFormatting sqref="D1:D105 D107:D1048576">
     <cfRule type="duplicateValues" priority="9" dxfId="0"/>
   </conditionalFormatting>

--- a/out/Таймшит_AdTech_октябрь_2026_заполнен.xlsx
+++ b/out/Таймшит_AdTech_октябрь_2026_заполнен.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Были в сентябре" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист1'!$A$1:$X$229</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист1'!$A$1:$X$228</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Были в сентябре'!$A$1:$L$37</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -735,7 +735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X229"/>
+  <dimension ref="A1:X228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="7"/>
@@ -2170,14 +2170,14 @@
         <v>1</v>
       </c>
       <c r="N15" s="23" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="O15" s="8" t="n"/>
       <c r="P15" s="27" t="n"/>
       <c r="Q15" s="27" t="n"/>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S15" s="8" t="inlineStr">
@@ -2187,19 +2187,19 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>Управление согласиями пользователей на обработку данных: детализация требований и приемка инкрементов</t>
+          <t>Аукцион первой цены с корректировкой ставок: оценка эффекта и подготовка бизнес-кейса</t>
         </is>
       </c>
       <c r="U15" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-280</t>
+          <t>ADTHPL-258</t>
         </is>
       </c>
       <c r="V15" s="28" t="n">
-        <v>46314</v>
+        <v>46300</v>
       </c>
       <c r="W15" s="28" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="X15" s="8" t="n"/>
     </row>
@@ -2268,14 +2268,14 @@
         <v>1</v>
       </c>
       <c r="N16" s="23" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="O16" s="8" t="n"/>
       <c r="P16" s="27" t="n"/>
       <c r="Q16" s="27" t="n"/>
       <c r="R16" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S16" s="8" t="inlineStr">
@@ -2285,19 +2285,19 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>Аукцион первой цены с корректировкой ставок: оценка эффекта и подготовка бизнес-кейса</t>
+          <t>Управление согласиями пользователей на обработку данных: детализация требований и приемка инкрементов</t>
         </is>
       </c>
       <c r="U16" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-258</t>
+          <t>ADTHPL-280</t>
         </is>
       </c>
       <c r="V16" s="28" t="n">
-        <v>46300</v>
+        <v>46314</v>
       </c>
       <c r="W16" s="28" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="X16" s="8" t="n"/>
     </row>
@@ -2464,14 +2464,14 @@
         <v>1</v>
       </c>
       <c r="N18" s="23" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="O18" s="8" t="n"/>
       <c r="P18" s="27" t="n"/>
       <c r="Q18" s="27" t="n"/>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
@@ -2481,19 +2481,19 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>Управление согласиями пользователей на обработку данных: детализация требований и приемка инкрементов</t>
+          <t>Аукцион первой цены с корректировкой ставок: оценка эффекта и подготовка бизнес-кейса</t>
         </is>
       </c>
       <c r="U18" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-280</t>
+          <t>ADTHPL-258</t>
         </is>
       </c>
       <c r="V18" s="28" t="n">
-        <v>46314</v>
+        <v>46300</v>
       </c>
       <c r="W18" s="28" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="X18" s="8" t="n"/>
     </row>
@@ -2562,14 +2562,14 @@
         <v>1</v>
       </c>
       <c r="N19" s="23" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="O19" s="8" t="n"/>
       <c r="P19" s="27" t="n"/>
       <c r="Q19" s="27" t="n"/>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S19" s="8" t="inlineStr">
@@ -2579,19 +2579,19 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>Аукцион первой цены с корректировкой ставок: оценка эффекта и подготовка бизнес-кейса</t>
+          <t>Управление согласиями пользователей на обработку данных: детализация требований и приемка инкрементов</t>
         </is>
       </c>
       <c r="U19" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-258</t>
+          <t>ADTHPL-280</t>
         </is>
       </c>
       <c r="V19" s="28" t="n">
-        <v>46300</v>
+        <v>46314</v>
       </c>
       <c r="W19" s="28" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="X19" s="8" t="n"/>
     </row>
@@ -2758,14 +2758,14 @@
         <v>1</v>
       </c>
       <c r="N21" s="23" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="O21" s="8" t="n"/>
       <c r="P21" s="27" t="n"/>
       <c r="Q21" s="27" t="n"/>
       <c r="R21" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S21" s="8" t="inlineStr">
@@ -2775,16 +2775,16 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>Управление согласиями пользователей на обработку данных: управление бэклогом эпика</t>
+          <t>Исследование рынка и конкурентных рекламных решений (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U21" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-281</t>
+          <t>ADTHPL-243</t>
         </is>
       </c>
       <c r="V21" s="28" t="n">
-        <v>46314</v>
+        <v>46296</v>
       </c>
       <c r="W21" s="28" t="n">
         <v>46326</v>
@@ -2856,14 +2856,14 @@
         <v>1</v>
       </c>
       <c r="N22" s="23" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="O22" s="8" t="n"/>
       <c r="P22" s="27" t="n"/>
       <c r="Q22" s="27" t="n"/>
       <c r="R22" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S22" s="8" t="inlineStr">
@@ -2873,16 +2873,16 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>Исследование рынка и конкурентных рекламных решений (4 кв. 2026)</t>
+          <t>Управление согласиями пользователей на обработку данных: управление бэклогом эпика</t>
         </is>
       </c>
       <c r="U22" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-243</t>
+          <t>ADTHPL-281</t>
         </is>
       </c>
       <c r="V22" s="28" t="n">
-        <v>46296</v>
+        <v>46314</v>
       </c>
       <c r="W22" s="28" t="n">
         <v>46326</v>
@@ -3052,14 +3052,14 @@
         <v>1</v>
       </c>
       <c r="N24" s="23" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="O24" s="8" t="n"/>
       <c r="P24" s="27" t="n"/>
       <c r="Q24" s="27" t="n"/>
       <c r="R24" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S24" s="8" t="inlineStr">
@@ -3069,16 +3069,16 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>Отчет sales lift по рекламной кампании: уточнение пользовательских сценариев</t>
+          <t>Исследование рынка и конкурентных рекламных решений (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-291</t>
+          <t>ADTHPL-243</t>
         </is>
       </c>
       <c r="V24" s="28" t="n">
-        <v>46314</v>
+        <v>46296</v>
       </c>
       <c r="W24" s="28" t="n">
         <v>46326</v>
@@ -3150,14 +3150,14 @@
         <v>1</v>
       </c>
       <c r="N25" s="23" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="O25" s="8" t="n"/>
       <c r="P25" s="27" t="n"/>
       <c r="Q25" s="27" t="n"/>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S25" s="8" t="inlineStr">
@@ -3167,16 +3167,16 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>Исследование рынка и конкурентных рекламных решений (4 кв. 2026)</t>
+          <t>Отчет sales lift по рекламной кампании: уточнение пользовательских сценариев</t>
         </is>
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-243</t>
+          <t>ADTHPL-291</t>
         </is>
       </c>
       <c r="V25" s="28" t="n">
-        <v>46296</v>
+        <v>46314</v>
       </c>
       <c r="W25" s="28" t="n">
         <v>46326</v>
@@ -3346,14 +3346,14 @@
         <v>1</v>
       </c>
       <c r="N27" s="23" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="O27" s="8" t="n"/>
       <c r="P27" s="27" t="n"/>
       <c r="Q27" s="27" t="n"/>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S27" s="8" t="inlineStr">
@@ -3363,16 +3363,16 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>Отчет sales lift по рекламной кампании: управление бэклогом эпика</t>
+          <t>Исследование рынка и конкурентных рекламных решений (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U27" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-292</t>
+          <t>ADTHPL-243</t>
         </is>
       </c>
       <c r="V27" s="28" t="n">
-        <v>46314</v>
+        <v>46296</v>
       </c>
       <c r="W27" s="28" t="n">
         <v>46326</v>
@@ -3444,14 +3444,14 @@
         <v>1</v>
       </c>
       <c r="N28" s="23" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="O28" s="8" t="n"/>
       <c r="P28" s="27" t="n"/>
       <c r="Q28" s="27" t="n"/>
       <c r="R28" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S28" s="8" t="inlineStr">
@@ -3461,16 +3461,16 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>Исследование рынка и конкурентных рекламных решений (4 кв. 2026)</t>
+          <t>Отчет sales lift по рекламной кампании: управление бэклогом эпика</t>
         </is>
       </c>
       <c r="U28" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-243</t>
+          <t>ADTHPL-292</t>
         </is>
       </c>
       <c r="V28" s="28" t="n">
-        <v>46296</v>
+        <v>46314</v>
       </c>
       <c r="W28" s="28" t="n">
         <v>46326</v>
@@ -3640,14 +3640,14 @@
         <v>1</v>
       </c>
       <c r="N30" s="23" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="O30" s="8" t="n"/>
       <c r="P30" s="27" t="n"/>
       <c r="Q30" s="27" t="n"/>
       <c r="R30" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S30" s="8" t="inlineStr">
@@ -3657,19 +3657,19 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>Отчет sales lift по рекламной кампании: детализация требований и приемка инкрементов</t>
+          <t>Аукцион первой цены с корректировкой ставок: исследование и формирование продуктовой гипотезы</t>
         </is>
       </c>
       <c r="U30" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-288</t>
+          <t>ADTHPL-257</t>
         </is>
       </c>
       <c r="V30" s="28" t="n">
-        <v>46314</v>
+        <v>46300</v>
       </c>
       <c r="W30" s="28" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="X30" s="8" t="n"/>
     </row>
@@ -3738,14 +3738,14 @@
         <v>1</v>
       </c>
       <c r="N31" s="23" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="O31" s="8" t="n"/>
       <c r="P31" s="27" t="n"/>
       <c r="Q31" s="27" t="n"/>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
@@ -3755,19 +3755,19 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>Аукцион первой цены с корректировкой ставок: исследование и формирование продуктовой гипотезы</t>
+          <t>Отчет sales lift по рекламной кампании: детализация требований и приемка инкрементов</t>
         </is>
       </c>
       <c r="U31" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-257</t>
+          <t>ADTHPL-288</t>
         </is>
       </c>
       <c r="V31" s="28" t="n">
-        <v>46300</v>
+        <v>46314</v>
       </c>
       <c r="W31" s="28" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="X31" s="8" t="n"/>
     </row>
@@ -3934,36 +3934,36 @@
         <v>1</v>
       </c>
       <c r="N33" s="23" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="O33" s="8" t="n"/>
       <c r="P33" s="27" t="n"/>
       <c r="Q33" s="27" t="n"/>
       <c r="R33" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S33" s="8" t="inlineStr">
         <is>
-          <t>Интеграция ПО</t>
+          <t>Анализ (системный)</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>Дедупликация событий показов и кликов: приемка функциональности и подготовка к запуску</t>
+          <t>Аукцион первой цены с корректировкой ставок: оценка эффекта и подготовка бизнес-кейса</t>
         </is>
       </c>
       <c r="U33" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-202</t>
+          <t>ADTHPL-258</t>
         </is>
       </c>
       <c r="V33" s="28" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="W33" s="28" t="n">
-        <v>46311</v>
+        <v>46325</v>
       </c>
       <c r="X33" s="8" t="n"/>
     </row>
@@ -4032,36 +4032,36 @@
         <v>1</v>
       </c>
       <c r="N34" s="23" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="O34" s="8" t="n"/>
       <c r="P34" s="27" t="n"/>
       <c r="Q34" s="27" t="n"/>
       <c r="R34" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S34" s="8" t="inlineStr">
         <is>
-          <t>Анализ (системный)</t>
+          <t>Интеграция ПО</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>Аукцион первой цены с корректировкой ставок: оценка эффекта и подготовка бизнес-кейса</t>
+          <t>Дедупликация событий показов и кликов: приемка функциональности и подготовка к запуску</t>
         </is>
       </c>
       <c r="U34" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-258</t>
+          <t>ADTHPL-202</t>
         </is>
       </c>
       <c r="V34" s="28" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="W34" s="28" t="n">
-        <v>46325</v>
+        <v>46311</v>
       </c>
       <c r="X34" s="8" t="n"/>
     </row>
@@ -4326,14 +4326,14 @@
         <v>1</v>
       </c>
       <c r="N37" s="23" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="O37" s="8" t="n"/>
       <c r="P37" s="27" t="n"/>
       <c r="Q37" s="27" t="n"/>
       <c r="R37" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S37" s="8" t="inlineStr">
@@ -4343,19 +4343,19 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>Отчет sales lift по рекламной кампании: уточнение пользовательских сценариев, итерация 2</t>
+          <t>Аукцион первой цены с корректировкой ставок: исследование и формирование продуктовой гипотезы</t>
         </is>
       </c>
       <c r="U37" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-289</t>
+          <t>ADTHPL-257</t>
         </is>
       </c>
       <c r="V37" s="28" t="n">
-        <v>46314</v>
+        <v>46300</v>
       </c>
       <c r="W37" s="28" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="X37" s="8" t="n"/>
     </row>
@@ -4424,14 +4424,14 @@
         <v>1</v>
       </c>
       <c r="N38" s="23" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="O38" s="8" t="n"/>
       <c r="P38" s="27" t="n"/>
       <c r="Q38" s="27" t="n"/>
       <c r="R38" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S38" s="8" t="inlineStr">
@@ -4441,19 +4441,19 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>Аукцион первой цены с корректировкой ставок: исследование и формирование продуктовой гипотезы</t>
+          <t>Отчет sales lift по рекламной кампании: уточнение пользовательских сценариев, итерация 2</t>
         </is>
       </c>
       <c r="U38" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-257</t>
+          <t>ADTHPL-289</t>
         </is>
       </c>
       <c r="V38" s="28" t="n">
-        <v>46300</v>
+        <v>46314</v>
       </c>
       <c r="W38" s="28" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="X38" s="8" t="n"/>
     </row>
@@ -4620,14 +4620,14 @@
         <v>1</v>
       </c>
       <c r="N40" s="23" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="O40" s="8" t="n"/>
       <c r="P40" s="27" t="n"/>
       <c r="Q40" s="27" t="n"/>
       <c r="R40" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S40" s="8" t="inlineStr">
@@ -4637,19 +4637,19 @@
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>Отчет sales lift по рекламной кампании: детализация требований и приемка инкрементов</t>
+          <t>Аукцион первой цены с корректировкой ставок: исследование и формирование продуктовой гипотезы</t>
         </is>
       </c>
       <c r="U40" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-288</t>
+          <t>ADTHPL-257</t>
         </is>
       </c>
       <c r="V40" s="28" t="n">
-        <v>46314</v>
+        <v>46300</v>
       </c>
       <c r="W40" s="28" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="X40" s="8" t="n"/>
     </row>
@@ -4718,14 +4718,14 @@
         <v>1</v>
       </c>
       <c r="N41" s="23" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="O41" s="8" t="n"/>
       <c r="P41" s="27" t="n"/>
       <c r="Q41" s="27" t="n"/>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S41" s="8" t="inlineStr">
@@ -4735,19 +4735,19 @@
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>Аукцион первой цены с корректировкой ставок: исследование и формирование продуктовой гипотезы</t>
+          <t>Отчет sales lift по рекламной кампании: детализация требований и приемка инкрементов</t>
         </is>
       </c>
       <c r="U41" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-257</t>
+          <t>ADTHPL-288</t>
         </is>
       </c>
       <c r="V41" s="28" t="n">
-        <v>46300</v>
+        <v>46314</v>
       </c>
       <c r="W41" s="28" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="X41" s="8" t="n"/>
     </row>
@@ -4914,14 +4914,14 @@
         <v>1</v>
       </c>
       <c r="N43" s="23" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="O43" s="8" t="n"/>
       <c r="P43" s="27" t="n"/>
       <c r="Q43" s="27" t="n"/>
       <c r="R43" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S43" s="8" t="inlineStr">
@@ -4931,19 +4931,19 @@
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>Отчет sales lift по рекламной кампании: уточнение пользовательских сценариев, итерация 2</t>
+          <t>Аукцион первой цены с корректировкой ставок: исследование и формирование продуктовой гипотезы</t>
         </is>
       </c>
       <c r="U43" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-289</t>
+          <t>ADTHPL-257</t>
         </is>
       </c>
       <c r="V43" s="28" t="n">
-        <v>46314</v>
+        <v>46300</v>
       </c>
       <c r="W43" s="28" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="X43" s="8" t="n"/>
     </row>
@@ -5012,14 +5012,14 @@
         <v>1</v>
       </c>
       <c r="N44" s="23" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="O44" s="8" t="n"/>
       <c r="P44" s="27" t="n"/>
       <c r="Q44" s="27" t="n"/>
       <c r="R44" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S44" s="8" t="inlineStr">
@@ -5029,19 +5029,19 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>Аукцион первой цены с корректировкой ставок: исследование и формирование продуктовой гипотезы</t>
+          <t>Отчет sales lift по рекламной кампании: уточнение пользовательских сценариев, итерация 2</t>
         </is>
       </c>
       <c r="U44" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-257</t>
+          <t>ADTHPL-289</t>
         </is>
       </c>
       <c r="V44" s="28" t="n">
-        <v>46300</v>
+        <v>46314</v>
       </c>
       <c r="W44" s="28" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="X44" s="8" t="n"/>
     </row>
@@ -8734,29 +8734,29 @@
         <v>1</v>
       </c>
       <c r="N82" s="23" t="n">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="O82" s="8" t="n"/>
       <c r="P82" s="27" t="n"/>
       <c r="Q82" s="27" t="n"/>
       <c r="R82" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S82" s="8" t="inlineStr">
         <is>
-          <t>Разработка (кодирование) ПО</t>
+          <t>Менеджмент/ Административные задачи</t>
         </is>
       </c>
       <c r="T82" s="8" t="inlineStr">
         <is>
-          <t>Дашборд эффективности кампаний в реальном времени: техническое руководство разработкой и код-ревью</t>
+          <t>Административное управление командой аналитики: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U82" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-149</t>
+          <t>ADTHPL-234</t>
         </is>
       </c>
       <c r="V82" s="28" t="n">
@@ -8832,7 +8832,7 @@
         <v>1</v>
       </c>
       <c r="N83" s="23" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="O83" s="8" t="n"/>
       <c r="P83" s="27" t="n"/>
@@ -8849,16 +8849,16 @@
       </c>
       <c r="T83" s="8" t="inlineStr">
         <is>
-          <t>Интеграция с внешними SSP по OpenRTB 2.6: техническое руководство разработкой и код-ревью</t>
+          <t>Дашборд эффективности кампаний в реальном времени: техническое руководство разработкой и код-ревью</t>
         </is>
       </c>
       <c r="U83" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-278</t>
+          <t>ADTHPL-149</t>
         </is>
       </c>
       <c r="V83" s="28" t="n">
-        <v>46314</v>
+        <v>46296</v>
       </c>
       <c r="W83" s="28" t="n">
         <v>46326</v>
@@ -8930,33 +8930,33 @@
         <v>1</v>
       </c>
       <c r="N84" s="23" t="n">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="O84" s="8" t="n"/>
       <c r="P84" s="27" t="n"/>
       <c r="Q84" s="27" t="n"/>
       <c r="R84" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S84" s="8" t="inlineStr">
         <is>
-          <t>Менеджмент/ Административные задачи</t>
+          <t>Разработка (кодирование) ПО</t>
         </is>
       </c>
       <c r="T84" s="8" t="inlineStr">
         <is>
-          <t>Административное управление командой аналитики: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Интеграция с внешними SSP по OpenRTB 2.6: техническое руководство разработкой и код-ревью</t>
         </is>
       </c>
       <c r="U84" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-234</t>
+          <t>ADTHPL-278</t>
         </is>
       </c>
       <c r="V84" s="28" t="n">
-        <v>46296</v>
+        <v>46314</v>
       </c>
       <c r="W84" s="28" t="n">
         <v>46326</v>
@@ -9028,29 +9028,29 @@
         <v>1</v>
       </c>
       <c r="N85" s="23" t="n">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="O85" s="8" t="n"/>
       <c r="P85" s="27" t="n"/>
       <c r="Q85" s="27" t="n"/>
       <c r="R85" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S85" s="8" t="inlineStr">
         <is>
-          <t>Разработка (кодирование) ПО</t>
+          <t>Менеджмент/ Административные задачи</t>
         </is>
       </c>
       <c r="T85" s="8" t="inlineStr">
         <is>
-          <t>Автоматическая регистрация креативов и получение erid: техническое руководство разработкой и код-ревью</t>
+          <t>Административное управление командой сбора событий: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U85" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-154</t>
+          <t>ADTHPL-227</t>
         </is>
       </c>
       <c r="V85" s="28" t="n">
@@ -9126,7 +9126,7 @@
         <v>1</v>
       </c>
       <c r="N86" s="23" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="O86" s="8" t="n"/>
       <c r="P86" s="27" t="n"/>
@@ -9143,16 +9143,16 @@
       </c>
       <c r="T86" s="8" t="inlineStr">
         <is>
-          <t>Управление согласиями пользователей на обработку данных: техническое руководство разработкой и код-ревью</t>
+          <t>Автоматическая регистрация креативов и получение erid: техническое руководство разработкой и код-ревью</t>
         </is>
       </c>
       <c r="U86" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-282</t>
+          <t>ADTHPL-154</t>
         </is>
       </c>
       <c r="V86" s="28" t="n">
-        <v>46314</v>
+        <v>46296</v>
       </c>
       <c r="W86" s="28" t="n">
         <v>46326</v>
@@ -9224,33 +9224,33 @@
         <v>1</v>
       </c>
       <c r="N87" s="23" t="n">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="O87" s="8" t="n"/>
       <c r="P87" s="27" t="n"/>
       <c r="Q87" s="27" t="n"/>
       <c r="R87" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S87" s="8" t="inlineStr">
         <is>
-          <t>Менеджмент/ Административные задачи</t>
+          <t>Разработка (кодирование) ПО</t>
         </is>
       </c>
       <c r="T87" s="8" t="inlineStr">
         <is>
-          <t>Административное управление командой сбора событий: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Управление согласиями пользователей на обработку данных: техническое руководство разработкой и код-ревью</t>
         </is>
       </c>
       <c r="U87" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-227</t>
+          <t>ADTHPL-282</t>
         </is>
       </c>
       <c r="V87" s="28" t="n">
-        <v>46296</v>
+        <v>46314</v>
       </c>
       <c r="W87" s="28" t="n">
         <v>46326</v>
@@ -9322,29 +9322,29 @@
         <v>1</v>
       </c>
       <c r="N88" s="23" t="n">
-        <v>37</v>
+        <v>123</v>
       </c>
       <c r="O88" s="8" t="n"/>
       <c r="P88" s="27" t="n"/>
       <c r="Q88" s="27" t="n"/>
       <c r="R88" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S88" s="8" t="inlineStr">
         <is>
-          <t>Разработка (кодирование) ПО</t>
+          <t>Менеджмент/ Административные задачи</t>
         </is>
       </c>
       <c r="T88" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: техническое руководство разработкой и код-ревью</t>
+          <t>Административное управление командой сбора событий: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U88" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-170</t>
+          <t>ADTHPL-227</t>
         </is>
       </c>
       <c r="V88" s="28" t="n">
@@ -9420,7 +9420,7 @@
         <v>1</v>
       </c>
       <c r="N89" s="23" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="O89" s="8" t="n"/>
       <c r="P89" s="27" t="n"/>
@@ -9437,16 +9437,16 @@
       </c>
       <c r="T89" s="8" t="inlineStr">
         <is>
-          <t>Интеграция с внешними SSP по OpenRTB 2.6: техническое руководство разработкой и код-ревью</t>
+          <t>Прогноз кликабельности для ранжирования ставок: техническое руководство разработкой и код-ревью</t>
         </is>
       </c>
       <c r="U89" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-278</t>
+          <t>ADTHPL-170</t>
         </is>
       </c>
       <c r="V89" s="28" t="n">
-        <v>46314</v>
+        <v>46296</v>
       </c>
       <c r="W89" s="28" t="n">
         <v>46326</v>
@@ -9518,33 +9518,33 @@
         <v>1</v>
       </c>
       <c r="N90" s="23" t="n">
-        <v>123</v>
+        <v>16</v>
       </c>
       <c r="O90" s="8" t="n"/>
       <c r="P90" s="27" t="n"/>
       <c r="Q90" s="27" t="n"/>
       <c r="R90" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S90" s="8" t="inlineStr">
         <is>
-          <t>Менеджмент/ Административные задачи</t>
+          <t>Разработка (кодирование) ПО</t>
         </is>
       </c>
       <c r="T90" s="8" t="inlineStr">
         <is>
-          <t>Административное управление командой сбора событий: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Интеграция с внешними SSP по OpenRTB 2.6: техническое руководство разработкой и код-ревью</t>
         </is>
       </c>
       <c r="U90" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-227</t>
+          <t>ADTHPL-278</t>
         </is>
       </c>
       <c r="V90" s="28" t="n">
-        <v>46296</v>
+        <v>46314</v>
       </c>
       <c r="W90" s="28" t="n">
         <v>46326</v>
@@ -12342,7 +12342,7 @@
         <v>1</v>
       </c>
       <c r="N118" s="23" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="O118" s="8" t="n">
         <v>2</v>
@@ -12498,32 +12498,32 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>CN-0879250</t>
+          <t>CN-1068030</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Гомзяков Денис Александрович</t>
+          <t>Вылегжанин Андрей Юрьевич</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>Главный специалист по тестированию</t>
+          <t>Ведущий инженер сопровождения</t>
         </is>
       </c>
       <c r="F120" s="8" t="inlineStr">
         <is>
-          <t>97212301-84d0-11f0-86a4-3a68dd8b748f</t>
+          <t>f8641859-a6d8-11f1-86a5-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G120" s="8" t="inlineStr">
         <is>
-          <t>97212426-84d0-11f0-86a4-3a68dd8b748f</t>
+          <t>3dadcaa1-a6d9-11f1-86a5-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H120" s="8" t="inlineStr">
         <is>
-          <t>gomzyakov_da@magnit.ru</t>
+          <t>vylegzhanin_ay@magnit.ru</t>
         </is>
       </c>
       <c r="I120" s="8" t="inlineStr">
@@ -12550,39 +12550,33 @@
         <v>1</v>
       </c>
       <c r="N120" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="O120" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P120" s="27" t="n">
+        <v>176</v>
+      </c>
+      <c r="O120" s="8" t="n"/>
+      <c r="P120" s="27" t="n"/>
+      <c r="Q120" s="27" t="n"/>
+      <c r="R120" s="8" t="inlineStr">
+        <is>
+          <t>OPEX</t>
+        </is>
+      </c>
+      <c r="S120" s="8" t="inlineStr">
+        <is>
+          <t>Разработка (кодирование) ПО</t>
+        </is>
+      </c>
+      <c r="T120" s="8" t="inlineStr">
+        <is>
+          <t>Сопровождение промышленной эксплуатации показа рекламы: мониторинг, инциденты, обновления (4 кв. 2026)</t>
+        </is>
+      </c>
+      <c r="U120" s="8" t="inlineStr">
+        <is>
+          <t>ADTHPL-221</t>
+        </is>
+      </c>
+      <c r="V120" s="28" t="n">
         <v>46296</v>
-      </c>
-      <c r="Q120" s="27" t="n">
-        <v>46297</v>
-      </c>
-      <c r="R120" s="8" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="S120" s="8" t="inlineStr">
-        <is>
-          <t>Тестирование ПО</t>
-        </is>
-      </c>
-      <c r="T120" s="8" t="inlineStr">
-        <is>
-          <t>Мастер создания кампании в рекламном кабинете: тестирование безопасности</t>
-        </is>
-      </c>
-      <c r="U120" s="8" t="inlineStr">
-        <is>
-          <t>ADTHPL-268</t>
-        </is>
-      </c>
-      <c r="V120" s="28" t="n">
-        <v>46307</v>
       </c>
       <c r="W120" s="28" t="n">
         <v>46326</v>
@@ -12602,32 +12596,32 @@
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>CN-1068030</t>
+          <t>CN-0902281</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>Вылегжанин Андрей Юрьевич</t>
+          <t>Козлова Юлия Александровна</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>Ведущий инженер сопровождения</t>
+          <t>Ведущий специалист по тестированию</t>
         </is>
       </c>
       <c r="F121" s="8" t="inlineStr">
         <is>
-          <t>f8641859-a6d8-11f1-86a5-3a68dd8b748f</t>
+          <t>111dd685-a386-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G121" s="8" t="inlineStr">
         <is>
-          <t>3dadcaa1-a6d9-11f1-86a5-3a68dd8b748f</t>
+          <t>111dd74d-a386-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H121" s="8" t="inlineStr">
         <is>
-          <t>vylegzhanin_ay@magnit.ru</t>
+          <t>kozlova_ya3@magnit.ru</t>
         </is>
       </c>
       <c r="I121" s="8" t="inlineStr">
@@ -12637,12 +12631,12 @@
       </c>
       <c r="J121" s="8" t="inlineStr">
         <is>
-          <t>Карпов Дмитрий Владимирович</t>
+          <t>Волков Игорь Игоревич</t>
         </is>
       </c>
       <c r="K121" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки инструментов повышения эффективности монетизации</t>
+          <t>Отдел разработки партнерской платформы</t>
         </is>
       </c>
       <c r="L121" s="23" t="inlineStr">
@@ -12654,29 +12648,29 @@
         <v>1</v>
       </c>
       <c r="N121" s="23" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="O121" s="8" t="n"/>
       <c r="P121" s="27" t="n"/>
       <c r="Q121" s="27" t="n"/>
       <c r="R121" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S121" s="8" t="inlineStr">
         <is>
-          <t>Разработка (кодирование) ПО</t>
+          <t>Тестирование ПО</t>
         </is>
       </c>
       <c r="T121" s="8" t="inlineStr">
         <is>
-          <t>Сопровождение промышленной эксплуатации показа рекламы: мониторинг, инциденты, обновления (4 кв. 2026)</t>
+          <t>Кабинет партнера: ссылки, промокоды, статистика: функциональное и интеграционное тестирование</t>
         </is>
       </c>
       <c r="U121" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-221</t>
+          <t>ADTHPL-217</t>
         </is>
       </c>
       <c r="V121" s="28" t="n">
@@ -12752,7 +12746,7 @@
         <v>1</v>
       </c>
       <c r="N122" s="23" t="n">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="O122" s="8" t="n"/>
       <c r="P122" s="27" t="n"/>
@@ -12769,19 +12763,19 @@
       </c>
       <c r="T122" s="8" t="inlineStr">
         <is>
-          <t>Кабинет партнера: ссылки, промокоды, статистика: функциональное и интеграционное тестирование</t>
+          <t>Доработка end-to-end тестов сторис в рекламном SDK для Android</t>
         </is>
       </c>
       <c r="U122" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-217</t>
+          <t>ADTHPL-150</t>
         </is>
       </c>
       <c r="V122" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W122" s="28" t="n">
-        <v>46326</v>
+        <v>46297</v>
       </c>
       <c r="X122" s="8" t="n"/>
     </row>
@@ -12798,32 +12792,32 @@
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>CN-0902281</t>
+          <t>CN-0863005</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>Козлова Юлия Александровна</t>
+          <t>Абитов Амин Алиевич</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>Ведущий специалист по тестированию</t>
+          <t>Главный специалист по тестированию</t>
         </is>
       </c>
       <c r="F123" s="8" t="inlineStr">
         <is>
-          <t>111dd685-a386-11f0-86a4-3a68dd8b748f</t>
+          <t>bddd7ca3-6ea3-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G123" s="8" t="inlineStr">
         <is>
-          <t>111dd74d-a386-11f0-86a4-3a68dd8b748f</t>
+          <t>bddd7e9c-6ea3-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H123" s="8" t="inlineStr">
         <is>
-          <t>kozlova_ya3@magnit.ru</t>
+          <t>abitov_a_a@magnit.ru</t>
         </is>
       </c>
       <c r="I123" s="8" t="inlineStr">
@@ -12833,12 +12827,12 @@
       </c>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>Волков Игорь Игоревич</t>
+          <t>Алтухов Руслан Дмитриевич</t>
         </is>
       </c>
       <c r="K123" s="8" t="inlineStr">
         <is>
-          <t>Отдел разработки партнерской платформы</t>
+          <t>Команда разработки продуктов закрепления и буста</t>
         </is>
       </c>
       <c r="L123" s="23" t="inlineStr">
@@ -12850,7 +12844,7 @@
         <v>1</v>
       </c>
       <c r="N123" s="23" t="n">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="O123" s="8" t="n"/>
       <c r="P123" s="27" t="n"/>
@@ -12867,19 +12861,19 @@
       </c>
       <c r="T123" s="8" t="inlineStr">
         <is>
-          <t>Доработка end-to-end тестов сторис в рекламном SDK для Android</t>
+          <t>Прогноз кликабельности для ранжирования ставок: тестирование отказоустойчивости</t>
         </is>
       </c>
       <c r="U123" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-150</t>
+          <t>ADTHPL-262</t>
         </is>
       </c>
       <c r="V123" s="28" t="n">
-        <v>46296</v>
+        <v>46307</v>
       </c>
       <c r="W123" s="28" t="n">
-        <v>46297</v>
+        <v>46326</v>
       </c>
       <c r="X123" s="8" t="n"/>
     </row>
@@ -12948,7 +12942,7 @@
         <v>1</v>
       </c>
       <c r="N124" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O124" s="8" t="n"/>
       <c r="P124" s="27" t="n"/>
@@ -12965,16 +12959,16 @@
       </c>
       <c r="T124" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: тестирование отказоустойчивости</t>
+          <t>Кабинет партнера: ссылки, промокоды, статистика: нагрузочное тестирование</t>
         </is>
       </c>
       <c r="U124" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-262</t>
+          <t>ADTHPL-218</t>
         </is>
       </c>
       <c r="V124" s="28" t="n">
-        <v>46307</v>
+        <v>46296</v>
       </c>
       <c r="W124" s="28" t="n">
         <v>46326</v>
@@ -12994,32 +12988,32 @@
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>CN-0863005</t>
+          <t>CN-0900292</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>Абитов Амин Алиевич</t>
+          <t>Наумов Михаил Юрьевич</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>Главный специалист по тестированию</t>
+          <t>Ведущий специалист по тестированию</t>
         </is>
       </c>
       <c r="F125" s="8" t="inlineStr">
         <is>
-          <t>bddd7ca3-6ea3-11f0-86a3-3a68dd8b748f</t>
+          <t>52262c9c-a057-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G125" s="8" t="inlineStr">
         <is>
-          <t>bddd7e9c-6ea3-11f0-86a3-3a68dd8b748f</t>
+          <t>5826b7b8-a057-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H125" s="8" t="inlineStr">
         <is>
-          <t>abitov_a_a@magnit.ru</t>
+          <t>naumov_my@magnit.ru</t>
         </is>
       </c>
       <c r="I125" s="8" t="inlineStr">
@@ -13029,12 +13023,12 @@
       </c>
       <c r="J125" s="8" t="inlineStr">
         <is>
-          <t>Алтухов Руслан Дмитриевич</t>
+          <t>Карпов Дмитрий Владимирович</t>
         </is>
       </c>
       <c r="K125" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки продуктов закрепления и буста</t>
+          <t>Команда разработки инструментов повышения эффективности монетизации</t>
         </is>
       </c>
       <c r="L125" s="23" t="inlineStr">
@@ -13046,7 +13040,7 @@
         <v>1</v>
       </c>
       <c r="N125" s="23" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="O125" s="8" t="n"/>
       <c r="P125" s="27" t="n"/>
@@ -13063,16 +13057,16 @@
       </c>
       <c r="T125" s="8" t="inlineStr">
         <is>
-          <t>Кабинет партнера: ссылки, промокоды, статистика: нагрузочное тестирование</t>
+          <t>Прогноз кликабельности для ранжирования ставок: автоматизация регрессионных тестов</t>
         </is>
       </c>
       <c r="U125" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-218</t>
+          <t>ADTHPL-261</t>
         </is>
       </c>
       <c r="V125" s="28" t="n">
-        <v>46296</v>
+        <v>46307</v>
       </c>
       <c r="W125" s="28" t="n">
         <v>46326</v>
@@ -13144,7 +13138,7 @@
         <v>1</v>
       </c>
       <c r="N126" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O126" s="8" t="n"/>
       <c r="P126" s="27" t="n"/>
@@ -13161,16 +13155,16 @@
       </c>
       <c r="T126" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: автоматизация регрессионных тестов</t>
+          <t>Кабинет партнера: ссылки, промокоды, статистика: функциональное и интеграционное тестирование</t>
         </is>
       </c>
       <c r="U126" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-261</t>
+          <t>ADTHPL-217</t>
         </is>
       </c>
       <c r="V126" s="28" t="n">
-        <v>46307</v>
+        <v>46296</v>
       </c>
       <c r="W126" s="28" t="n">
         <v>46326</v>
@@ -13180,7 +13174,7 @@
     <row r="127">
       <c r="A127" s="8" t="inlineStr">
         <is>
-          <t>ИТ</t>
+          <t>Бизнес</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
@@ -13190,32 +13184,32 @@
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>CN-0900292</t>
+          <t>CN-0765499</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>Наумов Михаил Юрьевич</t>
+          <t>Дырда Ярослав Евгеньевич</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>Ведущий специалист по тестированию</t>
+          <t>Ведущий инженер сопровождения</t>
         </is>
       </c>
       <c r="F127" s="8" t="inlineStr">
         <is>
-          <t>52262c9c-a057-11f0-86a4-3a68dd8b748f</t>
+          <t>6db71f8c-e788-11ef-ab45-e4434b7b9424</t>
         </is>
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>5826b7b8-a057-11f0-86a4-3a68dd8b748f</t>
+          <t>6db7208b-e788-11ef-ab45-e4434b7b9424</t>
         </is>
       </c>
       <c r="H127" s="8" t="inlineStr">
         <is>
-          <t>naumov_my@magnit.ru</t>
+          <t>dyrda_ye@magnit.ru</t>
         </is>
       </c>
       <c r="I127" s="8" t="inlineStr">
@@ -13225,12 +13219,12 @@
       </c>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>Карпов Дмитрий Владимирович</t>
+          <t>Науменко Андрей Викторович</t>
         </is>
       </c>
       <c r="K127" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки инструментов повышения эффективности монетизации</t>
+          <t>Команда развития медиаконтента</t>
         </is>
       </c>
       <c r="L127" s="23" t="inlineStr">
@@ -13242,29 +13236,35 @@
         <v>1</v>
       </c>
       <c r="N127" s="23" t="n">
-        <v>56</v>
-      </c>
-      <c r="O127" s="8" t="n"/>
-      <c r="P127" s="27" t="n"/>
-      <c r="Q127" s="27" t="n"/>
+        <v>96</v>
+      </c>
+      <c r="O127" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="P127" s="27" t="n">
+        <v>46307</v>
+      </c>
+      <c r="Q127" s="27" t="n">
+        <v>46318</v>
+      </c>
       <c r="R127" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S127" s="8" t="inlineStr">
         <is>
-          <t>Тестирование ПО</t>
+          <t>Разработка (кодирование) ПО</t>
         </is>
       </c>
       <c r="T127" s="8" t="inlineStr">
         <is>
-          <t>Кабинет партнера: ссылки, промокоды, статистика: функциональное и интеграционное тестирование</t>
+          <t>Сопровождение промышленной эксплуатации рекламного кабинета: мониторинг, инциденты, обновления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U127" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-217</t>
+          <t>ADTHPL-228</t>
         </is>
       </c>
       <c r="V127" s="28" t="n">
@@ -13278,7 +13278,7 @@
     <row r="128">
       <c r="A128" s="8" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>ИТ</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
@@ -13288,32 +13288,32 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>CN-0765499</t>
+          <t>CN-0044250</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Дырда Ярослав Евгеньевич</t>
+          <t>Завьялов Алексей Сергеевич</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>Ведущий инженер сопровождения</t>
+          <t>Ведущий специалист по тестированию</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr">
         <is>
-          <t>6db71f8c-e788-11ef-ab45-e4434b7b9424</t>
+          <t>af7679bf-bf88-11eb-ab38-e4434b7b9424</t>
         </is>
       </c>
       <c r="G128" s="8" t="inlineStr">
         <is>
-          <t>6db7208b-e788-11ef-ab45-e4434b7b9424</t>
+          <t>38c8efcd-7e76-11ec-ab44-e4434b7a9a22</t>
         </is>
       </c>
       <c r="H128" s="8" t="inlineStr">
         <is>
-          <t>dyrda_ye@magnit.ru</t>
+          <t>zavyalov_a_s@magnit.ru</t>
         </is>
       </c>
       <c r="I128" s="8" t="inlineStr">
@@ -13323,12 +13323,12 @@
       </c>
       <c r="J128" s="8" t="inlineStr">
         <is>
-          <t>Науменко Андрей Викторович</t>
+          <t>Ермолаев Максим Михайлович</t>
         </is>
       </c>
       <c r="K128" s="8" t="inlineStr">
         <is>
-          <t>Команда развития медиаконтента</t>
+          <t>Команда разработки рекламной платформы</t>
         </is>
       </c>
       <c r="L128" s="23" t="inlineStr">
@@ -13340,39 +13340,39 @@
         <v>1</v>
       </c>
       <c r="N128" s="23" t="n">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="O128" s="8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P128" s="27" t="n">
+        <v>46296</v>
+      </c>
+      <c r="Q128" s="27" t="n">
+        <v>46297</v>
+      </c>
+      <c r="R128" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="S128" s="8" t="inlineStr">
+        <is>
+          <t>Тестирование ПО</t>
+        </is>
+      </c>
+      <c r="T128" s="8" t="inlineStr">
+        <is>
+          <t>Прогноз кликабельности для ранжирования ставок: нагрузочное тестирование</t>
+        </is>
+      </c>
+      <c r="U128" s="8" t="inlineStr">
+        <is>
+          <t>ADTHPL-260</t>
+        </is>
+      </c>
+      <c r="V128" s="28" t="n">
         <v>46307</v>
-      </c>
-      <c r="Q128" s="27" t="n">
-        <v>46318</v>
-      </c>
-      <c r="R128" s="8" t="inlineStr">
-        <is>
-          <t>OPEX</t>
-        </is>
-      </c>
-      <c r="S128" s="8" t="inlineStr">
-        <is>
-          <t>Разработка (кодирование) ПО</t>
-        </is>
-      </c>
-      <c r="T128" s="8" t="inlineStr">
-        <is>
-          <t>Сопровождение промышленной эксплуатации рекламного кабинета: мониторинг, инциденты, обновления (4 кв. 2026)</t>
-        </is>
-      </c>
-      <c r="U128" s="8" t="inlineStr">
-        <is>
-          <t>ADTHPL-228</t>
-        </is>
-      </c>
-      <c r="V128" s="28" t="n">
-        <v>46296</v>
       </c>
       <c r="W128" s="28" t="n">
         <v>46326</v>
@@ -13444,7 +13444,7 @@
         <v>1</v>
       </c>
       <c r="N129" s="23" t="n">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="O129" s="8" t="n">
         <v>2</v>
@@ -13467,16 +13467,16 @@
       </c>
       <c r="T129" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: нагрузочное тестирование</t>
+          <t>Геораспределенная отказоустойчивая инфраструктура выдачи: функциональное и интеграционное тестирование</t>
         </is>
       </c>
       <c r="U129" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-260</t>
+          <t>ADTHPL-253</t>
         </is>
       </c>
       <c r="V129" s="28" t="n">
-        <v>46307</v>
+        <v>46300</v>
       </c>
       <c r="W129" s="28" t="n">
         <v>46326</v>
@@ -13496,32 +13496,32 @@
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>CN-0044250</t>
+          <t>CN-0902759</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Завьялов Алексей Сергеевич</t>
+          <t>Багрин Иван Васильевич</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>Ведущий специалист по тестированию</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr">
         <is>
-          <t>af7679bf-bf88-11eb-ab38-e4434b7b9424</t>
+          <t>87692fd1-a424-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G130" s="8" t="inlineStr">
         <is>
-          <t>38c8efcd-7e76-11ec-ab44-e4434b7a9a22</t>
+          <t>8e9a517d-a424-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H130" s="8" t="inlineStr">
         <is>
-          <t>zavyalov_a_s@magnit.ru</t>
+          <t>bagrin_iv@magnit.ru</t>
         </is>
       </c>
       <c r="I130" s="8" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>Ермолаев Максим Михайлович</t>
+          <t>Авилов Александр Андреевич</t>
         </is>
       </c>
       <c r="K130" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки рекламной платформы</t>
+          <t>Команда разработки аффилиатной платформы</t>
         </is>
       </c>
       <c r="L130" s="23" t="inlineStr">
@@ -13548,39 +13548,33 @@
         <v>1</v>
       </c>
       <c r="N130" s="23" t="n">
-        <v>48</v>
-      </c>
-      <c r="O130" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P130" s="27" t="n">
+        <v>120</v>
+      </c>
+      <c r="O130" s="8" t="n"/>
+      <c r="P130" s="27" t="n"/>
+      <c r="Q130" s="27" t="n"/>
+      <c r="R130" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="S130" s="8" t="inlineStr">
+        <is>
+          <t>Разработка (кодирование) ПО</t>
+        </is>
+      </c>
+      <c r="T130" s="8" t="inlineStr">
+        <is>
+          <t>Автоматическая регистрация креативов и получение erid: разработка пользовательского интерфейса</t>
+        </is>
+      </c>
+      <c r="U130" s="8" t="inlineStr">
+        <is>
+          <t>ADTHPL-153</t>
+        </is>
+      </c>
+      <c r="V130" s="28" t="n">
         <v>46296</v>
-      </c>
-      <c r="Q130" s="27" t="n">
-        <v>46297</v>
-      </c>
-      <c r="R130" s="8" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="S130" s="8" t="inlineStr">
-        <is>
-          <t>Тестирование ПО</t>
-        </is>
-      </c>
-      <c r="T130" s="8" t="inlineStr">
-        <is>
-          <t>Геораспределенная отказоустойчивая инфраструктура выдачи: функциональное и интеграционное тестирование</t>
-        </is>
-      </c>
-      <c r="U130" s="8" t="inlineStr">
-        <is>
-          <t>ADTHPL-253</t>
-        </is>
-      </c>
-      <c r="V130" s="28" t="n">
-        <v>46300</v>
       </c>
       <c r="W130" s="28" t="n">
         <v>46326</v>
@@ -13652,7 +13646,7 @@
         <v>1</v>
       </c>
       <c r="N131" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O131" s="8" t="n"/>
       <c r="P131" s="27" t="n"/>
@@ -13669,12 +13663,12 @@
       </c>
       <c r="T131" s="8" t="inlineStr">
         <is>
-          <t>Автоматическая регистрация креативов и получение erid: разработка пользовательского интерфейса</t>
+          <t>Автоматическая регистрация креативов и получение erid: разработка серверной части и API</t>
         </is>
       </c>
       <c r="U131" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-153</t>
+          <t>ADTHPL-152</t>
         </is>
       </c>
       <c r="V131" s="28" t="n">
@@ -13698,12 +13692,12 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>CN-0902759</t>
+          <t>CN-0874859</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>Багрин Иван Васильевич</t>
+          <t>Заручевский Илья Вадимович</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
@@ -13713,17 +13707,17 @@
       </c>
       <c r="F132" s="8" t="inlineStr">
         <is>
-          <t>87692fd1-a424-11f0-86a4-3a68dd8b748f</t>
+          <t>19e72992-7e83-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G132" s="8" t="inlineStr">
         <is>
-          <t>8e9a517d-a424-11f0-86a4-3a68dd8b748f</t>
+          <t>19e72a13-7e83-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H132" s="8" t="inlineStr">
         <is>
-          <t>bagrin_iv@magnit.ru</t>
+          <t>zaruchevskiy_iv@magnit.ru</t>
         </is>
       </c>
       <c r="I132" s="8" t="inlineStr">
@@ -13733,12 +13727,12 @@
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>Авилов Александр Андреевич</t>
+          <t>Карпов Дмитрий Владимирович</t>
         </is>
       </c>
       <c r="K132" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки аффилиатной платформы</t>
+          <t>Команда разработки инструментов повышения эффективности монетизации</t>
         </is>
       </c>
       <c r="L132" s="23" t="inlineStr">
@@ -13750,11 +13744,17 @@
         <v>1</v>
       </c>
       <c r="N132" s="23" t="n">
-        <v>56</v>
-      </c>
-      <c r="O132" s="8" t="n"/>
-      <c r="P132" s="27" t="n"/>
-      <c r="Q132" s="27" t="n"/>
+        <v>64</v>
+      </c>
+      <c r="O132" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="P132" s="27" t="n">
+        <v>46314</v>
+      </c>
+      <c r="Q132" s="27" t="n">
+        <v>46325</v>
+      </c>
       <c r="R132" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -13767,19 +13767,19 @@
       </c>
       <c r="T132" s="8" t="inlineStr">
         <is>
-          <t>Автоматическая регистрация креативов и получение erid: разработка серверной части и API</t>
+          <t>Мастер создания кампании в рекламном кабинете: интеграция со смежными модулями платформы</t>
         </is>
       </c>
       <c r="U132" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-152</t>
+          <t>ADTHPL-172</t>
         </is>
       </c>
       <c r="V132" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W132" s="28" t="n">
-        <v>46326</v>
+        <v>46311</v>
       </c>
       <c r="X132" s="8" t="n"/>
     </row>
@@ -13848,7 +13848,7 @@
         <v>1</v>
       </c>
       <c r="N133" s="23" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="O133" s="8" t="n">
         <v>10</v>
@@ -13871,12 +13871,12 @@
       </c>
       <c r="T133" s="8" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: интеграция со смежными модулями платформы</t>
+          <t>Мастер создания кампании в рекламном кабинете: разработка хранения и обработки данных</t>
         </is>
       </c>
       <c r="U133" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-172</t>
+          <t>ADTHPL-173</t>
         </is>
       </c>
       <c r="V133" s="28" t="n">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>CN-0874859</t>
+          <t>CN-0619770</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Заручевский Илья Вадимович</t>
+          <t>Селезнёв Сергей Евгеньевич</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
@@ -13915,17 +13915,17 @@
       </c>
       <c r="F134" s="8" t="inlineStr">
         <is>
-          <t>19e72992-7e83-11f0-86a3-3a68dd8b748f</t>
+          <t>db283b3e-1c02-11ef-ab43-e4434b7b9424</t>
         </is>
       </c>
       <c r="G134" s="8" t="inlineStr">
         <is>
-          <t>19e72a13-7e83-11f0-86a3-3a68dd8b748f</t>
+          <t>db283c99-1c02-11ef-ab43-e4434b7b9424</t>
         </is>
       </c>
       <c r="H134" s="8" t="inlineStr">
         <is>
-          <t>zaruchevskiy_iv@magnit.ru</t>
+          <t>seleznev_se@magnit.ru</t>
         </is>
       </c>
       <c r="I134" s="8" t="inlineStr">
@@ -13935,12 +13935,12 @@
       </c>
       <c r="J134" s="8" t="inlineStr">
         <is>
-          <t>Карпов Дмитрий Владимирович</t>
+          <t>Абрамов Иван Андреевич</t>
         </is>
       </c>
       <c r="K134" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки инструментов повышения эффективности монетизации</t>
+          <t>Команда мобильной разработки медийной рекламы</t>
         </is>
       </c>
       <c r="L134" s="23" t="inlineStr">
@@ -13952,17 +13952,11 @@
         <v>1</v>
       </c>
       <c r="N134" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="O134" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="P134" s="27" t="n">
-        <v>46314</v>
-      </c>
-      <c r="Q134" s="27" t="n">
-        <v>46325</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="O134" s="8" t="n"/>
+      <c r="P134" s="27" t="n"/>
+      <c r="Q134" s="27" t="n"/>
       <c r="R134" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -13975,19 +13969,19 @@
       </c>
       <c r="T134" s="8" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: разработка хранения и обработки данных</t>
+          <t>Аукцион второй цены с динамическим минимальным порогом: разработка серверной части и API</t>
         </is>
       </c>
       <c r="U134" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-173</t>
+          <t>ADTHPL-155</t>
         </is>
       </c>
       <c r="V134" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W134" s="28" t="n">
-        <v>46311</v>
+        <v>46326</v>
       </c>
       <c r="X134" s="8" t="n"/>
     </row>
@@ -14056,7 +14050,7 @@
         <v>1</v>
       </c>
       <c r="N135" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O135" s="8" t="n"/>
       <c r="P135" s="27" t="n"/>
@@ -14073,16 +14067,16 @@
       </c>
       <c r="T135" s="8" t="inlineStr">
         <is>
-          <t>Аукцион второй цены с динамическим минимальным порогом: разработка серверной части и API</t>
+          <t>Модерация креативов в рекламном кабинете: разработка серверной части и API</t>
         </is>
       </c>
       <c r="U135" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-155</t>
+          <t>ADTHPL-255</t>
         </is>
       </c>
       <c r="V135" s="28" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="W135" s="28" t="n">
         <v>46326</v>
@@ -14102,12 +14096,12 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>CN-0619770</t>
+          <t>CN-0900302</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Селезнёв Сергей Евгеньевич</t>
+          <t>Муковня Александр Андреевич</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
@@ -14117,17 +14111,17 @@
       </c>
       <c r="F136" s="8" t="inlineStr">
         <is>
-          <t>db283b3e-1c02-11ef-ab43-e4434b7b9424</t>
+          <t>46fb9b7a-a058-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G136" s="8" t="inlineStr">
         <is>
-          <t>db283c99-1c02-11ef-ab43-e4434b7b9424</t>
+          <t>4d1ae72c-a058-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H136" s="8" t="inlineStr">
         <is>
-          <t>seleznev_se@magnit.ru</t>
+          <t>mukovnya_aa@magnit.ru</t>
         </is>
       </c>
       <c r="I136" s="8" t="inlineStr">
@@ -14137,12 +14131,12 @@
       </c>
       <c r="J136" s="8" t="inlineStr">
         <is>
-          <t>Абрамов Иван Андреевич</t>
+          <t>Карпов Дмитрий Владимирович</t>
         </is>
       </c>
       <c r="K136" s="8" t="inlineStr">
         <is>
-          <t>Команда мобильной разработки медийной рекламы</t>
+          <t>Команда разработки инструментов повышения эффективности монетизации</t>
         </is>
       </c>
       <c r="L136" s="23" t="inlineStr">
@@ -14154,7 +14148,7 @@
         <v>1</v>
       </c>
       <c r="N136" s="23" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="O136" s="8" t="n"/>
       <c r="P136" s="27" t="n"/>
@@ -14171,16 +14165,16 @@
       </c>
       <c r="T136" s="8" t="inlineStr">
         <is>
-          <t>Модерация креативов в рекламном кабинете: разработка серверной части и API</t>
+          <t>Прогноз кликабельности для ранжирования ставок: интеграция со смежными модулями платформы</t>
         </is>
       </c>
       <c r="U136" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-255</t>
+          <t>ADTHPL-160</t>
         </is>
       </c>
       <c r="V136" s="28" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="W136" s="28" t="n">
         <v>46326</v>
@@ -14252,7 +14246,7 @@
         <v>1</v>
       </c>
       <c r="N137" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O137" s="8" t="n"/>
       <c r="P137" s="27" t="n"/>
@@ -14269,12 +14263,12 @@
       </c>
       <c r="T137" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: интеграция со смежными модулями платформы</t>
+          <t>Прогноз кликабельности для ранжирования ставок: разработка фоновых обработчиков</t>
         </is>
       </c>
       <c r="U137" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-160</t>
+          <t>ADTHPL-163</t>
         </is>
       </c>
       <c r="V137" s="28" t="n">
@@ -14298,32 +14292,32 @@
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>CN-0900302</t>
+          <t>CN-0866070</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Муковня Александр Андреевич</t>
+          <t>Карпов Дмитрий Владимирович</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Руководитель команды</t>
         </is>
       </c>
       <c r="F138" s="8" t="inlineStr">
         <is>
-          <t>46fb9b7a-a058-11f0-86a4-3a68dd8b748f</t>
+          <t>745fcc50-72a6-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G138" s="8" t="inlineStr">
         <is>
-          <t>4d1ae72c-a058-11f0-86a4-3a68dd8b748f</t>
+          <t>745fcd18-72a6-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H138" s="8" t="inlineStr">
         <is>
-          <t>mukovnya_aa@magnit.ru</t>
+          <t>karpov_d_v@magnit.ru</t>
         </is>
       </c>
       <c r="I138" s="8" t="inlineStr">
@@ -14333,12 +14327,12 @@
       </c>
       <c r="J138" s="8" t="inlineStr">
         <is>
-          <t>Карпов Дмитрий Владимирович</t>
+          <t>Буров Глеб Олегович</t>
         </is>
       </c>
       <c r="K138" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки инструментов повышения эффективности монетизации</t>
+          <t>Управление разработки Эдтех</t>
         </is>
       </c>
       <c r="L138" s="23" t="inlineStr">
@@ -14350,36 +14344,42 @@
         <v>1</v>
       </c>
       <c r="N138" s="23" t="n">
-        <v>56</v>
-      </c>
-      <c r="O138" s="8" t="n"/>
-      <c r="P138" s="27" t="n"/>
-      <c r="Q138" s="27" t="n"/>
+        <v>95</v>
+      </c>
+      <c r="O138" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P138" s="27" t="n">
+        <v>46321</v>
+      </c>
+      <c r="Q138" s="27" t="n">
+        <v>46325</v>
+      </c>
       <c r="R138" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S138" s="8" t="inlineStr">
         <is>
-          <t>Разработка (кодирование) ПО</t>
+          <t>Менеджмент/ Административные задачи</t>
         </is>
       </c>
       <c r="T138" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: разработка хранения и обработки данных</t>
+          <t>Административное управление командой аналитики: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U138" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-161</t>
+          <t>ADTHPL-234</t>
         </is>
       </c>
       <c r="V138" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W138" s="28" t="n">
-        <v>46326</v>
+        <v>46318</v>
       </c>
       <c r="X138" s="8" t="n"/>
     </row>
@@ -14604,32 +14604,32 @@
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>CN-0866070</t>
+          <t>CN-0907215</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>Карпов Дмитрий Владимирович</t>
+          <t>Баланов Артем Романович</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>Руководитель команды</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="F141" s="8" t="inlineStr">
         <is>
-          <t>745fcc50-72a6-11f0-86a3-3a68dd8b748f</t>
+          <t>fecbfdf5-a9bb-11f0-93e0-c4cbe1a36811</t>
         </is>
       </c>
       <c r="G141" s="8" t="inlineStr">
         <is>
-          <t>745fcd18-72a6-11f0-86a3-3a68dd8b748f</t>
+          <t>fecbffb8-a9bb-11f0-93e0-c4cbe1a36811</t>
         </is>
       </c>
       <c r="H141" s="8" t="inlineStr">
         <is>
-          <t>karpov_d_v@magnit.ru</t>
+          <t>balanov_ar@magnit.ru</t>
         </is>
       </c>
       <c r="I141" s="8" t="inlineStr">
@@ -14639,12 +14639,12 @@
       </c>
       <c r="J141" s="8" t="inlineStr">
         <is>
-          <t>Буров Глеб Олегович</t>
+          <t>Ермолаев Максим Михайлович</t>
         </is>
       </c>
       <c r="K141" s="8" t="inlineStr">
         <is>
-          <t>Управление разработки Эдтех</t>
+          <t>Команда разработки рекламной платформы</t>
         </is>
       </c>
       <c r="L141" s="23" t="inlineStr">
@@ -14656,42 +14656,36 @@
         <v>1</v>
       </c>
       <c r="N141" s="23" t="n">
-        <v>95</v>
-      </c>
-      <c r="O141" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="P141" s="27" t="n">
-        <v>46321</v>
-      </c>
-      <c r="Q141" s="27" t="n">
-        <v>46325</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="O141" s="8" t="n"/>
+      <c r="P141" s="27" t="n"/>
+      <c r="Q141" s="27" t="n"/>
       <c r="R141" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S141" s="8" t="inlineStr">
         <is>
-          <t>Менеджмент/ Административные задачи</t>
+          <t>Разработка (кодирование) ПО</t>
         </is>
       </c>
       <c r="T141" s="8" t="inlineStr">
         <is>
-          <t>Административное управление командой аналитики: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Прогноз кликабельности для ранжирования ставок: разработка хранения и обработки данных</t>
         </is>
       </c>
       <c r="U141" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-234</t>
+          <t>ADTHPL-161</t>
         </is>
       </c>
       <c r="V141" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W141" s="28" t="n">
-        <v>46318</v>
+        <v>46326</v>
       </c>
       <c r="X141" s="8" t="n"/>
     </row>
@@ -14760,7 +14754,7 @@
         <v>1</v>
       </c>
       <c r="N142" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O142" s="8" t="n"/>
       <c r="P142" s="27" t="n"/>
@@ -14777,12 +14771,12 @@
       </c>
       <c r="T142" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: разработка хранения и обработки данных</t>
+          <t>Прогноз кликабельности для ранжирования ставок: разработка пользовательского интерфейса</t>
         </is>
       </c>
       <c r="U142" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-161</t>
+          <t>ADTHPL-159</t>
         </is>
       </c>
       <c r="V142" s="28" t="n">
@@ -14806,32 +14800,32 @@
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>CN-0907215</t>
+          <t>CN-0874823</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>Баланов Артем Романович</t>
+          <t>Пономарева Яна Дмитриевна</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Ведущий специалист по тестированию</t>
         </is>
       </c>
       <c r="F143" s="8" t="inlineStr">
         <is>
-          <t>fecbfdf5-a9bb-11f0-93e0-c4cbe1a36811</t>
+          <t>55d53f06-7e7f-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G143" s="8" t="inlineStr">
         <is>
-          <t>fecbffb8-a9bb-11f0-93e0-c4cbe1a36811</t>
+          <t>55d53fe0-7e7f-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H143" s="8" t="inlineStr">
         <is>
-          <t>balanov_ar@magnit.ru</t>
+          <t>ponomarevayd@magnit.ru</t>
         </is>
       </c>
       <c r="I143" s="8" t="inlineStr">
@@ -14841,12 +14835,12 @@
       </c>
       <c r="J143" s="8" t="inlineStr">
         <is>
-          <t>Ермолаев Максим Михайлович</t>
+          <t>Авилов Александр Андреевич</t>
         </is>
       </c>
       <c r="K143" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки рекламной платформы</t>
+          <t>Команда разработки аффилиатной платформы</t>
         </is>
       </c>
       <c r="L143" s="23" t="inlineStr">
@@ -14858,7 +14852,7 @@
         <v>1</v>
       </c>
       <c r="N143" s="23" t="n">
-        <v>56</v>
+        <v>160</v>
       </c>
       <c r="O143" s="8" t="n"/>
       <c r="P143" s="27" t="n"/>
@@ -14870,17 +14864,17 @@
       </c>
       <c r="S143" s="8" t="inlineStr">
         <is>
-          <t>Разработка (кодирование) ПО</t>
+          <t>Тестирование ПО</t>
         </is>
       </c>
       <c r="T143" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: разработка пользовательского интерфейса</t>
+          <t>Кабинет партнера: ссылки, промокоды, статистика: автоматизация регрессионных тестов</t>
         </is>
       </c>
       <c r="U143" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-159</t>
+          <t>ADTHPL-219</t>
         </is>
       </c>
       <c r="V143" s="28" t="n">
@@ -14956,7 +14950,7 @@
         <v>1</v>
       </c>
       <c r="N144" s="23" t="n">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="O144" s="8" t="n"/>
       <c r="P144" s="27" t="n"/>
@@ -14973,19 +14967,19 @@
       </c>
       <c r="T144" s="8" t="inlineStr">
         <is>
-          <t>Кабинет партнера: ссылки, промокоды, статистика: автоматизация регрессионных тестов</t>
+          <t>Доработка end-to-end тестов сторис в рекламном SDK для Android</t>
         </is>
       </c>
       <c r="U144" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-219</t>
+          <t>ADTHPL-150</t>
         </is>
       </c>
       <c r="V144" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W144" s="28" t="n">
-        <v>46326</v>
+        <v>46297</v>
       </c>
       <c r="X144" s="8" t="n"/>
     </row>
@@ -15002,32 +14996,32 @@
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>CN-0874823</t>
+          <t>KRF005946</t>
         </is>
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>Пономарева Яна Дмитриевна</t>
+          <t>Клименко Иван Сергеевич</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>Ведущий специалист по тестированию</t>
+          <t>Главный инженер по поддержке оборудования</t>
         </is>
       </c>
       <c r="F145" s="8" t="inlineStr">
         <is>
-          <t>55d53f06-7e7f-11f0-86a3-3a68dd8b748f</t>
+          <t>9982ddd8-6add-11dd-9dd3-00304834a125</t>
         </is>
       </c>
       <c r="G145" s="8" t="inlineStr">
         <is>
-          <t>55d53fe0-7e7f-11f0-86a3-3a68dd8b748f</t>
+          <t>f61101a2-0c7c-11eb-811d-42f2e92b7729</t>
         </is>
       </c>
       <c r="H145" s="8" t="inlineStr">
         <is>
-          <t>ponomarevayd@magnit.ru</t>
+          <t>klimenko@magnit.ru</t>
         </is>
       </c>
       <c r="I145" s="8" t="inlineStr">
@@ -15037,12 +15031,12 @@
       </c>
       <c r="J145" s="8" t="inlineStr">
         <is>
-          <t>Авилов Александр Андреевич</t>
+          <t>Науменко Андрей Викторович</t>
         </is>
       </c>
       <c r="K145" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки аффилиатной платформы</t>
+          <t>Команда развития медиаконтента</t>
         </is>
       </c>
       <c r="L145" s="23" t="inlineStr">
@@ -15054,11 +15048,17 @@
         <v>1</v>
       </c>
       <c r="N145" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="O145" s="8" t="n"/>
-      <c r="P145" s="27" t="n"/>
-      <c r="Q145" s="27" t="n"/>
+        <v>96</v>
+      </c>
+      <c r="O145" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P145" s="27" t="n">
+        <v>46321</v>
+      </c>
+      <c r="Q145" s="27" t="n">
+        <v>46325</v>
+      </c>
       <c r="R145" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -15066,24 +15066,24 @@
       </c>
       <c r="S145" s="8" t="inlineStr">
         <is>
-          <t>Тестирование ПО</t>
+          <t>Интеграция ПО</t>
         </is>
       </c>
       <c r="T145" s="8" t="inlineStr">
         <is>
-          <t>Доработка end-to-end тестов сторис в рекламном SDK для Android</t>
+          <t>Прогноз кликабельности для ранжирования ставок: развертывание и настройка серверной инфраструктуры</t>
         </is>
       </c>
       <c r="U145" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-150</t>
+          <t>ADTHPL-166</t>
         </is>
       </c>
       <c r="V145" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W145" s="28" t="n">
-        <v>46297</v>
+        <v>46318</v>
       </c>
       <c r="X145" s="8" t="n"/>
     </row>
@@ -15152,7 +15152,7 @@
         <v>1</v>
       </c>
       <c r="N146" s="23" t="n">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="O146" s="8" t="n">
         <v>5</v>
@@ -15175,19 +15175,19 @@
       </c>
       <c r="T146" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: развертывание и настройка серверной инфраструктуры</t>
+          <t>Дедупликация событий показов и кликов: приемка функциональности и подготовка к запуску</t>
         </is>
       </c>
       <c r="U146" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-166</t>
+          <t>ADTHPL-202</t>
         </is>
       </c>
       <c r="V146" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W146" s="28" t="n">
-        <v>46318</v>
+        <v>46311</v>
       </c>
       <c r="X146" s="8" t="n"/>
     </row>
@@ -15204,32 +15204,32 @@
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>KRF005946</t>
+          <t>CN-0871737</t>
         </is>
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>Клименко Иван Сергеевич</t>
+          <t>Кондукторов Артём Олегович</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>Главный инженер по поддержке оборудования</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="F147" s="8" t="inlineStr">
         <is>
-          <t>9982ddd8-6add-11dd-9dd3-00304834a125</t>
+          <t>3d1c3bc0-79c5-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G147" s="8" t="inlineStr">
         <is>
-          <t>f61101a2-0c7c-11eb-811d-42f2e92b7729</t>
+          <t>3d1c3cbe-79c5-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H147" s="8" t="inlineStr">
         <is>
-          <t>klimenko@magnit.ru</t>
+          <t>konduktorov_ao@magnit.ru</t>
         </is>
       </c>
       <c r="I147" s="8" t="inlineStr">
@@ -15239,12 +15239,12 @@
       </c>
       <c r="J147" s="8" t="inlineStr">
         <is>
-          <t>Науменко Андрей Викторович</t>
+          <t>Ермолаев Максим Михайлович</t>
         </is>
       </c>
       <c r="K147" s="8" t="inlineStr">
         <is>
-          <t>Команда развития медиаконтента</t>
+          <t>Команда разработки рекламной платформы</t>
         </is>
       </c>
       <c r="L147" s="23" t="inlineStr">
@@ -15256,17 +15256,11 @@
         <v>1</v>
       </c>
       <c r="N147" s="23" t="n">
-        <v>40</v>
-      </c>
-      <c r="O147" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="P147" s="27" t="n">
-        <v>46321</v>
-      </c>
-      <c r="Q147" s="27" t="n">
-        <v>46325</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="O147" s="8" t="n"/>
+      <c r="P147" s="27" t="n"/>
+      <c r="Q147" s="27" t="n"/>
       <c r="R147" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -15274,24 +15268,24 @@
       </c>
       <c r="S147" s="8" t="inlineStr">
         <is>
-          <t>Интеграция ПО</t>
+          <t>Разработка (кодирование) ПО</t>
         </is>
       </c>
       <c r="T147" s="8" t="inlineStr">
         <is>
-          <t>Дедупликация событий показов и кликов: приемка функциональности и подготовка к запуску</t>
+          <t>Прогноз кликабельности для ранжирования ставок: разработка фоновых обработчиков</t>
         </is>
       </c>
       <c r="U147" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-202</t>
+          <t>ADTHPL-163</t>
         </is>
       </c>
       <c r="V147" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W147" s="28" t="n">
-        <v>46311</v>
+        <v>46326</v>
       </c>
       <c r="X147" s="8" t="n"/>
     </row>
@@ -15360,7 +15354,7 @@
         <v>1</v>
       </c>
       <c r="N148" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O148" s="8" t="n"/>
       <c r="P148" s="27" t="n"/>
@@ -15377,12 +15371,12 @@
       </c>
       <c r="T148" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: разработка фоновых обработчиков</t>
+          <t>Прогноз кликабельности для ранжирования ставок: разработка хранения и обработки данных</t>
         </is>
       </c>
       <c r="U148" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-163</t>
+          <t>ADTHPL-161</t>
         </is>
       </c>
       <c r="V148" s="28" t="n">
@@ -15406,32 +15400,32 @@
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>CN-0871737</t>
+          <t>CN-0874711</t>
         </is>
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>Кондукторов Артём Олегович</t>
+          <t>Абдулхаков Амир Вахиджонович</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Главный разработчик</t>
         </is>
       </c>
       <c r="F149" s="8" t="inlineStr">
         <is>
-          <t>3d1c3bc0-79c5-11f0-86a3-3a68dd8b748f</t>
+          <t>0a7903e7-7e71-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G149" s="8" t="inlineStr">
         <is>
-          <t>3d1c3cbe-79c5-11f0-86a3-3a68dd8b748f</t>
+          <t>106fec9b-7e71-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H149" s="8" t="inlineStr">
         <is>
-          <t>konduktorov_ao@magnit.ru</t>
+          <t>abdulkhakov_av@magnit.ru</t>
         </is>
       </c>
       <c r="I149" s="8" t="inlineStr">
@@ -15441,12 +15435,12 @@
       </c>
       <c r="J149" s="8" t="inlineStr">
         <is>
-          <t>Ермолаев Максим Михайлович</t>
+          <t>Авилов Александр Андреевич</t>
         </is>
       </c>
       <c r="K149" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки рекламной платформы</t>
+          <t>Команда разработки аффилиатной платформы</t>
         </is>
       </c>
       <c r="L149" s="23" t="inlineStr">
@@ -15458,7 +15452,7 @@
         <v>1</v>
       </c>
       <c r="N149" s="23" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="O149" s="8" t="n"/>
       <c r="P149" s="27" t="n"/>
@@ -15475,19 +15469,19 @@
       </c>
       <c r="T149" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: разработка пользовательского интерфейса</t>
+          <t>Кабинет партнера: ссылки, промокоды, статистика: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="U149" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-159</t>
+          <t>ADTHPL-142</t>
         </is>
       </c>
       <c r="V149" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W149" s="28" t="n">
-        <v>46326</v>
+        <v>46325</v>
       </c>
       <c r="X149" s="8" t="n"/>
     </row>
@@ -15556,7 +15550,7 @@
         <v>1</v>
       </c>
       <c r="N150" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O150" s="8" t="n"/>
       <c r="P150" s="27" t="n"/>
@@ -15573,19 +15567,19 @@
       </c>
       <c r="T150" s="8" t="inlineStr">
         <is>
-          <t>Кабинет партнера: ссылки, промокоды, статистика: проектирование архитектуры и разработка ядра</t>
+          <t>Прогноз кликабельности для ранжирования ставок: разработка серверной части и API</t>
         </is>
       </c>
       <c r="U150" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-142</t>
+          <t>ADTHPL-168</t>
         </is>
       </c>
       <c r="V150" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W150" s="28" t="n">
-        <v>46325</v>
+        <v>46326</v>
       </c>
       <c r="X150" s="8" t="n"/>
     </row>
@@ -15602,32 +15596,32 @@
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>CN-0874711</t>
+          <t>CN-0962771</t>
         </is>
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>Абдулхаков Амир Вахиджонович</t>
+          <t>Золин Михаил Андреевич</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>Главный разработчик</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="F151" s="8" t="inlineStr">
         <is>
-          <t>0a7903e7-7e71-11f0-86a3-3a68dd8b748f</t>
+          <t>bc148265-0334-11f1-93e2-c4cbe1a36811</t>
         </is>
       </c>
       <c r="G151" s="8" t="inlineStr">
         <is>
-          <t>106fec9b-7e71-11f0-86a3-3a68dd8b748f</t>
+          <t>c20cf4ee-0334-11f1-93e2-c4cbe1a36811</t>
         </is>
       </c>
       <c r="H151" s="8" t="inlineStr">
         <is>
-          <t>abdulkhakov_av@magnit.ru</t>
+          <t>zolin_m_a@magnit.ru</t>
         </is>
       </c>
       <c r="I151" s="8" t="inlineStr">
@@ -15637,12 +15631,12 @@
       </c>
       <c r="J151" s="8" t="inlineStr">
         <is>
-          <t>Авилов Александр Андреевич</t>
+          <t>Абрамов Иван Андреевич</t>
         </is>
       </c>
       <c r="K151" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки аффилиатной платформы</t>
+          <t>Команда мобильной разработки медийной рекламы</t>
         </is>
       </c>
       <c r="L151" s="23" t="inlineStr">
@@ -15654,7 +15648,7 @@
         <v>1</v>
       </c>
       <c r="N151" s="23" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="O151" s="8" t="n"/>
       <c r="P151" s="27" t="n"/>
@@ -15671,12 +15665,12 @@
       </c>
       <c r="T151" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: разработка серверной части и API</t>
+          <t>Прогноз кликабельности для ранжирования ставок: оптимизация производительности</t>
         </is>
       </c>
       <c r="U151" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-168</t>
+          <t>ADTHPL-162</t>
         </is>
       </c>
       <c r="V151" s="28" t="n">
@@ -15752,7 +15746,7 @@
         <v>1</v>
       </c>
       <c r="N152" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O152" s="8" t="n"/>
       <c r="P152" s="27" t="n"/>
@@ -15769,12 +15763,12 @@
       </c>
       <c r="T152" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: оптимизация производительности</t>
+          <t>Прогноз кликабельности для ранжирования ставок: разработка пользовательского интерфейса</t>
         </is>
       </c>
       <c r="U152" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-162</t>
+          <t>ADTHPL-159</t>
         </is>
       </c>
       <c r="V152" s="28" t="n">
@@ -15798,32 +15792,32 @@
       </c>
       <c r="C153" s="8" t="inlineStr">
         <is>
-          <t>CN-0962771</t>
+          <t>CN-0877473</t>
         </is>
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>Золин Михаил Андреевич</t>
+          <t>Магомедалиев Алихан Магомедович</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Ведущий специалист по тестированию</t>
         </is>
       </c>
       <c r="F153" s="8" t="inlineStr">
         <is>
-          <t>bc148265-0334-11f1-93e2-c4cbe1a36811</t>
+          <t>06a0a01f-8320-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G153" s="8" t="inlineStr">
         <is>
-          <t>c20cf4ee-0334-11f1-93e2-c4cbe1a36811</t>
+          <t>0ca8d024-8320-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H153" s="8" t="inlineStr">
         <is>
-          <t>zolin_m_a@magnit.ru</t>
+          <t>magomedaliev_am@magnit.ru</t>
         </is>
       </c>
       <c r="I153" s="8" t="inlineStr">
@@ -15833,12 +15827,12 @@
       </c>
       <c r="J153" s="8" t="inlineStr">
         <is>
-          <t>Абрамов Иван Андреевич</t>
+          <t>Авилов Александр Андреевич</t>
         </is>
       </c>
       <c r="K153" s="8" t="inlineStr">
         <is>
-          <t>Команда мобильной разработки медийной рекламы</t>
+          <t>Команда разработки аффилиатной платформы</t>
         </is>
       </c>
       <c r="L153" s="23" t="inlineStr">
@@ -15850,11 +15844,17 @@
         <v>1</v>
       </c>
       <c r="N153" s="23" t="n">
-        <v>56</v>
-      </c>
-      <c r="O153" s="8" t="n"/>
-      <c r="P153" s="27" t="n"/>
-      <c r="Q153" s="27" t="n"/>
+        <v>120</v>
+      </c>
+      <c r="O153" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P153" s="27" t="n">
+        <v>46300</v>
+      </c>
+      <c r="Q153" s="27" t="n">
+        <v>46304</v>
+      </c>
       <c r="R153" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -15862,17 +15862,17 @@
       </c>
       <c r="S153" s="8" t="inlineStr">
         <is>
-          <t>Разработка (кодирование) ПО</t>
+          <t>Тестирование ПО</t>
         </is>
       </c>
       <c r="T153" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: разработка фоновых обработчиков</t>
+          <t>Кабинет партнера: ссылки, промокоды, статистика: нагрузочное тестирование</t>
         </is>
       </c>
       <c r="U153" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-163</t>
+          <t>ADTHPL-218</t>
         </is>
       </c>
       <c r="V153" s="28" t="n">
@@ -15948,7 +15948,7 @@
         <v>1</v>
       </c>
       <c r="N154" s="23" t="n">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="O154" s="8" t="n">
         <v>5</v>
@@ -15971,26 +15971,26 @@
       </c>
       <c r="T154" s="8" t="inlineStr">
         <is>
-          <t>Кабинет партнера: ссылки, промокоды, статистика: нагрузочное тестирование</t>
+          <t>Разработка интеграционных тестов модальных окон рекламного SDK в Android-приложении</t>
         </is>
       </c>
       <c r="U154" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-218</t>
+          <t>ADTHPL-151</t>
         </is>
       </c>
       <c r="V154" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W154" s="28" t="n">
-        <v>46326</v>
+        <v>46297</v>
       </c>
       <c r="X154" s="8" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="8" t="inlineStr">
         <is>
-          <t>ИТ</t>
+          <t>Аналитика</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
@@ -16000,68 +16000,68 @@
       </c>
       <c r="C155" s="8" t="inlineStr">
         <is>
-          <t>CN-0877473</t>
+          <t>CN-1087865</t>
         </is>
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>Магомедалиев Алихан Магомедович</t>
+          <t>Маслов Захар Михайлович</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>Ведущий специалист по тестированию</t>
+          <t>Аналитик данных</t>
         </is>
       </c>
       <c r="F155" s="8" t="inlineStr">
         <is>
-          <t>06a0a01f-8320-11f0-86a4-3a68dd8b748f</t>
+          <t>fc959cfe-c0b1-11f1-86a6-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G155" s="8" t="inlineStr">
         <is>
-          <t>0ca8d024-8320-11f0-86a4-3a68dd8b748f</t>
+          <t>6b3fdc82-c0b2-11f1-86a6-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H155" s="8" t="inlineStr">
         <is>
-          <t>magomedaliev_am@magnit.ru</t>
+          <t>maslov_zm@magnit.ru</t>
         </is>
       </c>
       <c r="I155" s="8" t="inlineStr">
         <is>
-          <t>Департамент по развитию и разработке онлайн платформ</t>
+          <t>Департамент по управлению данными и операционной аналитике цифровых платформ</t>
         </is>
       </c>
       <c r="J155" s="8" t="inlineStr">
         <is>
-          <t>Авилов Александр Андреевич</t>
+          <t>Убский Даниил Николаевич</t>
         </is>
       </c>
       <c r="K155" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки аффилиатной платформы</t>
+          <t>Направление продуктовой аналитики рекламных технологий</t>
         </is>
       </c>
       <c r="L155" s="23" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M155" s="23" t="n">
         <v>1</v>
       </c>
       <c r="N155" s="23" t="n">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="O155" s="8" t="n">
         <v>5</v>
       </c>
       <c r="P155" s="27" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="Q155" s="27" t="n">
-        <v>46304</v>
+        <v>46302</v>
       </c>
       <c r="R155" s="8" t="inlineStr">
         <is>
@@ -16070,26 +16070,30 @@
       </c>
       <c r="S155" s="8" t="inlineStr">
         <is>
-          <t>Тестирование ПО</t>
+          <t>Анализ (системный)</t>
         </is>
       </c>
       <c r="T155" s="8" t="inlineStr">
         <is>
-          <t>Разработка интеграционных тестов модальных окон рекламного SDK в Android-приложении</t>
+          <t>Автоматическая передача в ОРД данных о показах и актах: анализ данных и проектирование метрик</t>
         </is>
       </c>
       <c r="U155" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-151</t>
+          <t>ADTHPL-196</t>
         </is>
       </c>
       <c r="V155" s="28" t="n">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="W155" s="28" t="n">
-        <v>46297</v>
-      </c>
-      <c r="X155" s="8" t="n"/>
+        <v>46318</v>
+      </c>
+      <c r="X155" s="8" t="inlineStr">
+        <is>
+          <t>приступили к работе в октябре</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="8" t="inlineStr">
@@ -16156,7 +16160,7 @@
         <v>1</v>
       </c>
       <c r="N156" s="23" t="n">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="O156" s="8" t="n">
         <v>5</v>
@@ -16179,19 +16183,19 @@
       </c>
       <c r="T156" s="8" t="inlineStr">
         <is>
-          <t>Автоматическая передача в ОРД данных о показах и актах: анализ данных и проектирование метрик</t>
+          <t>Автоматическая передача в ОРД данных о показах и актах: проверка расчета метрик</t>
         </is>
       </c>
       <c r="U156" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-196</t>
+          <t>ADTHPL-296</t>
         </is>
       </c>
       <c r="V156" s="28" t="n">
-        <v>46303</v>
+        <v>46321</v>
       </c>
       <c r="W156" s="28" t="n">
-        <v>46318</v>
+        <v>46326</v>
       </c>
       <c r="X156" s="8" t="inlineStr">
         <is>
@@ -16202,7 +16206,7 @@
     <row r="157">
       <c r="A157" s="8" t="inlineStr">
         <is>
-          <t>Аналитика</t>
+          <t>ИТ</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
@@ -16212,100 +16216,90 @@
       </c>
       <c r="C157" s="8" t="inlineStr">
         <is>
-          <t>CN-1087865</t>
+          <t>CN-0920478</t>
         </is>
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>Маслов Захар Михайлович</t>
+          <t>Соколов Сергей Леонидович</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>Аналитик данных</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="F157" s="8" t="inlineStr">
         <is>
-          <t>fc959cfe-c0b1-11f1-86a6-3a68dd8b748f</t>
+          <t>bd8e4832-be0c-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G157" s="8" t="inlineStr">
         <is>
-          <t>6b3fdc82-c0b2-11f1-86a6-3a68dd8b748f</t>
+          <t>bd8e499d-be0c-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H157" s="8" t="inlineStr">
         <is>
-          <t>maslov_zm@magnit.ru</t>
+          <t>sokolov_sl@magnit.ru</t>
         </is>
       </c>
       <c r="I157" s="8" t="inlineStr">
         <is>
-          <t>Департамент по управлению данными и операционной аналитике цифровых платформ</t>
+          <t>Департамент по развитию и разработке онлайн платформ</t>
         </is>
       </c>
       <c r="J157" s="8" t="inlineStr">
         <is>
-          <t>Убский Даниил Николаевич</t>
+          <t>Авилов Александр Андреевич</t>
         </is>
       </c>
       <c r="K157" s="8" t="inlineStr">
         <is>
-          <t>Направление продуктовой аналитики рекламных технологий</t>
+          <t>Команда разработки аффилиатной платформы</t>
         </is>
       </c>
       <c r="L157" s="23" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>да</t>
         </is>
       </c>
       <c r="M157" s="23" t="n">
         <v>1</v>
       </c>
       <c r="N157" s="23" t="n">
-        <v>40</v>
-      </c>
-      <c r="O157" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="P157" s="27" t="n">
+        <v>120</v>
+      </c>
+      <c r="O157" s="8" t="n"/>
+      <c r="P157" s="27" t="n"/>
+      <c r="Q157" s="27" t="n"/>
+      <c r="R157" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="S157" s="8" t="inlineStr">
+        <is>
+          <t>Разработка (кодирование) ПО</t>
+        </is>
+      </c>
+      <c r="T157" s="8" t="inlineStr">
+        <is>
+          <t>Автоматическая регистрация креативов и получение erid: разработка серверной части и API</t>
+        </is>
+      </c>
+      <c r="U157" s="8" t="inlineStr">
+        <is>
+          <t>ADTHPL-152</t>
+        </is>
+      </c>
+      <c r="V157" s="28" t="n">
         <v>46296</v>
-      </c>
-      <c r="Q157" s="27" t="n">
-        <v>46302</v>
-      </c>
-      <c r="R157" s="8" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="S157" s="8" t="inlineStr">
-        <is>
-          <t>Анализ (системный)</t>
-        </is>
-      </c>
-      <c r="T157" s="8" t="inlineStr">
-        <is>
-          <t>Автоматическая передача в ОРД данных о показах и актах: проверка расчета метрик</t>
-        </is>
-      </c>
-      <c r="U157" s="8" t="inlineStr">
-        <is>
-          <t>ADTHPL-296</t>
-        </is>
-      </c>
-      <c r="V157" s="28" t="n">
-        <v>46321</v>
       </c>
       <c r="W157" s="28" t="n">
         <v>46326</v>
       </c>
-      <c r="X157" s="8" t="inlineStr">
-        <is>
-          <t>приступили к работе в октябре</t>
-        </is>
-      </c>
+      <c r="X157" s="8" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="8" t="inlineStr">
@@ -16372,7 +16366,7 @@
         <v>1</v>
       </c>
       <c r="N158" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O158" s="8" t="n"/>
       <c r="P158" s="27" t="n"/>
@@ -16389,12 +16383,12 @@
       </c>
       <c r="T158" s="8" t="inlineStr">
         <is>
-          <t>Автоматическая регистрация креативов и получение erid: разработка серверной части и API</t>
+          <t>Автоматическая регистрация креативов и получение erid: разработка пользовательского интерфейса</t>
         </is>
       </c>
       <c r="U158" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-152</t>
+          <t>ADTHPL-153</t>
         </is>
       </c>
       <c r="V158" s="28" t="n">
@@ -16418,12 +16412,12 @@
       </c>
       <c r="C159" s="8" t="inlineStr">
         <is>
-          <t>CN-0920478</t>
+          <t>CN-0654071</t>
         </is>
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>Соколов Сергей Леонидович</t>
+          <t>Кириенко Никита Алексеевич</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
@@ -16433,17 +16427,17 @@
       </c>
       <c r="F159" s="8" t="inlineStr">
         <is>
-          <t>bd8e4832-be0c-11f0-86a4-3a68dd8b748f</t>
+          <t>ee9047b6-4598-11ef-ab43-e4434b7b9424</t>
         </is>
       </c>
       <c r="G159" s="8" t="inlineStr">
         <is>
-          <t>bd8e499d-be0c-11f0-86a4-3a68dd8b748f</t>
+          <t>ee9048c6-4598-11ef-ab43-e4434b7b9424</t>
         </is>
       </c>
       <c r="H159" s="8" t="inlineStr">
         <is>
-          <t>sokolov_sl@magnit.ru</t>
+          <t>kirienko_na@magnit.ru</t>
         </is>
       </c>
       <c r="I159" s="8" t="inlineStr">
@@ -16453,12 +16447,12 @@
       </c>
       <c r="J159" s="8" t="inlineStr">
         <is>
-          <t>Авилов Александр Андреевич</t>
+          <t>Ермолаев Максим Михайлович</t>
         </is>
       </c>
       <c r="K159" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки аффилиатной платформы</t>
+          <t>Команда разработки рекламной платформы</t>
         </is>
       </c>
       <c r="L159" s="23" t="inlineStr">
@@ -16470,7 +16464,7 @@
         <v>1</v>
       </c>
       <c r="N159" s="23" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="O159" s="8" t="n"/>
       <c r="P159" s="27" t="n"/>
@@ -16487,12 +16481,12 @@
       </c>
       <c r="T159" s="8" t="inlineStr">
         <is>
-          <t>Автоматическая регистрация креативов и получение erid: разработка пользовательского интерфейса</t>
+          <t>Мастер создания кампании в рекламном кабинете: интеграция со смежными модулями платформы</t>
         </is>
       </c>
       <c r="U159" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-153</t>
+          <t>ADTHPL-172</t>
         </is>
       </c>
       <c r="V159" s="28" t="n">
@@ -16568,7 +16562,7 @@
         <v>1</v>
       </c>
       <c r="N160" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O160" s="8" t="n"/>
       <c r="P160" s="27" t="n"/>
@@ -16585,12 +16579,12 @@
       </c>
       <c r="T160" s="8" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: интеграция со смежными модулями платформы</t>
+          <t>Мастер создания кампании в рекламном кабинете: разработка хранения и обработки данных</t>
         </is>
       </c>
       <c r="U160" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-172</t>
+          <t>ADTHPL-173</t>
         </is>
       </c>
       <c r="V160" s="28" t="n">
@@ -16614,32 +16608,32 @@
       </c>
       <c r="C161" s="8" t="inlineStr">
         <is>
-          <t>CN-0654071</t>
+          <t>GKF010548</t>
         </is>
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>Кириенко Никита Алексеевич</t>
+          <t>Науменко Андрей Викторович</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Руководитель команды</t>
         </is>
       </c>
       <c r="F161" s="8" t="inlineStr">
         <is>
-          <t>ee9047b6-4598-11ef-ab43-e4434b7b9424</t>
+          <t>7eaeadd9-7263-11e5-89cf-5ef3fce0873b</t>
         </is>
       </c>
       <c r="G161" s="8" t="inlineStr">
         <is>
-          <t>ee9048c6-4598-11ef-ab43-e4434b7b9424</t>
+          <t>10ff5100-839d-11ee-ab42-e4434b7b9424</t>
         </is>
       </c>
       <c r="H161" s="8" t="inlineStr">
         <is>
-          <t>kirienko_na@magnit.ru</t>
+          <t>naumenko_av@magnit.ru</t>
         </is>
       </c>
       <c r="I161" s="8" t="inlineStr">
@@ -16649,12 +16643,12 @@
       </c>
       <c r="J161" s="8" t="inlineStr">
         <is>
-          <t>Ермолаев Максим Михайлович</t>
+          <t>Буров Глеб Олегович</t>
         </is>
       </c>
       <c r="K161" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки рекламной платформы</t>
+          <t>Управление разработки Эдтех</t>
         </is>
       </c>
       <c r="L161" s="23" t="inlineStr">
@@ -16666,36 +16660,42 @@
         <v>1</v>
       </c>
       <c r="N161" s="23" t="n">
-        <v>56</v>
-      </c>
-      <c r="O161" s="8" t="n"/>
-      <c r="P161" s="27" t="n"/>
-      <c r="Q161" s="27" t="n"/>
+        <v>95</v>
+      </c>
+      <c r="O161" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P161" s="27" t="n">
+        <v>46321</v>
+      </c>
+      <c r="Q161" s="27" t="n">
+        <v>46325</v>
+      </c>
       <c r="R161" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S161" s="8" t="inlineStr">
         <is>
-          <t>Разработка (кодирование) ПО</t>
+          <t>Менеджмент/ Административные задачи</t>
         </is>
       </c>
       <c r="T161" s="8" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: разработка хранения и обработки данных</t>
+          <t>Административное управление командой рекламного кабинета: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U161" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-173</t>
+          <t>ADTHPL-230</t>
         </is>
       </c>
       <c r="V161" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W161" s="28" t="n">
-        <v>46326</v>
+        <v>46318</v>
       </c>
       <c r="X161" s="8" t="n"/>
     </row>
@@ -16920,32 +16920,32 @@
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>GKF010548</t>
+          <t>CN-0997678</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>Науменко Андрей Викторович</t>
+          <t>Нестеров Владимир Алексеевич</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>Руководитель команды</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="F164" s="8" t="inlineStr">
         <is>
-          <t>7eaeadd9-7263-11e5-89cf-5ef3fce0873b</t>
+          <t>4c4f3334-3ed9-11f1-86a5-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G164" s="8" t="inlineStr">
         <is>
-          <t>10ff5100-839d-11ee-ab42-e4434b7b9424</t>
+          <t>12d04254-3eda-11f1-86a5-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H164" s="8" t="inlineStr">
         <is>
-          <t>naumenko_av@magnit.ru</t>
+          <t>nesterov_v@magnit.ru</t>
         </is>
       </c>
       <c r="I164" s="8" t="inlineStr">
@@ -16955,12 +16955,12 @@
       </c>
       <c r="J164" s="8" t="inlineStr">
         <is>
-          <t>Буров Глеб Олегович</t>
+          <t>Авилов Александр Андреевич</t>
         </is>
       </c>
       <c r="K164" s="8" t="inlineStr">
         <is>
-          <t>Управление разработки Эдтех</t>
+          <t>Команда разработки аффилиатной платформы</t>
         </is>
       </c>
       <c r="L164" s="23" t="inlineStr">
@@ -16972,42 +16972,46 @@
         <v>1</v>
       </c>
       <c r="N164" s="23" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O164" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="P164" s="27" t="n">
-        <v>46321</v>
-      </c>
-      <c r="Q164" s="27" t="n">
-        <v>46325</v>
+        <v>4</v>
+      </c>
+      <c r="P164" s="27" t="inlineStr">
+        <is>
+          <t>01.10.2026/08.10.2026</t>
+        </is>
+      </c>
+      <c r="Q164" s="27" t="inlineStr">
+        <is>
+          <t>02.10.2026/09.10.2026</t>
+        </is>
       </c>
       <c r="R164" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S164" s="8" t="inlineStr">
         <is>
-          <t>Менеджмент/ Административные задачи</t>
+          <t>Разработка (кодирование) ПО</t>
         </is>
       </c>
       <c r="T164" s="8" t="inlineStr">
         <is>
-          <t>Административное управление командой рекламного кабинета: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Автоматическая регистрация креативов и получение erid: разработка пользовательского интерфейса</t>
         </is>
       </c>
       <c r="U164" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-230</t>
+          <t>ADTHPL-153</t>
         </is>
       </c>
       <c r="V164" s="28" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="W164" s="28" t="n">
-        <v>46318</v>
+        <v>46326</v>
       </c>
       <c r="X164" s="8" t="n"/>
     </row>
@@ -17076,7 +17080,7 @@
         <v>1</v>
       </c>
       <c r="N165" s="23" t="n">
-        <v>104</v>
+        <v>40</v>
       </c>
       <c r="O165" s="8" t="n">
         <v>4</v>
@@ -17103,12 +17107,12 @@
       </c>
       <c r="T165" s="8" t="inlineStr">
         <is>
-          <t>Автоматическая регистрация креативов и получение erid: разработка пользовательского интерфейса</t>
+          <t>Автоматическая регистрация креативов и получение erid: разработка серверной части и API</t>
         </is>
       </c>
       <c r="U165" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-153</t>
+          <t>ADTHPL-152</t>
         </is>
       </c>
       <c r="V165" s="28" t="n">
@@ -17132,12 +17136,12 @@
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>CN-0997678</t>
+          <t>CN-0969365</t>
         </is>
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>Нестеров Владимир Алексеевич</t>
+          <t>Кузнецов Артем Сергеевич</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
@@ -17147,17 +17151,17 @@
       </c>
       <c r="F166" s="8" t="inlineStr">
         <is>
-          <t>4c4f3334-3ed9-11f1-86a5-3a68dd8b748f</t>
+          <t>b517858d-0d85-11f1-93e2-c4cbe1a36811</t>
         </is>
       </c>
       <c r="G166" s="8" t="inlineStr">
         <is>
-          <t>12d04254-3eda-11f1-86a5-3a68dd8b748f</t>
+          <t>bb143486-0d85-11f1-93e2-c4cbe1a36811</t>
         </is>
       </c>
       <c r="H166" s="8" t="inlineStr">
         <is>
-          <t>nesterov_v@magnit.ru</t>
+          <t>kuznetcov_as18@magnit.ru</t>
         </is>
       </c>
       <c r="I166" s="8" t="inlineStr">
@@ -17167,12 +17171,12 @@
       </c>
       <c r="J166" s="8" t="inlineStr">
         <is>
-          <t>Авилов Александр Андреевич</t>
+          <t>Ермолаев Максим Михайлович</t>
         </is>
       </c>
       <c r="K166" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки аффилиатной платформы</t>
+          <t>Команда разработки рекламной платформы</t>
         </is>
       </c>
       <c r="L166" s="23" t="inlineStr">
@@ -17184,21 +17188,11 @@
         <v>1</v>
       </c>
       <c r="N166" s="23" t="n">
-        <v>40</v>
-      </c>
-      <c r="O166" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="P166" s="27" t="inlineStr">
-        <is>
-          <t>01.10.2026/08.10.2026</t>
-        </is>
-      </c>
-      <c r="Q166" s="27" t="inlineStr">
-        <is>
-          <t>02.10.2026/09.10.2026</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="O166" s="8" t="n"/>
+      <c r="P166" s="27" t="n"/>
+      <c r="Q166" s="27" t="n"/>
       <c r="R166" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -17211,16 +17205,16 @@
       </c>
       <c r="T166" s="8" t="inlineStr">
         <is>
-          <t>Автоматическая регистрация креативов и получение erid: разработка серверной части и API</t>
+          <t>Мастер создания кампании в рекламном кабинете: разработка фоновых обработчиков</t>
         </is>
       </c>
       <c r="U166" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-152</t>
+          <t>ADTHPL-174</t>
         </is>
       </c>
       <c r="V166" s="28" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="W166" s="28" t="n">
         <v>46326</v>
@@ -17292,7 +17286,7 @@
         <v>1</v>
       </c>
       <c r="N167" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O167" s="8" t="n"/>
       <c r="P167" s="27" t="n"/>
@@ -17309,12 +17303,12 @@
       </c>
       <c r="T167" s="8" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: разработка фоновых обработчиков</t>
+          <t>Мастер создания кампании в рекламном кабинете: разработка хранения и обработки данных</t>
         </is>
       </c>
       <c r="U167" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-174</t>
+          <t>ADTHPL-173</t>
         </is>
       </c>
       <c r="V167" s="28" t="n">
@@ -17338,32 +17332,32 @@
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>CN-0969365</t>
+          <t>CN-0547657</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>Кузнецов Артем Сергеевич</t>
+          <t>Дмитриев Илья Владиславович</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Главный разработчик</t>
         </is>
       </c>
       <c r="F168" s="8" t="inlineStr">
         <is>
-          <t>b517858d-0d85-11f1-93e2-c4cbe1a36811</t>
+          <t>47d63bf9-b38d-11ee-ab4e-f8f21e64b171</t>
         </is>
       </c>
       <c r="G168" s="8" t="inlineStr">
         <is>
-          <t>bb143486-0d85-11f1-93e2-c4cbe1a36811</t>
+          <t>4dd15bcc-b38d-11ee-ab4e-f8f21e64b171</t>
         </is>
       </c>
       <c r="H168" s="8" t="inlineStr">
         <is>
-          <t>kuznetcov_as18@magnit.ru</t>
+          <t>dmitriev_iv@magnit.ru</t>
         </is>
       </c>
       <c r="I168" s="8" t="inlineStr">
@@ -17390,7 +17384,7 @@
         <v>1</v>
       </c>
       <c r="N168" s="23" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="O168" s="8" t="n"/>
       <c r="P168" s="27" t="n"/>
@@ -17407,12 +17401,12 @@
       </c>
       <c r="T168" s="8" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: разработка хранения и обработки данных</t>
+          <t>Мастер создания кампании в рекламном кабинете: разработка пользовательского интерфейса</t>
         </is>
       </c>
       <c r="U168" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-173</t>
+          <t>ADTHPL-177</t>
         </is>
       </c>
       <c r="V168" s="28" t="n">
@@ -17488,7 +17482,7 @@
         <v>1</v>
       </c>
       <c r="N169" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O169" s="8" t="n"/>
       <c r="P169" s="27" t="n"/>
@@ -17505,12 +17499,12 @@
       </c>
       <c r="T169" s="8" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: разработка пользовательского интерфейса</t>
+          <t>Мастер создания кампании в рекламном кабинете: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="U169" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-177</t>
+          <t>ADTHPL-175</t>
         </is>
       </c>
       <c r="V169" s="28" t="n">
@@ -17534,32 +17528,32 @@
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>CN-0547657</t>
+          <t>CN-1048160</t>
         </is>
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>Дмитриев Илья Владиславович</t>
+          <t>Горобец Александр Николаевич</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>Главный разработчик</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="F170" s="8" t="inlineStr">
         <is>
-          <t>47d63bf9-b38d-11ee-ab4e-f8f21e64b171</t>
+          <t>46fde8e9-8b48-11f1-86a5-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G170" s="8" t="inlineStr">
         <is>
-          <t>4dd15bcc-b38d-11ee-ab4e-f8f21e64b171</t>
+          <t>0dd0ff3b-8b49-11f1-86a5-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H170" s="8" t="inlineStr">
         <is>
-          <t>dmitriev_iv@magnit.ru</t>
+          <t>gorobetc_an@magnit.ru</t>
         </is>
       </c>
       <c r="I170" s="8" t="inlineStr">
@@ -17569,12 +17563,12 @@
       </c>
       <c r="J170" s="8" t="inlineStr">
         <is>
-          <t>Ермолаев Максим Михайлович</t>
+          <t>Абрамов Иван Андреевич</t>
         </is>
       </c>
       <c r="K170" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки рекламной платформы</t>
+          <t>Команда мобильной разработки медийной рекламы</t>
         </is>
       </c>
       <c r="L170" s="23" t="inlineStr">
@@ -17586,7 +17580,7 @@
         <v>1</v>
       </c>
       <c r="N170" s="23" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="O170" s="8" t="n"/>
       <c r="P170" s="27" t="n"/>
@@ -17603,12 +17597,12 @@
       </c>
       <c r="T170" s="8" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: проектирование архитектуры и разработка ядра</t>
+          <t>Прогноз кликабельности для ранжирования ставок: разработка пользовательского интерфейса</t>
         </is>
       </c>
       <c r="U170" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-175</t>
+          <t>ADTHPL-159</t>
         </is>
       </c>
       <c r="V170" s="28" t="n">
@@ -17684,7 +17678,7 @@
         <v>1</v>
       </c>
       <c r="N171" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O171" s="8" t="n"/>
       <c r="P171" s="27" t="n"/>
@@ -17701,12 +17695,12 @@
       </c>
       <c r="T171" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: разработка пользовательского интерфейса</t>
+          <t>Прогноз кликабельности для ранжирования ставок: разработка хранения и обработки данных</t>
         </is>
       </c>
       <c r="U171" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-159</t>
+          <t>ADTHPL-161</t>
         </is>
       </c>
       <c r="V171" s="28" t="n">
@@ -17730,32 +17724,32 @@
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>CN-1048160</t>
+          <t>CN-0881158</t>
         </is>
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>Горобец Александр Николаевич</t>
+          <t>Мерионков Кирилл Анатольевич</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Главный разработчик</t>
         </is>
       </c>
       <c r="F172" s="8" t="inlineStr">
         <is>
-          <t>46fde8e9-8b48-11f1-86a5-3a68dd8b748f</t>
+          <t>a4fe7c50-87fe-11f0-af3a-f8f21e64d511</t>
         </is>
       </c>
       <c r="G172" s="8" t="inlineStr">
         <is>
-          <t>0dd0ff3b-8b49-11f1-86a5-3a68dd8b748f</t>
+          <t>a4fe7dde-87fe-11f0-af3a-f8f21e64d511</t>
         </is>
       </c>
       <c r="H172" s="8" t="inlineStr">
         <is>
-          <t>gorobetc_an@magnit.ru</t>
+          <t>merionkov_ka@magnit.ru</t>
         </is>
       </c>
       <c r="I172" s="8" t="inlineStr">
@@ -17782,7 +17776,7 @@
         <v>1</v>
       </c>
       <c r="N172" s="23" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="O172" s="8" t="n"/>
       <c r="P172" s="27" t="n"/>
@@ -17799,12 +17793,12 @@
       </c>
       <c r="T172" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: разработка хранения и обработки данных</t>
+          <t>Аукцион второй цены с динамическим минимальным порогом: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="U172" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-161</t>
+          <t>ADTHPL-156</t>
         </is>
       </c>
       <c r="V172" s="28" t="n">
@@ -17880,7 +17874,7 @@
         <v>1</v>
       </c>
       <c r="N173" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O173" s="8" t="n"/>
       <c r="P173" s="27" t="n"/>
@@ -17897,16 +17891,16 @@
       </c>
       <c r="T173" s="8" t="inlineStr">
         <is>
-          <t>Аукцион второй цены с динамическим минимальным порогом: проектирование архитектуры и разработка ядра</t>
+          <t>Таргетинг по сегментам аудиторий в реальном времени: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="U173" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-156</t>
+          <t>ADTHPL-264</t>
         </is>
       </c>
       <c r="V173" s="28" t="n">
-        <v>46296</v>
+        <v>46307</v>
       </c>
       <c r="W173" s="28" t="n">
         <v>46326</v>
@@ -17926,12 +17920,12 @@
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>CN-0881158</t>
+          <t>CN-0851939</t>
         </is>
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>Мерионков Кирилл Анатольевич</t>
+          <t>Руденов Андрей Петрович</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
@@ -17941,17 +17935,17 @@
       </c>
       <c r="F174" s="8" t="inlineStr">
         <is>
-          <t>a4fe7c50-87fe-11f0-af3a-f8f21e64d511</t>
+          <t>86bc25a0-6189-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G174" s="8" t="inlineStr">
         <is>
-          <t>a4fe7dde-87fe-11f0-af3a-f8f21e64d511</t>
+          <t>86bc268c-6189-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H174" s="8" t="inlineStr">
         <is>
-          <t>merionkov_ka@magnit.ru</t>
+          <t>rudenov_ap@magnit.ru</t>
         </is>
       </c>
       <c r="I174" s="8" t="inlineStr">
@@ -17961,12 +17955,12 @@
       </c>
       <c r="J174" s="8" t="inlineStr">
         <is>
-          <t>Абрамов Иван Андреевич</t>
+          <t>Алтухов Руслан Дмитриевич</t>
         </is>
       </c>
       <c r="K174" s="8" t="inlineStr">
         <is>
-          <t>Команда мобильной разработки медийной рекламы</t>
+          <t>Команда разработки продуктов закрепления и буста</t>
         </is>
       </c>
       <c r="L174" s="23" t="inlineStr">
@@ -17978,7 +17972,7 @@
         <v>1</v>
       </c>
       <c r="N174" s="23" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="O174" s="8" t="n"/>
       <c r="P174" s="27" t="n"/>
@@ -17995,16 +17989,16 @@
       </c>
       <c r="T174" s="8" t="inlineStr">
         <is>
-          <t>Таргетинг по сегментам аудиторий в реальном времени: проектирование архитектуры и разработка ядра</t>
+          <t>Мастер создания кампании в рекламном кабинете: разработка серверной части и API</t>
         </is>
       </c>
       <c r="U174" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-264</t>
+          <t>ADTHPL-176</t>
         </is>
       </c>
       <c r="V174" s="28" t="n">
-        <v>46307</v>
+        <v>46296</v>
       </c>
       <c r="W174" s="28" t="n">
         <v>46326</v>
@@ -18076,7 +18070,7 @@
         <v>1</v>
       </c>
       <c r="N175" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O175" s="8" t="n"/>
       <c r="P175" s="27" t="n"/>
@@ -18093,12 +18087,12 @@
       </c>
       <c r="T175" s="8" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: разработка серверной части и API</t>
+          <t>Мастер создания кампании в рекламном кабинете: разработка пользовательского интерфейса</t>
         </is>
       </c>
       <c r="U175" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-176</t>
+          <t>ADTHPL-177</t>
         </is>
       </c>
       <c r="V175" s="28" t="n">
@@ -18122,32 +18116,32 @@
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>CN-0851939</t>
+          <t>CN-0632696</t>
         </is>
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>Руденов Андрей Петрович</t>
+          <t>Ромашов Владимир Сергеевич</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>Главный разработчик</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="F176" s="8" t="inlineStr">
         <is>
-          <t>86bc25a0-6189-11f0-86a3-3a68dd8b748f</t>
+          <t>67cccb78-2e2f-11ef-ab43-e4434b7b9424</t>
         </is>
       </c>
       <c r="G176" s="8" t="inlineStr">
         <is>
-          <t>86bc268c-6189-11f0-86a3-3a68dd8b748f</t>
+          <t>67cccd4f-2e2f-11ef-ab43-e4434b7b9424</t>
         </is>
       </c>
       <c r="H176" s="8" t="inlineStr">
         <is>
-          <t>rudenov_ap@magnit.ru</t>
+          <t>romashov_vs@magnit.ru</t>
         </is>
       </c>
       <c r="I176" s="8" t="inlineStr">
@@ -18157,12 +18151,12 @@
       </c>
       <c r="J176" s="8" t="inlineStr">
         <is>
-          <t>Алтухов Руслан Дмитриевич</t>
+          <t>Абрамов Иван Андреевич</t>
         </is>
       </c>
       <c r="K176" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки продуктов закрепления и буста</t>
+          <t>Команда мобильной разработки медийной рекламы</t>
         </is>
       </c>
       <c r="L176" s="23" t="inlineStr">
@@ -18174,11 +18168,21 @@
         <v>1</v>
       </c>
       <c r="N176" s="23" t="n">
-        <v>56</v>
-      </c>
-      <c r="O176" s="8" t="n"/>
-      <c r="P176" s="27" t="n"/>
-      <c r="Q176" s="27" t="n"/>
+        <v>112</v>
+      </c>
+      <c r="O176" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="P176" s="27" t="inlineStr">
+        <is>
+          <t>23.10.2026/30.10.2026</t>
+        </is>
+      </c>
+      <c r="Q176" s="27" t="inlineStr">
+        <is>
+          <t>23.10.2026/30.10.2026</t>
+        </is>
+      </c>
       <c r="R176" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -18191,19 +18195,19 @@
       </c>
       <c r="T176" s="8" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: разработка пользовательского интерфейса</t>
+          <t>Прогноз кликабельности для ранжирования ставок: интеграция со смежными модулями платформы</t>
         </is>
       </c>
       <c r="U176" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-177</t>
+          <t>ADTHPL-160</t>
         </is>
       </c>
       <c r="V176" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W176" s="28" t="n">
-        <v>46326</v>
+        <v>46324</v>
       </c>
       <c r="X176" s="8" t="n"/>
     </row>
@@ -18272,7 +18276,7 @@
         <v>1</v>
       </c>
       <c r="N177" s="23" t="n">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="O177" s="8" t="n">
         <v>2</v>
@@ -18299,12 +18303,12 @@
       </c>
       <c r="T177" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: интеграция со смежными модулями платформы</t>
+          <t>Прогноз кликабельности для ранжирования ставок: разработка пользовательского интерфейса</t>
         </is>
       </c>
       <c r="U177" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-160</t>
+          <t>ADTHPL-159</t>
         </is>
       </c>
       <c r="V177" s="28" t="n">
@@ -18328,32 +18332,32 @@
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>CN-0632696</t>
+          <t>CN-0699129</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>Ромашов Владимир Сергеевич</t>
+          <t>Самойлов Илья Алексеевич</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Главный разработчик</t>
         </is>
       </c>
       <c r="F178" s="8" t="inlineStr">
         <is>
-          <t>67cccb78-2e2f-11ef-ab43-e4434b7b9424</t>
+          <t>d727f4cc-86e6-11ef-ab45-e4434b7b9424</t>
         </is>
       </c>
       <c r="G178" s="8" t="inlineStr">
         <is>
-          <t>67cccd4f-2e2f-11ef-ab43-e4434b7b9424</t>
+          <t>d727f6fd-86e6-11ef-ab45-e4434b7b9424</t>
         </is>
       </c>
       <c r="H178" s="8" t="inlineStr">
         <is>
-          <t>romashov_vs@magnit.ru</t>
+          <t>samoylov_i_a@magnit.ru</t>
         </is>
       </c>
       <c r="I178" s="8" t="inlineStr">
@@ -18363,12 +18367,12 @@
       </c>
       <c r="J178" s="8" t="inlineStr">
         <is>
-          <t>Абрамов Иван Андреевич</t>
+          <t>Алтухов Руслан Дмитриевич</t>
         </is>
       </c>
       <c r="K178" s="8" t="inlineStr">
         <is>
-          <t>Команда мобильной разработки медийной рекламы</t>
+          <t>Команда разработки продуктов закрепления и буста</t>
         </is>
       </c>
       <c r="L178" s="23" t="inlineStr">
@@ -18380,20 +18384,16 @@
         <v>1</v>
       </c>
       <c r="N178" s="23" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="O178" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P178" s="27" t="inlineStr">
-        <is>
-          <t>23.10.2026/30.10.2026</t>
-        </is>
-      </c>
-      <c r="Q178" s="27" t="inlineStr">
-        <is>
-          <t>23.10.2026/30.10.2026</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="P178" s="27" t="n">
+        <v>46307</v>
+      </c>
+      <c r="Q178" s="27" t="n">
+        <v>46311</v>
       </c>
       <c r="R178" s="8" t="inlineStr">
         <is>
@@ -18407,19 +18407,19 @@
       </c>
       <c r="T178" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: разработка фоновых обработчиков</t>
+          <t>Бюджет и биллинг рекламодателя в кабинете: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="U178" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-163</t>
+          <t>ADTHPL-146</t>
         </is>
       </c>
       <c r="V178" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W178" s="28" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="X178" s="8" t="n"/>
     </row>
@@ -18488,7 +18488,7 @@
         <v>1</v>
       </c>
       <c r="N179" s="23" t="n">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="O179" s="8" t="n">
         <v>5</v>
@@ -18511,16 +18511,16 @@
       </c>
       <c r="T179" s="8" t="inlineStr">
         <is>
-          <t>Бюджет и биллинг рекламодателя в кабинете: проектирование архитектуры и разработка ядра</t>
+          <t>Интеграция с внешними SSP по OpenRTB 2.6: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="U179" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-146</t>
+          <t>ADTHPL-277</t>
         </is>
       </c>
       <c r="V179" s="28" t="n">
-        <v>46296</v>
+        <v>46314</v>
       </c>
       <c r="W179" s="28" t="n">
         <v>46326</v>
@@ -18540,32 +18540,32 @@
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>CN-0699129</t>
+          <t>CN-0680813</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>Самойлов Илья Алексеевич</t>
+          <t>Синявский Артур Игоревич</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>Главный разработчик</t>
+          <t>Ведущий разработчик</t>
         </is>
       </c>
       <c r="F180" s="8" t="inlineStr">
         <is>
-          <t>d727f4cc-86e6-11ef-ab45-e4434b7b9424</t>
+          <t>ed2d697f-6c56-11ef-ab44-e4434b7b9424</t>
         </is>
       </c>
       <c r="G180" s="8" t="inlineStr">
         <is>
-          <t>d727f6fd-86e6-11ef-ab45-e4434b7b9424</t>
+          <t>ed2d6a23-6c56-11ef-ab44-e4434b7b9424</t>
         </is>
       </c>
       <c r="H180" s="8" t="inlineStr">
         <is>
-          <t>samoylov_i_a@magnit.ru</t>
+          <t>sinyavskiy_ai@magnit.ru</t>
         </is>
       </c>
       <c r="I180" s="8" t="inlineStr">
@@ -18575,12 +18575,12 @@
       </c>
       <c r="J180" s="8" t="inlineStr">
         <is>
-          <t>Алтухов Руслан Дмитриевич</t>
+          <t>Чудинов Валерий Иванович</t>
         </is>
       </c>
       <c r="K180" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки продуктов закрепления и буста</t>
+          <t>Отдел разработки медийной рекламы</t>
         </is>
       </c>
       <c r="L180" s="23" t="inlineStr">
@@ -18592,16 +18592,20 @@
         <v>1</v>
       </c>
       <c r="N180" s="23" t="n">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="O180" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="P180" s="27" t="n">
-        <v>46307</v>
-      </c>
-      <c r="Q180" s="27" t="n">
-        <v>46311</v>
+        <v>2</v>
+      </c>
+      <c r="P180" s="27" t="inlineStr">
+        <is>
+          <t>09.10.2026/12.10.2026</t>
+        </is>
+      </c>
+      <c r="Q180" s="27" t="inlineStr">
+        <is>
+          <t>09.10.2026/12.10.2026</t>
+        </is>
       </c>
       <c r="R180" s="8" t="inlineStr">
         <is>
@@ -18615,16 +18619,16 @@
       </c>
       <c r="T180" s="8" t="inlineStr">
         <is>
-          <t>Интеграция с внешними SSP по OpenRTB 2.6: проектирование архитектуры и разработка ядра</t>
+          <t>Прогноз кликабельности для ранжирования ставок: оптимизация производительности</t>
         </is>
       </c>
       <c r="U180" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-277</t>
+          <t>ADTHPL-162</t>
         </is>
       </c>
       <c r="V180" s="28" t="n">
-        <v>46314</v>
+        <v>46296</v>
       </c>
       <c r="W180" s="28" t="n">
         <v>46326</v>
@@ -18696,7 +18700,7 @@
         <v>1</v>
       </c>
       <c r="N181" s="23" t="n">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="O181" s="8" t="n">
         <v>2</v>
@@ -18723,12 +18727,12 @@
       </c>
       <c r="T181" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: оптимизация производительности</t>
+          <t>Прогноз кликабельности для ранжирования ставок: интеграция со смежными модулями платформы</t>
         </is>
       </c>
       <c r="U181" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-162</t>
+          <t>ADTHPL-160</t>
         </is>
       </c>
       <c r="V181" s="28" t="n">
@@ -18752,32 +18756,32 @@
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>CN-0680813</t>
+          <t>CN-0920422</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>Синявский Артур Игоревич</t>
+          <t>Третьяков Денис Владимирович</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>Ведущий разработчик</t>
+          <t>Главный разработчик</t>
         </is>
       </c>
       <c r="F182" s="8" t="inlineStr">
         <is>
-          <t>ed2d697f-6c56-11ef-ab44-e4434b7b9424</t>
+          <t>1a99d136-be08-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G182" s="8" t="inlineStr">
         <is>
-          <t>ed2d6a23-6c56-11ef-ab44-e4434b7b9424</t>
+          <t>1a99d2da-be08-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H182" s="8" t="inlineStr">
         <is>
-          <t>sinyavskiy_ai@magnit.ru</t>
+          <t>dvtretyakov@magnit.ru</t>
         </is>
       </c>
       <c r="I182" s="8" t="inlineStr">
@@ -18787,12 +18791,12 @@
       </c>
       <c r="J182" s="8" t="inlineStr">
         <is>
-          <t>Чудинов Валерий Иванович</t>
+          <t>Абрамов Иван Андреевич</t>
         </is>
       </c>
       <c r="K182" s="8" t="inlineStr">
         <is>
-          <t>Отдел разработки медийной рекламы</t>
+          <t>Команда мобильной разработки медийной рекламы</t>
         </is>
       </c>
       <c r="L182" s="23" t="inlineStr">
@@ -18804,21 +18808,11 @@
         <v>1</v>
       </c>
       <c r="N182" s="23" t="n">
-        <v>48</v>
-      </c>
-      <c r="O182" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="P182" s="27" t="inlineStr">
-        <is>
-          <t>09.10.2026/12.10.2026</t>
-        </is>
-      </c>
-      <c r="Q182" s="27" t="inlineStr">
-        <is>
-          <t>09.10.2026/12.10.2026</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="O182" s="8" t="n"/>
+      <c r="P182" s="27" t="n"/>
+      <c r="Q182" s="27" t="n"/>
       <c r="R182" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -18831,12 +18825,12 @@
       </c>
       <c r="T182" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: разработка фоновых обработчиков</t>
+          <t>Аукцион второй цены с динамическим минимальным порогом: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="U182" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-163</t>
+          <t>ADTHPL-156</t>
         </is>
       </c>
       <c r="V182" s="28" t="n">
@@ -18912,7 +18906,7 @@
         <v>1</v>
       </c>
       <c r="N183" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O183" s="8" t="n"/>
       <c r="P183" s="27" t="n"/>
@@ -18929,12 +18923,12 @@
       </c>
       <c r="T183" s="8" t="inlineStr">
         <is>
-          <t>Аукцион второй цены с динамическим минимальным порогом: проектирование архитектуры и разработка ядра</t>
+          <t>Прогноз кликабельности для ранжирования ставок: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="U183" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-156</t>
+          <t>ADTHPL-167</t>
         </is>
       </c>
       <c r="V183" s="28" t="n">
@@ -18958,12 +18952,12 @@
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>CN-0920422</t>
+          <t>CN-0997224</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Третьяков Денис Владимирович</t>
+          <t>Скворцов Виталий Павлович</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
@@ -18973,17 +18967,17 @@
       </c>
       <c r="F184" s="8" t="inlineStr">
         <is>
-          <t>1a99d136-be08-11f0-86a4-3a68dd8b748f</t>
+          <t>172ea39b-3e1f-11f1-a42b-f8f21e64b171</t>
         </is>
       </c>
       <c r="G184" s="8" t="inlineStr">
         <is>
-          <t>1a99d2da-be08-11f0-86a4-3a68dd8b748f</t>
+          <t>172ea5a6-3e1f-11f1-a42b-f8f21e64b171</t>
         </is>
       </c>
       <c r="H184" s="8" t="inlineStr">
         <is>
-          <t>dvtretyakov@magnit.ru</t>
+          <t>skvortcov_v_p@magnit.ru</t>
         </is>
       </c>
       <c r="I184" s="8" t="inlineStr">
@@ -18993,12 +18987,12 @@
       </c>
       <c r="J184" s="8" t="inlineStr">
         <is>
-          <t>Абрамов Иван Андреевич</t>
+          <t>Миронов Максим Владимирович</t>
         </is>
       </c>
       <c r="K184" s="8" t="inlineStr">
         <is>
-          <t>Команда мобильной разработки медийной рекламы</t>
+          <t>Команда разработки оффлайн инвентаря</t>
         </is>
       </c>
       <c r="L184" s="23" t="inlineStr">
@@ -19010,7 +19004,7 @@
         <v>1</v>
       </c>
       <c r="N184" s="23" t="n">
-        <v>56</v>
+        <v>120</v>
       </c>
       <c r="O184" s="8" t="n"/>
       <c r="P184" s="27" t="n"/>
@@ -19027,12 +19021,12 @@
       </c>
       <c r="T184" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: проектирование архитектуры и разработка ядра</t>
+          <t>Бюджет и биллинг рекламодателя в кабинете: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="U184" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-167</t>
+          <t>ADTHPL-146</t>
         </is>
       </c>
       <c r="V184" s="28" t="n">
@@ -19108,7 +19102,7 @@
         <v>1</v>
       </c>
       <c r="N185" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O185" s="8" t="n"/>
       <c r="P185" s="27" t="n"/>
@@ -19125,16 +19119,16 @@
       </c>
       <c r="T185" s="8" t="inlineStr">
         <is>
-          <t>Бюджет и биллинг рекламодателя в кабинете: проектирование архитектуры и разработка ядра</t>
+          <t>Кабинет селлера для самостоятельного запуска продвижения: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="U185" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-146</t>
+          <t>ADTHPL-285</t>
         </is>
       </c>
       <c r="V185" s="28" t="n">
-        <v>46296</v>
+        <v>46314</v>
       </c>
       <c r="W185" s="28" t="n">
         <v>46326</v>
@@ -19154,32 +19148,32 @@
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>CN-0997224</t>
+          <t>CN-0900263</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>Скворцов Виталий Павлович</t>
+          <t>Скороходов Максим Евгеньевич</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>Главный разработчик</t>
+          <t>Руководитель команды</t>
         </is>
       </c>
       <c r="F186" s="8" t="inlineStr">
         <is>
-          <t>172ea39b-3e1f-11f1-a42b-f8f21e64b171</t>
+          <t>62a50f7c-a054-11f0-af3a-f8f21e64d511</t>
         </is>
       </c>
       <c r="G186" s="8" t="inlineStr">
         <is>
-          <t>172ea5a6-3e1f-11f1-a42b-f8f21e64b171</t>
+          <t>68fb165b-a054-11f0-af3a-f8f21e64d511</t>
         </is>
       </c>
       <c r="H186" s="8" t="inlineStr">
         <is>
-          <t>skvortcov_v_p@magnit.ru</t>
+          <t>skorokhodov_me@magnit.ru</t>
         </is>
       </c>
       <c r="I186" s="8" t="inlineStr">
@@ -19189,12 +19183,12 @@
       </c>
       <c r="J186" s="8" t="inlineStr">
         <is>
-          <t>Миронов Максим Владимирович</t>
+          <t>Волков Игорь Игоревич</t>
         </is>
       </c>
       <c r="K186" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки оффлайн инвентаря</t>
+          <t>Отдел разработки партнерской платформы</t>
         </is>
       </c>
       <c r="L186" s="23" t="inlineStr">
@@ -19206,33 +19200,39 @@
         <v>1</v>
       </c>
       <c r="N186" s="23" t="n">
-        <v>56</v>
-      </c>
-      <c r="O186" s="8" t="n"/>
-      <c r="P186" s="27" t="n"/>
-      <c r="Q186" s="27" t="n"/>
+        <v>95</v>
+      </c>
+      <c r="O186" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P186" s="27" t="n">
+        <v>46307</v>
+      </c>
+      <c r="Q186" s="27" t="n">
+        <v>46312</v>
+      </c>
       <c r="R186" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S186" s="8" t="inlineStr">
         <is>
-          <t>Разработка (кодирование) ПО</t>
+          <t>Менеджмент/ Административные задачи</t>
         </is>
       </c>
       <c r="T186" s="8" t="inlineStr">
         <is>
-          <t>Кабинет селлера для самостоятельного запуска продвижения: проектирование архитектуры и разработка ядра</t>
+          <t>Административное управление командой партнерской платформы: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U186" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-285</t>
+          <t>ADTHPL-236</t>
         </is>
       </c>
       <c r="V186" s="28" t="n">
-        <v>46314</v>
+        <v>46296</v>
       </c>
       <c r="W186" s="28" t="n">
         <v>46326</v>
@@ -19460,12 +19460,12 @@
       </c>
       <c r="C189" s="8" t="inlineStr">
         <is>
-          <t>CN-0900263</t>
+          <t>CN-0507019</t>
         </is>
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>Скороходов Максим Евгеньевич</t>
+          <t>Абрамов Иван Андреевич</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
@@ -19475,17 +19475,17 @@
       </c>
       <c r="F189" s="8" t="inlineStr">
         <is>
-          <t>62a50f7c-a054-11f0-af3a-f8f21e64d511</t>
+          <t>d5970aa9-77ed-11ee-ab4d-f8f21e64b171</t>
         </is>
       </c>
       <c r="G189" s="8" t="inlineStr">
         <is>
-          <t>68fb165b-a054-11f0-af3a-f8f21e64d511</t>
+          <t>d5970b29-77ed-11ee-ab4d-f8f21e64b171</t>
         </is>
       </c>
       <c r="H189" s="8" t="inlineStr">
         <is>
-          <t>skorokhodov_me@magnit.ru</t>
+          <t>abramov_ia@magnit.ru</t>
         </is>
       </c>
       <c r="I189" s="8" t="inlineStr">
@@ -19495,12 +19495,12 @@
       </c>
       <c r="J189" s="8" t="inlineStr">
         <is>
-          <t>Волков Игорь Игоревич</t>
+          <t>Чудинов Валерий Иванович</t>
         </is>
       </c>
       <c r="K189" s="8" t="inlineStr">
         <is>
-          <t>Отдел разработки партнерской платформы</t>
+          <t>Отдел разработки медийной рекламы</t>
         </is>
       </c>
       <c r="L189" s="23" t="inlineStr">
@@ -19512,17 +19512,11 @@
         <v>1</v>
       </c>
       <c r="N189" s="23" t="n">
-        <v>95</v>
-      </c>
-      <c r="O189" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="P189" s="27" t="n">
-        <v>46307</v>
-      </c>
-      <c r="Q189" s="27" t="n">
-        <v>46312</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="O189" s="8" t="n"/>
+      <c r="P189" s="27" t="n"/>
+      <c r="Q189" s="27" t="n"/>
       <c r="R189" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -19535,12 +19529,12 @@
       </c>
       <c r="T189" s="8" t="inlineStr">
         <is>
-          <t>Административное управление командой партнерской платформы: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Участие в найме и онбординге сотрудников платформы (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U189" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-236</t>
+          <t>ADTHPL-245</t>
         </is>
       </c>
       <c r="V189" s="28" t="n">
@@ -19760,32 +19754,32 @@
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>CN-0507019</t>
+          <t>CN-0944891</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>Абрамов Иван Андреевич</t>
+          <t>Рандин Никита Андреевич</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>Руководитель команды</t>
+          <t>Главный разработчик</t>
         </is>
       </c>
       <c r="F192" s="8" t="inlineStr">
         <is>
-          <t>d5970aa9-77ed-11ee-ab4d-f8f21e64b171</t>
+          <t>fa794222-dffc-11f0-93e0-c4cbe1a36811</t>
         </is>
       </c>
       <c r="G192" s="8" t="inlineStr">
         <is>
-          <t>d5970b29-77ed-11ee-ab4d-f8f21e64b171</t>
+          <t>00fe5f23-dffd-11f0-93e0-c4cbe1a36811</t>
         </is>
       </c>
       <c r="H192" s="8" t="inlineStr">
         <is>
-          <t>abramov_ia@magnit.ru</t>
+          <t>randin_na@magnit.ru</t>
         </is>
       </c>
       <c r="I192" s="8" t="inlineStr">
@@ -19812,29 +19806,29 @@
         <v>1</v>
       </c>
       <c r="N192" s="23" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O192" s="8" t="n"/>
       <c r="P192" s="27" t="n"/>
       <c r="Q192" s="27" t="n"/>
       <c r="R192" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S192" s="8" t="inlineStr">
         <is>
-          <t>Менеджмент/ Административные задачи</t>
+          <t>Разработка (кодирование) ПО</t>
         </is>
       </c>
       <c r="T192" s="8" t="inlineStr">
         <is>
-          <t>Участие в найме и онбординге сотрудников платформы (4 кв. 2026)</t>
+          <t>Прогноз кликабельности для ранжирования ставок: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="U192" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-245</t>
+          <t>ADTHPL-167</t>
         </is>
       </c>
       <c r="V192" s="28" t="n">
@@ -19910,7 +19904,7 @@
         <v>1</v>
       </c>
       <c r="N193" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O193" s="8" t="n"/>
       <c r="P193" s="27" t="n"/>
@@ -19927,12 +19921,12 @@
       </c>
       <c r="T193" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: проектирование архитектуры и разработка ядра</t>
+          <t>Прогноз кликабельности для ранжирования ставок: разработка серверной части и API</t>
         </is>
       </c>
       <c r="U193" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-167</t>
+          <t>ADTHPL-168</t>
         </is>
       </c>
       <c r="V193" s="28" t="n">
@@ -19956,12 +19950,12 @@
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>CN-0944891</t>
+          <t>CN-0890704</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>Рандин Никита Андреевич</t>
+          <t>Соловьев Константин Валерьевич</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
@@ -19971,17 +19965,17 @@
       </c>
       <c r="F194" s="8" t="inlineStr">
         <is>
-          <t>fa794222-dffc-11f0-93e0-c4cbe1a36811</t>
+          <t>d6137c81-9457-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G194" s="8" t="inlineStr">
         <is>
-          <t>00fe5f23-dffd-11f0-93e0-c4cbe1a36811</t>
+          <t>dc0be8ca-9457-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H194" s="8" t="inlineStr">
         <is>
-          <t>randin_na@magnit.ru</t>
+          <t>solovev_k_v@magnit.ru</t>
         </is>
       </c>
       <c r="I194" s="8" t="inlineStr">
@@ -19991,12 +19985,12 @@
       </c>
       <c r="J194" s="8" t="inlineStr">
         <is>
-          <t>Чудинов Валерий Иванович</t>
+          <t>Ермолаев Максим Михайлович</t>
         </is>
       </c>
       <c r="K194" s="8" t="inlineStr">
         <is>
-          <t>Отдел разработки медийной рекламы</t>
+          <t>Команда разработки рекламной платформы</t>
         </is>
       </c>
       <c r="L194" s="23" t="inlineStr">
@@ -20008,11 +20002,17 @@
         <v>1</v>
       </c>
       <c r="N194" s="23" t="n">
-        <v>56</v>
-      </c>
-      <c r="O194" s="8" t="n"/>
-      <c r="P194" s="27" t="n"/>
-      <c r="Q194" s="27" t="n"/>
+        <v>96</v>
+      </c>
+      <c r="O194" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P194" s="27" t="n">
+        <v>46321</v>
+      </c>
+      <c r="Q194" s="27" t="n">
+        <v>46325</v>
+      </c>
       <c r="R194" s="8" t="inlineStr">
         <is>
           <t>CAPEX</t>
@@ -20025,19 +20025,19 @@
       </c>
       <c r="T194" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: разработка серверной части и API</t>
+          <t>Кабинет партнера: ссылки, промокоды, статистика: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="U194" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-168</t>
+          <t>ADTHPL-142</t>
         </is>
       </c>
       <c r="V194" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W194" s="28" t="n">
-        <v>46326</v>
+        <v>46318</v>
       </c>
       <c r="X194" s="8" t="n"/>
     </row>
@@ -20106,7 +20106,7 @@
         <v>1</v>
       </c>
       <c r="N195" s="23" t="n">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="O195" s="8" t="n">
         <v>5</v>
@@ -20129,16 +20129,16 @@
       </c>
       <c r="T195" s="8" t="inlineStr">
         <is>
-          <t>Кабинет партнера: ссылки, промокоды, статистика: проектирование архитектуры и разработка ядра</t>
+          <t>Кабинет селлера для самостоятельного запуска продвижения: разработка серверной части и API</t>
         </is>
       </c>
       <c r="U195" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-142</t>
+          <t>ADTHPL-286</t>
         </is>
       </c>
       <c r="V195" s="28" t="n">
-        <v>46296</v>
+        <v>46314</v>
       </c>
       <c r="W195" s="28" t="n">
         <v>46318</v>
@@ -20158,32 +20158,32 @@
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>CN-0890704</t>
+          <t>CN-0578690</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>Соловьев Константин Валерьевич</t>
+          <t>Алтухов Руслан Дмитриевич</t>
         </is>
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>Главный разработчик</t>
+          <t>Руководитель команды</t>
         </is>
       </c>
       <c r="F196" s="8" t="inlineStr">
         <is>
-          <t>d6137c81-9457-11f0-86a4-3a68dd8b748f</t>
+          <t>d2f4e8e2-d7c8-11ee-ab43-e4434b7b9424</t>
         </is>
       </c>
       <c r="G196" s="8" t="inlineStr">
         <is>
-          <t>dc0be8ca-9457-11f0-86a4-3a68dd8b748f</t>
+          <t>d2f4e9df-d7c8-11ee-ab43-e4434b7b9424</t>
         </is>
       </c>
       <c r="H196" s="8" t="inlineStr">
         <is>
-          <t>solovev_k_v@magnit.ru</t>
+          <t>altukhov_rd@magnit.ru</t>
         </is>
       </c>
       <c r="I196" s="8" t="inlineStr">
@@ -20193,12 +20193,12 @@
       </c>
       <c r="J196" s="8" t="inlineStr">
         <is>
-          <t>Ермолаев Максим Михайлович</t>
+          <t>Буров Глеб Олегович</t>
         </is>
       </c>
       <c r="K196" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки рекламной платформы</t>
+          <t>Управление разработки Эдтех</t>
         </is>
       </c>
       <c r="L196" s="23" t="inlineStr">
@@ -20210,42 +20210,36 @@
         <v>1</v>
       </c>
       <c r="N196" s="23" t="n">
-        <v>40</v>
-      </c>
-      <c r="O196" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="P196" s="27" t="n">
-        <v>46321</v>
-      </c>
-      <c r="Q196" s="27" t="n">
-        <v>46325</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="O196" s="8" t="n"/>
+      <c r="P196" s="27" t="n"/>
+      <c r="Q196" s="27" t="n"/>
       <c r="R196" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S196" s="8" t="inlineStr">
         <is>
-          <t>Разработка (кодирование) ПО</t>
+          <t>Менеджмент/ Административные задачи</t>
         </is>
       </c>
       <c r="T196" s="8" t="inlineStr">
         <is>
-          <t>Кабинет селлера для самостоятельного запуска продвижения: разработка серверной части и API</t>
+          <t>Административное управление командой рекламного кабинета: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U196" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-286</t>
+          <t>ADTHPL-230</t>
         </is>
       </c>
       <c r="V196" s="28" t="n">
-        <v>46314</v>
+        <v>46296</v>
       </c>
       <c r="W196" s="28" t="n">
-        <v>46318</v>
+        <v>46326</v>
       </c>
       <c r="X196" s="8" t="n"/>
     </row>
@@ -20458,32 +20452,32 @@
       </c>
       <c r="C199" s="8" t="inlineStr">
         <is>
-          <t>CN-0578690</t>
+          <t>CN-0937481</t>
         </is>
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>Алтухов Руслан Дмитриевич</t>
+          <t>Суринова Александра Валерьевна</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>Руководитель команды</t>
+          <t>Ведущий специалист по тестированию</t>
         </is>
       </c>
       <c r="F199" s="8" t="inlineStr">
         <is>
-          <t>d2f4e8e2-d7c8-11ee-ab43-e4434b7b9424</t>
+          <t>6a03edf2-d43d-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G199" s="8" t="inlineStr">
         <is>
-          <t>d2f4e9df-d7c8-11ee-ab43-e4434b7b9424</t>
+          <t>7005cac4-d43d-11f0-86a4-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H199" s="8" t="inlineStr">
         <is>
-          <t>altukhov_rd@magnit.ru</t>
+          <t>surinova_av@magnit.ru</t>
         </is>
       </c>
       <c r="I199" s="8" t="inlineStr">
@@ -20493,12 +20487,12 @@
       </c>
       <c r="J199" s="8" t="inlineStr">
         <is>
-          <t>Буров Глеб Олегович</t>
+          <t>Абрамов Иван Андреевич</t>
         </is>
       </c>
       <c r="K199" s="8" t="inlineStr">
         <is>
-          <t>Управление разработки Эдтех</t>
+          <t>Команда мобильной разработки медийной рекламы</t>
         </is>
       </c>
       <c r="L199" s="23" t="inlineStr">
@@ -20510,33 +20504,39 @@
         <v>1</v>
       </c>
       <c r="N199" s="23" t="n">
-        <v>123</v>
-      </c>
-      <c r="O199" s="8" t="n"/>
-      <c r="P199" s="27" t="n"/>
-      <c r="Q199" s="27" t="n"/>
+        <v>88</v>
+      </c>
+      <c r="O199" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P199" s="27" t="n">
+        <v>46296</v>
+      </c>
+      <c r="Q199" s="27" t="n">
+        <v>46304</v>
+      </c>
       <c r="R199" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S199" s="8" t="inlineStr">
         <is>
-          <t>Менеджмент/ Административные задачи</t>
+          <t>Тестирование ПО</t>
         </is>
       </c>
       <c r="T199" s="8" t="inlineStr">
         <is>
-          <t>Административное управление командой рекламного кабинета: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Мастер создания кампании в рекламном кабинете: функциональное и интеграционное тестирование</t>
         </is>
       </c>
       <c r="U199" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-230</t>
+          <t>ADTHPL-265</t>
         </is>
       </c>
       <c r="V199" s="28" t="n">
-        <v>46296</v>
+        <v>46307</v>
       </c>
       <c r="W199" s="28" t="n">
         <v>46326</v>
@@ -20608,7 +20608,7 @@
         <v>1</v>
       </c>
       <c r="N200" s="23" t="n">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="O200" s="8" t="n">
         <v>7</v>
@@ -20631,12 +20631,12 @@
       </c>
       <c r="T200" s="8" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: функциональное и интеграционное тестирование</t>
+          <t>Мастер создания кампании в рекламном кабинете: тестирование отказоустойчивости</t>
         </is>
       </c>
       <c r="U200" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-265</t>
+          <t>ADTHPL-266</t>
         </is>
       </c>
       <c r="V200" s="28" t="n">
@@ -20660,32 +20660,32 @@
       </c>
       <c r="C201" s="8" t="inlineStr">
         <is>
-          <t>CN-0937481</t>
+          <t>CN-0883770</t>
         </is>
       </c>
       <c r="D201" s="8" t="inlineStr">
         <is>
-          <t>Суринова Александра Валерьевна</t>
+          <t>Шалымов Роман Сергеевич</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>Ведущий специалист по тестированию</t>
+          <t>Главный разработчик</t>
         </is>
       </c>
       <c r="F201" s="8" t="inlineStr">
         <is>
-          <t>6a03edf2-d43d-11f0-86a4-3a68dd8b748f</t>
+          <t>76c1a927-8a57-11f0-af3a-f8f21e64d511</t>
         </is>
       </c>
       <c r="G201" s="8" t="inlineStr">
         <is>
-          <t>7005cac4-d43d-11f0-86a4-3a68dd8b748f</t>
+          <t>7cdc8d47-8a57-11f0-af3a-f8f21e64d511</t>
         </is>
       </c>
       <c r="H201" s="8" t="inlineStr">
         <is>
-          <t>surinova_av@magnit.ru</t>
+          <t>shalymov_rs@magnit.ru</t>
         </is>
       </c>
       <c r="I201" s="8" t="inlineStr">
@@ -20695,12 +20695,12 @@
       </c>
       <c r="J201" s="8" t="inlineStr">
         <is>
-          <t>Абрамов Иван Андреевич</t>
+          <t>Карпов Дмитрий Владимирович</t>
         </is>
       </c>
       <c r="K201" s="8" t="inlineStr">
         <is>
-          <t>Команда мобильной разработки медийной рекламы</t>
+          <t>Команда разработки инструментов повышения эффективности монетизации</t>
         </is>
       </c>
       <c r="L201" s="23" t="inlineStr">
@@ -20712,39 +20712,33 @@
         <v>1</v>
       </c>
       <c r="N201" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="O201" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="P201" s="27" t="n">
+        <v>120</v>
+      </c>
+      <c r="O201" s="8" t="n"/>
+      <c r="P201" s="27" t="n"/>
+      <c r="Q201" s="27" t="n"/>
+      <c r="R201" s="8" t="inlineStr">
+        <is>
+          <t>CAPEX</t>
+        </is>
+      </c>
+      <c r="S201" s="8" t="inlineStr">
+        <is>
+          <t>Разработка (кодирование) ПО</t>
+        </is>
+      </c>
+      <c r="T201" s="8" t="inlineStr">
+        <is>
+          <t>Мастер создания кампании в рекламном кабинете: разработка серверной части и API</t>
+        </is>
+      </c>
+      <c r="U201" s="8" t="inlineStr">
+        <is>
+          <t>ADTHPL-176</t>
+        </is>
+      </c>
+      <c r="V201" s="28" t="n">
         <v>46296</v>
-      </c>
-      <c r="Q201" s="27" t="n">
-        <v>46304</v>
-      </c>
-      <c r="R201" s="8" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="S201" s="8" t="inlineStr">
-        <is>
-          <t>Тестирование ПО</t>
-        </is>
-      </c>
-      <c r="T201" s="8" t="inlineStr">
-        <is>
-          <t>Мастер создания кампании в рекламном кабинете: тестирование отказоустойчивости</t>
-        </is>
-      </c>
-      <c r="U201" s="8" t="inlineStr">
-        <is>
-          <t>ADTHPL-266</t>
-        </is>
-      </c>
-      <c r="V201" s="28" t="n">
-        <v>46307</v>
       </c>
       <c r="W201" s="28" t="n">
         <v>46326</v>
@@ -20816,7 +20810,7 @@
         <v>1</v>
       </c>
       <c r="N202" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O202" s="8" t="n"/>
       <c r="P202" s="27" t="n"/>
@@ -20833,12 +20827,12 @@
       </c>
       <c r="T202" s="8" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: разработка серверной части и API</t>
+          <t>Мастер создания кампании в рекламном кабинете: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="U202" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-176</t>
+          <t>ADTHPL-175</t>
         </is>
       </c>
       <c r="V202" s="28" t="n">
@@ -20862,32 +20856,32 @@
       </c>
       <c r="C203" s="8" t="inlineStr">
         <is>
-          <t>CN-0883770</t>
+          <t>CN-0860810</t>
         </is>
       </c>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t>Шалымов Роман Сергеевич</t>
+          <t>Ермолаев Максим Михайлович</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>Главный разработчик</t>
+          <t>Руководитель команды</t>
         </is>
       </c>
       <c r="F203" s="8" t="inlineStr">
         <is>
-          <t>76c1a927-8a57-11f0-af3a-f8f21e64d511</t>
+          <t>fdfaaacd-6c76-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G203" s="8" t="inlineStr">
         <is>
-          <t>7cdc8d47-8a57-11f0-af3a-f8f21e64d511</t>
+          <t>03f75286-6c77-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H203" s="8" t="inlineStr">
         <is>
-          <t>shalymov_rs@magnit.ru</t>
+          <t>ermolaev_mm@magnit.ru</t>
         </is>
       </c>
       <c r="I203" s="8" t="inlineStr">
@@ -20897,12 +20891,12 @@
       </c>
       <c r="J203" s="8" t="inlineStr">
         <is>
-          <t>Карпов Дмитрий Владимирович</t>
+          <t>Буров Глеб Олегович</t>
         </is>
       </c>
       <c r="K203" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки инструментов повышения эффективности монетизации</t>
+          <t>Управление разработки Эдтех</t>
         </is>
       </c>
       <c r="L203" s="23" t="inlineStr">
@@ -20914,29 +20908,29 @@
         <v>1</v>
       </c>
       <c r="N203" s="23" t="n">
-        <v>56</v>
+        <v>123</v>
       </c>
       <c r="O203" s="8" t="n"/>
       <c r="P203" s="27" t="n"/>
       <c r="Q203" s="27" t="n"/>
       <c r="R203" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S203" s="8" t="inlineStr">
         <is>
-          <t>Разработка (кодирование) ПО</t>
+          <t>Менеджмент/ Административные задачи</t>
         </is>
       </c>
       <c r="T203" s="8" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: проектирование архитектуры и разработка ядра</t>
+          <t>Административное управление командой партнерской платформы: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U203" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-175</t>
+          <t>ADTHPL-236</t>
         </is>
       </c>
       <c r="V203" s="28" t="n">
@@ -21156,12 +21150,12 @@
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>CN-0860810</t>
+          <t>CN-0842637</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>Ермолаев Максим Михайлович</t>
+          <t>Авилов Александр Андреевич</t>
         </is>
       </c>
       <c r="E206" s="8" t="inlineStr">
@@ -21171,17 +21165,17 @@
       </c>
       <c r="F206" s="8" t="inlineStr">
         <is>
-          <t>fdfaaacd-6c76-11f0-86a3-3a68dd8b748f</t>
+          <t>7eadfca8-5815-11f0-ab50-f8f21e64b170</t>
         </is>
       </c>
       <c r="G206" s="8" t="inlineStr">
         <is>
-          <t>03f75286-6c77-11f0-86a3-3a68dd8b748f</t>
+          <t>7eadfd82-5815-11f0-ab50-f8f21e64b170</t>
         </is>
       </c>
       <c r="H206" s="8" t="inlineStr">
         <is>
-          <t>ermolaev_mm@magnit.ru</t>
+          <t>avilov_aa@magnit.ru</t>
         </is>
       </c>
       <c r="I206" s="8" t="inlineStr">
@@ -21225,12 +21219,12 @@
       </c>
       <c r="T206" s="8" t="inlineStr">
         <is>
-          <t>Административное управление командой партнерской платформы: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Административное управление командой показа рекламы: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U206" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-236</t>
+          <t>ADTHPL-224</t>
         </is>
       </c>
       <c r="V206" s="28" t="n">
@@ -21450,32 +21444,32 @@
       </c>
       <c r="C209" s="8" t="inlineStr">
         <is>
-          <t>CN-0842637</t>
+          <t>CN-0996426</t>
         </is>
       </c>
       <c r="D209" s="8" t="inlineStr">
         <is>
-          <t>Авилов Александр Андреевич</t>
+          <t>Ельниковский Василий Владиславович</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>Руководитель команды</t>
+          <t>Главный разработчик</t>
         </is>
       </c>
       <c r="F209" s="8" t="inlineStr">
         <is>
-          <t>7eadfca8-5815-11f0-ab50-f8f21e64b170</t>
+          <t>62fd89bc-3cba-11f1-93e3-c4cbe1a36811</t>
         </is>
       </c>
       <c r="G209" s="8" t="inlineStr">
         <is>
-          <t>7eadfd82-5815-11f0-ab50-f8f21e64b170</t>
+          <t>22089387-3cbb-11f1-93e3-c4cbe1a36811</t>
         </is>
       </c>
       <c r="H209" s="8" t="inlineStr">
         <is>
-          <t>avilov_aa@magnit.ru</t>
+          <t>elnikovskiy_vv@magnit.ru</t>
         </is>
       </c>
       <c r="I209" s="8" t="inlineStr">
@@ -21485,12 +21479,12 @@
       </c>
       <c r="J209" s="8" t="inlineStr">
         <is>
-          <t>Буров Глеб Олегович</t>
+          <t>Миронов Максим Владимирович</t>
         </is>
       </c>
       <c r="K209" s="8" t="inlineStr">
         <is>
-          <t>Управление разработки Эдтех</t>
+          <t>Команда разработки оффлайн инвентаря</t>
         </is>
       </c>
       <c r="L209" s="23" t="inlineStr">
@@ -21502,29 +21496,29 @@
         <v>1</v>
       </c>
       <c r="N209" s="23" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O209" s="8" t="n"/>
       <c r="P209" s="27" t="n"/>
       <c r="Q209" s="27" t="n"/>
       <c r="R209" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S209" s="8" t="inlineStr">
         <is>
-          <t>Менеджмент/ Административные задачи</t>
+          <t>Разработка (кодирование) ПО</t>
         </is>
       </c>
       <c r="T209" s="8" t="inlineStr">
         <is>
-          <t>Административное управление командой показа рекламы: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Мастер создания кампании в рекламном кабинете: проектирование архитектуры и разработка ядра</t>
         </is>
       </c>
       <c r="U209" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-224</t>
+          <t>ADTHPL-175</t>
         </is>
       </c>
       <c r="V209" s="28" t="n">
@@ -21600,7 +21594,7 @@
         <v>1</v>
       </c>
       <c r="N210" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O210" s="8" t="n"/>
       <c r="P210" s="27" t="n"/>
@@ -21617,12 +21611,12 @@
       </c>
       <c r="T210" s="8" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: проектирование архитектуры и разработка ядра</t>
+          <t>Мастер создания кампании в рекламном кабинете: разработка пользовательского интерфейса</t>
         </is>
       </c>
       <c r="U210" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-175</t>
+          <t>ADTHPL-177</t>
         </is>
       </c>
       <c r="V210" s="28" t="n">
@@ -21646,32 +21640,32 @@
       </c>
       <c r="C211" s="8" t="inlineStr">
         <is>
-          <t>CN-0996426</t>
+          <t>CN-0336988</t>
         </is>
       </c>
       <c r="D211" s="8" t="inlineStr">
         <is>
-          <t>Ельниковский Василий Владиславович</t>
+          <t>Харагезов Аркадий Иванович</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>Главный разработчик</t>
+          <t>Инженер сопровождения</t>
         </is>
       </c>
       <c r="F211" s="8" t="inlineStr">
         <is>
-          <t>62fd89bc-3cba-11f1-93e3-c4cbe1a36811</t>
+          <t>7910d25a-8515-11ed-ab41-e4434b7b9424</t>
         </is>
       </c>
       <c r="G211" s="8" t="inlineStr">
         <is>
-          <t>22089387-3cbb-11f1-93e3-c4cbe1a36811</t>
+          <t>7910d2ff-8515-11ed-ab41-e4434b7b9424</t>
         </is>
       </c>
       <c r="H211" s="8" t="inlineStr">
         <is>
-          <t>elnikovskiy_vv@magnit.ru</t>
+          <t>kharagezov_ai@magnit.ru</t>
         </is>
       </c>
       <c r="I211" s="8" t="inlineStr">
@@ -21681,12 +21675,12 @@
       </c>
       <c r="J211" s="8" t="inlineStr">
         <is>
-          <t>Миронов Максим Владимирович</t>
+          <t>Науменко Андрей Викторович</t>
         </is>
       </c>
       <c r="K211" s="8" t="inlineStr">
         <is>
-          <t>Команда разработки оффлайн инвентаря</t>
+          <t>Команда развития медиаконтента</t>
         </is>
       </c>
       <c r="L211" s="23" t="inlineStr">
@@ -21698,14 +21692,20 @@
         <v>1</v>
       </c>
       <c r="N211" s="23" t="n">
-        <v>56</v>
-      </c>
-      <c r="O211" s="8" t="n"/>
-      <c r="P211" s="27" t="n"/>
-      <c r="Q211" s="27" t="n"/>
+        <v>136</v>
+      </c>
+      <c r="O211" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P211" s="27" t="n">
+        <v>46321</v>
+      </c>
+      <c r="Q211" s="27" t="n">
+        <v>46325</v>
+      </c>
       <c r="R211" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S211" s="8" t="inlineStr">
@@ -21715,19 +21715,19 @@
       </c>
       <c r="T211" s="8" t="inlineStr">
         <is>
-          <t>Мастер создания кампании в рекламном кабинете: разработка пользовательского интерфейса</t>
+          <t>Сопровождение промышленной эксплуатации партнерской платформы: мониторинг, инциденты, обновления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U211" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-177</t>
+          <t>ADTHPL-235</t>
         </is>
       </c>
       <c r="V211" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W211" s="28" t="n">
-        <v>46326</v>
+        <v>46318</v>
       </c>
       <c r="X211" s="8" t="n"/>
     </row>
@@ -21744,32 +21744,32 @@
       </c>
       <c r="C212" s="8" t="inlineStr">
         <is>
-          <t>CN-0336988</t>
+          <t>CN-0987163</t>
         </is>
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>Харагезов Аркадий Иванович</t>
+          <t>Миронов Максим Владимирович</t>
         </is>
       </c>
       <c r="E212" s="8" t="inlineStr">
         <is>
-          <t>Инженер сопровождения</t>
+          <t>Руководитель команды</t>
         </is>
       </c>
       <c r="F212" s="8" t="inlineStr">
         <is>
-          <t>7910d25a-8515-11ed-ab41-e4434b7b9424</t>
+          <t>cc3965ca-2d08-11f1-93e2-c4cbe1a36811</t>
         </is>
       </c>
       <c r="G212" s="8" t="inlineStr">
         <is>
-          <t>7910d2ff-8515-11ed-ab41-e4434b7b9424</t>
+          <t>cc39667f-2d08-11f1-93e2-c4cbe1a36811</t>
         </is>
       </c>
       <c r="H212" s="8" t="inlineStr">
         <is>
-          <t>kharagezov_ai@magnit.ru</t>
+          <t>mironovmv@magnit.ru</t>
         </is>
       </c>
       <c r="I212" s="8" t="inlineStr">
@@ -21779,12 +21779,12 @@
       </c>
       <c r="J212" s="8" t="inlineStr">
         <is>
-          <t>Науменко Андрей Викторович</t>
+          <t>Буров Глеб Олегович</t>
         </is>
       </c>
       <c r="K212" s="8" t="inlineStr">
         <is>
-          <t>Команда развития медиаконтента</t>
+          <t>Управление разработки Эдтех</t>
         </is>
       </c>
       <c r="L212" s="23" t="inlineStr">
@@ -21796,17 +21796,11 @@
         <v>1</v>
       </c>
       <c r="N212" s="23" t="n">
-        <v>136</v>
-      </c>
-      <c r="O212" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="P212" s="27" t="n">
-        <v>46321</v>
-      </c>
-      <c r="Q212" s="27" t="n">
-        <v>46325</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="O212" s="8" t="n"/>
+      <c r="P212" s="27" t="n"/>
+      <c r="Q212" s="27" t="n"/>
       <c r="R212" s="8" t="inlineStr">
         <is>
           <t>OPEX</t>
@@ -21814,24 +21808,24 @@
       </c>
       <c r="S212" s="8" t="inlineStr">
         <is>
-          <t>Разработка (кодирование) ПО</t>
+          <t>Менеджмент/ Административные задачи</t>
         </is>
       </c>
       <c r="T212" s="8" t="inlineStr">
         <is>
-          <t>Сопровождение промышленной эксплуатации партнерской платформы: мониторинг, инциденты, обновления (4 кв. 2026)</t>
+          <t>Административное управление командой показа рекламы: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U212" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-235</t>
+          <t>ADTHPL-224</t>
         </is>
       </c>
       <c r="V212" s="28" t="n">
         <v>46296</v>
       </c>
       <c r="W212" s="28" t="n">
-        <v>46318</v>
+        <v>46326</v>
       </c>
       <c r="X212" s="8" t="n"/>
     </row>
@@ -22044,32 +22038,32 @@
       </c>
       <c r="C215" s="8" t="inlineStr">
         <is>
-          <t>CN-0987163</t>
+          <t>CN-0853693</t>
         </is>
       </c>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t>Миронов Максим Владимирович</t>
+          <t>Чудинов Валерий Иванович</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>Руководитель команды</t>
+          <t>Начальник отдела</t>
         </is>
       </c>
       <c r="F215" s="8" t="inlineStr">
         <is>
-          <t>cc3965ca-2d08-11f1-93e2-c4cbe1a36811</t>
+          <t>09dc8a87-6304-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G215" s="8" t="inlineStr">
         <is>
-          <t>cc39667f-2d08-11f1-93e2-c4cbe1a36811</t>
+          <t>0feb9cbf-6304-11f0-86a3-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H215" s="8" t="inlineStr">
         <is>
-          <t>mironovmv@magnit.ru</t>
+          <t>chudinov_vi@magnit.ru</t>
         </is>
       </c>
       <c r="I215" s="8" t="inlineStr">
@@ -22096,7 +22090,7 @@
         <v>1</v>
       </c>
       <c r="N215" s="23" t="n">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="O215" s="8" t="n"/>
       <c r="P215" s="27" t="n"/>
@@ -22292,29 +22286,29 @@
         <v>1</v>
       </c>
       <c r="N217" s="23" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O217" s="8" t="n"/>
       <c r="P217" s="27" t="n"/>
       <c r="Q217" s="27" t="n"/>
       <c r="R217" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S217" s="8" t="inlineStr">
         <is>
-          <t>Разработка (кодирование) ПО</t>
+          <t>Менеджмент/ Административные задачи</t>
         </is>
       </c>
       <c r="T217" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: техническое руководство разработкой и код-ревью</t>
+          <t>Административное управление командой интеграции с ОРД: планирование, найм, оценка (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U217" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-170</t>
+          <t>ADTHPL-238</t>
         </is>
       </c>
       <c r="V217" s="28" t="n">
@@ -22390,29 +22384,29 @@
         <v>1</v>
       </c>
       <c r="N218" s="23" t="n">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="O218" s="8" t="n"/>
       <c r="P218" s="27" t="n"/>
       <c r="Q218" s="27" t="n"/>
       <c r="R218" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S218" s="8" t="inlineStr">
         <is>
-          <t>Менеджмент/ Административные задачи</t>
+          <t>Разработка (кодирование) ПО</t>
         </is>
       </c>
       <c r="T218" s="8" t="inlineStr">
         <is>
-          <t>Административное управление командой показа рекламы: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Прогноз кликабельности для ранжирования ставок: техническое руководство разработкой и код-ревью</t>
         </is>
       </c>
       <c r="U218" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-224</t>
+          <t>ADTHPL-170</t>
         </is>
       </c>
       <c r="V218" s="28" t="n">
@@ -22436,32 +22430,32 @@
       </c>
       <c r="C219" s="8" t="inlineStr">
         <is>
-          <t>CN-0853693</t>
+          <t>CN-1015209</t>
         </is>
       </c>
       <c r="D219" s="8" t="inlineStr">
         <is>
-          <t>Чудинов Валерий Иванович</t>
+          <t>Шаламов Павел Александрович</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>Начальник отдела</t>
+          <t>Ведущий специалист по тестированию</t>
         </is>
       </c>
       <c r="F219" s="8" t="inlineStr">
         <is>
-          <t>09dc8a87-6304-11f0-86a3-3a68dd8b748f</t>
+          <t>a233f15d-5f1e-11f1-86a5-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G219" s="8" t="inlineStr">
         <is>
-          <t>0feb9cbf-6304-11f0-86a3-3a68dd8b748f</t>
+          <t>32e4c6dd-5f1f-11f1-86a5-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H219" s="8" t="inlineStr">
         <is>
-          <t>chudinov_vi@magnit.ru</t>
+          <t>shalamov_pa@magnit.ru</t>
         </is>
       </c>
       <c r="I219" s="8" t="inlineStr">
@@ -22471,12 +22465,12 @@
       </c>
       <c r="J219" s="8" t="inlineStr">
         <is>
-          <t>Буров Глеб Олегович</t>
+          <t>Абрамов Иван Андреевич</t>
         </is>
       </c>
       <c r="K219" s="8" t="inlineStr">
         <is>
-          <t>Управление разработки Эдтех</t>
+          <t>Команда мобильной разработки медийной рекламы</t>
         </is>
       </c>
       <c r="L219" s="23" t="inlineStr">
@@ -22488,33 +22482,39 @@
         <v>1</v>
       </c>
       <c r="N219" s="23" t="n">
-        <v>19</v>
-      </c>
-      <c r="O219" s="8" t="n"/>
-      <c r="P219" s="27" t="n"/>
-      <c r="Q219" s="27" t="n"/>
+        <v>96</v>
+      </c>
+      <c r="O219" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P219" s="27" t="n">
+        <v>46307</v>
+      </c>
+      <c r="Q219" s="27" t="n">
+        <v>46313</v>
+      </c>
       <c r="R219" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S219" s="8" t="inlineStr">
         <is>
-          <t>Менеджмент/ Административные задачи</t>
+          <t>Тестирование ПО</t>
         </is>
       </c>
       <c r="T219" s="8" t="inlineStr">
         <is>
-          <t>Административное управление командой интеграции с ОРД: планирование, найм, оценка (4 кв. 2026)</t>
+          <t>Бюджет и биллинг рекламодателя в кабинете: функциональное и интеграционное тестирование</t>
         </is>
       </c>
       <c r="U219" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-238</t>
+          <t>ADTHPL-254</t>
         </is>
       </c>
       <c r="V219" s="28" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="W219" s="28" t="n">
         <v>46326</v>
@@ -22586,7 +22586,7 @@
         <v>1</v>
       </c>
       <c r="N220" s="23" t="n">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="O220" s="8" t="n">
         <v>5</v>
@@ -22609,16 +22609,16 @@
       </c>
       <c r="T220" s="8" t="inlineStr">
         <is>
-          <t>Бюджет и биллинг рекламодателя в кабинете: функциональное и интеграционное тестирование</t>
+          <t>Кабинет партнера: ссылки, промокоды, статистика: автоматизация регрессионных тестов</t>
         </is>
       </c>
       <c r="U220" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-254</t>
+          <t>ADTHPL-219</t>
         </is>
       </c>
       <c r="V220" s="28" t="n">
-        <v>46300</v>
+        <v>46296</v>
       </c>
       <c r="W220" s="28" t="n">
         <v>46326</v>
@@ -22638,32 +22638,32 @@
       </c>
       <c r="C221" s="8" t="inlineStr">
         <is>
-          <t>CN-1015209</t>
+          <t>CN-0825875</t>
         </is>
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>Шаламов Павел Александрович</t>
+          <t>Буров Глеб Олегович</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>Ведущий специалист по тестированию</t>
+          <t>Руководитель управления</t>
         </is>
       </c>
       <c r="F221" s="8" t="inlineStr">
         <is>
-          <t>a233f15d-5f1e-11f1-86a5-3a68dd8b748f</t>
+          <t>f20707a3-448c-11f0-ab45-e4434b7b9424</t>
         </is>
       </c>
       <c r="G221" s="8" t="inlineStr">
         <is>
-          <t>32e4c6dd-5f1f-11f1-86a5-3a68dd8b748f</t>
+          <t>f2070813-448c-11f0-ab45-e4434b7b9424</t>
         </is>
       </c>
       <c r="H221" s="8" t="inlineStr">
         <is>
-          <t>shalamov_pa@magnit.ru</t>
+          <t>burov_go@magnit.ru</t>
         </is>
       </c>
       <c r="I221" s="8" t="inlineStr">
@@ -22673,12 +22673,12 @@
       </c>
       <c r="J221" s="8" t="inlineStr">
         <is>
-          <t>Абрамов Иван Андреевич</t>
+          <t>Сачков Антон Константинович</t>
         </is>
       </c>
       <c r="K221" s="8" t="inlineStr">
         <is>
-          <t>Команда мобильной разработки медийной рекламы</t>
+          <t>Департамент по развитию и разработке онлайн платформ</t>
         </is>
       </c>
       <c r="L221" s="23" t="inlineStr">
@@ -22690,35 +22690,29 @@
         <v>1</v>
       </c>
       <c r="N221" s="23" t="n">
-        <v>40</v>
-      </c>
-      <c r="O221" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="P221" s="27" t="n">
-        <v>46307</v>
-      </c>
-      <c r="Q221" s="27" t="n">
-        <v>46313</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="O221" s="8" t="n"/>
+      <c r="P221" s="27" t="n"/>
+      <c r="Q221" s="27" t="n"/>
       <c r="R221" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S221" s="8" t="inlineStr">
         <is>
-          <t>Тестирование ПО</t>
+          <t>Менеджмент/ Административные задачи</t>
         </is>
       </c>
       <c r="T221" s="8" t="inlineStr">
         <is>
-          <t>Кабинет партнера: ссылки, промокоды, статистика: автоматизация регрессионных тестов</t>
+          <t>Управление портфелем разработки и бюджетом управления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U221" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-219</t>
+          <t>ADTHPL-249</t>
         </is>
       </c>
       <c r="V221" s="28" t="n">
@@ -22794,7 +22788,7 @@
         <v>1</v>
       </c>
       <c r="N222" s="23" t="n">
-        <v>168</v>
+        <v>8</v>
       </c>
       <c r="O222" s="8" t="n"/>
       <c r="P222" s="27" t="n"/>
@@ -22811,12 +22805,12 @@
       </c>
       <c r="T222" s="8" t="inlineStr">
         <is>
-          <t>Управление портфелем разработки и бюджетом управления (4 кв. 2026)</t>
+          <t>Взаимодействие с бизнес-заказчиками и приоритизация бэклога (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U222" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-249</t>
+          <t>ADTHPL-250</t>
         </is>
       </c>
       <c r="V222" s="28" t="n">
@@ -22830,7 +22824,7 @@
     <row r="223">
       <c r="A223" s="8" t="inlineStr">
         <is>
-          <t>ИТ</t>
+          <t>Бизнес</t>
         </is>
       </c>
       <c r="B223" s="8" t="inlineStr">
@@ -22840,47 +22834,43 @@
       </c>
       <c r="C223" s="8" t="inlineStr">
         <is>
-          <t>CN-0825875</t>
+          <t>GK-0002680</t>
         </is>
       </c>
       <c r="D223" s="8" t="inlineStr">
         <is>
-          <t>Буров Глеб Олегович</t>
+          <t>Гряда Игорь Леонидович</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>Руководитель управления</t>
+          <t>Ведущий разработчик проекта Эдтех</t>
         </is>
       </c>
       <c r="F223" s="8" t="inlineStr">
         <is>
-          <t>f20707a3-448c-11f0-ab45-e4434b7b9424</t>
+          <t>401c7277-4316-11e8-8109-5cf3fc374db0</t>
         </is>
       </c>
       <c r="G223" s="8" t="inlineStr">
         <is>
-          <t>f2070813-448c-11f0-ab45-e4434b7b9424</t>
+          <t>512cec66-1cb6-11ef-ab4e-f8f21e64b171</t>
         </is>
       </c>
       <c r="H223" s="8" t="inlineStr">
         <is>
-          <t>burov_go@magnit.ru</t>
-        </is>
-      </c>
-      <c r="I223" s="8" t="inlineStr">
-        <is>
-          <t>Департамент по развитию и разработке онлайн платформ</t>
-        </is>
-      </c>
+          <t>gryada_il@magnit.ru</t>
+        </is>
+      </c>
+      <c r="I223" s="8" t="n"/>
       <c r="J223" s="8" t="inlineStr">
         <is>
-          <t>Сачков Антон Константинович</t>
+          <t>Моисеенко Ярослав Александрович</t>
         </is>
       </c>
       <c r="K223" s="8" t="inlineStr">
         <is>
-          <t>Департамент по развитию и разработке онлайн платформ</t>
+          <t>Сектор разработки регулярной отчётности</t>
         </is>
       </c>
       <c r="L223" s="23" t="inlineStr">
@@ -22892,29 +22882,29 @@
         <v>1</v>
       </c>
       <c r="N223" s="23" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="O223" s="8" t="n"/>
       <c r="P223" s="27" t="n"/>
       <c r="Q223" s="27" t="n"/>
       <c r="R223" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S223" s="8" t="inlineStr">
         <is>
-          <t>Менеджмент/ Административные задачи</t>
+          <t>Разработка (кодирование) ПО</t>
         </is>
       </c>
       <c r="T223" s="8" t="inlineStr">
         <is>
-          <t>Планирование численности и развитие команд управления (4 кв. 2026)</t>
+          <t>Прогноз кликабельности для ранжирования ставок: мониторинг и логирование новой функциональности</t>
         </is>
       </c>
       <c r="U223" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-251</t>
+          <t>ADTHPL-164</t>
         </is>
       </c>
       <c r="V223" s="28" t="n">
@@ -22986,7 +22976,7 @@
         <v>1</v>
       </c>
       <c r="N224" s="23" t="n">
-        <v>120</v>
+        <v>56</v>
       </c>
       <c r="O224" s="8" t="n"/>
       <c r="P224" s="27" t="n"/>
@@ -23003,12 +22993,12 @@
       </c>
       <c r="T224" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: мониторинг и логирование новой функциональности</t>
+          <t>Прогноз кликабельности для ранжирования ставок: разработка фоновых обработчиков</t>
         </is>
       </c>
       <c r="U224" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-164</t>
+          <t>ADTHPL-163</t>
         </is>
       </c>
       <c r="V224" s="28" t="n">
@@ -23032,43 +23022,47 @@
       </c>
       <c r="C225" s="8" t="inlineStr">
         <is>
-          <t>GK-0002680</t>
+          <t>CN-0981142</t>
         </is>
       </c>
       <c r="D225" s="8" t="inlineStr">
         <is>
-          <t>Гряда Игорь Леонидович</t>
+          <t>Лошманов Александр Борисович</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>Ведущий разработчик проекта Эдтех</t>
+          <t>Инженер сопровождения</t>
         </is>
       </c>
       <c r="F225" s="8" t="inlineStr">
         <is>
-          <t>401c7277-4316-11e8-8109-5cf3fc374db0</t>
+          <t>0f507677-229f-11f1-93e2-c4cbe1a36811</t>
         </is>
       </c>
       <c r="G225" s="8" t="inlineStr">
         <is>
-          <t>512cec66-1cb6-11ef-ab4e-f8f21e64b171</t>
+          <t>c0029a41-22a0-11f1-93e2-c4cbe1a36811</t>
         </is>
       </c>
       <c r="H225" s="8" t="inlineStr">
         <is>
-          <t>gryada_il@magnit.ru</t>
-        </is>
-      </c>
-      <c r="I225" s="8" t="n"/>
+          <t>loshmanov_ab@magnit.ru</t>
+        </is>
+      </c>
+      <c r="I225" s="8" t="inlineStr">
+        <is>
+          <t>Департамент по развитию и разработке онлайн платформ</t>
+        </is>
+      </c>
       <c r="J225" s="8" t="inlineStr">
         <is>
-          <t>Моисеенко Ярослав Александрович</t>
+          <t>Науменко Андрей Викторович</t>
         </is>
       </c>
       <c r="K225" s="8" t="inlineStr">
         <is>
-          <t>Сектор разработки регулярной отчётности</t>
+          <t>Команда развития медиаконтента</t>
         </is>
       </c>
       <c r="L225" s="23" t="inlineStr">
@@ -23080,14 +23074,14 @@
         <v>1</v>
       </c>
       <c r="N225" s="23" t="n">
-        <v>56</v>
+        <v>176</v>
       </c>
       <c r="O225" s="8" t="n"/>
       <c r="P225" s="27" t="n"/>
       <c r="Q225" s="27" t="n"/>
       <c r="R225" s="8" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>OPEX</t>
         </is>
       </c>
       <c r="S225" s="8" t="inlineStr">
@@ -23097,12 +23091,12 @@
       </c>
       <c r="T225" s="8" t="inlineStr">
         <is>
-          <t>Прогноз кликабельности для ранжирования ставок: разработка серверной части и API</t>
+          <t>Сопровождение промышленной эксплуатации партнерской платформы: мониторинг, инциденты, обновления (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U225" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-168</t>
+          <t>ADTHPL-235</t>
         </is>
       </c>
       <c r="V225" s="28" t="n">
@@ -23126,47 +23120,47 @@
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>CN-0981142</t>
+          <t>CN-0744573</t>
         </is>
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>Лошманов Александр Борисович</t>
+          <t>Ардаширов Денис Тимурович</t>
         </is>
       </c>
       <c r="E226" s="8" t="inlineStr">
         <is>
-          <t>Инженер сопровождения</t>
+          <t>Директор департамента</t>
         </is>
       </c>
       <c r="F226" s="8" t="inlineStr">
         <is>
-          <t>0f507677-229f-11f1-93e2-c4cbe1a36811</t>
+          <t>8b6edcd4-c45f-11ef-ab50-f8f21e64b170</t>
         </is>
       </c>
       <c r="G226" s="8" t="inlineStr">
         <is>
-          <t>c0029a41-22a0-11f1-93e2-c4cbe1a36811</t>
+          <t>8b6edd55-c45f-11ef-ab50-f8f21e64b170</t>
         </is>
       </c>
       <c r="H226" s="8" t="inlineStr">
         <is>
-          <t>loshmanov_ab@magnit.ru</t>
+          <t>ardashirov@magnit.ru</t>
         </is>
       </c>
       <c r="I226" s="8" t="inlineStr">
         <is>
-          <t>Департамент по развитию и разработке онлайн платформ</t>
+          <t>Департамент продуктов коммерции и механики рекламных технологий</t>
         </is>
       </c>
       <c r="J226" s="8" t="inlineStr">
         <is>
-          <t>Науменко Андрей Викторович</t>
+          <t>Марлье Людмила Анатольевна</t>
         </is>
       </c>
       <c r="K226" s="8" t="inlineStr">
         <is>
-          <t>Команда развития медиаконтента</t>
+          <t>Бизнес-формат Рекламные технологии</t>
         </is>
       </c>
       <c r="L226" s="23" t="inlineStr">
@@ -23190,17 +23184,17 @@
       </c>
       <c r="S226" s="8" t="inlineStr">
         <is>
-          <t>Разработка (кодирование) ПО</t>
+          <t>Менеджмент/ Административные задачи</t>
         </is>
       </c>
       <c r="T226" s="8" t="inlineStr">
         <is>
-          <t>Сопровождение промышленной эксплуатации партнерской платформы: мониторинг, инциденты, обновления (4 кв. 2026)</t>
+          <t>Стратегическое управление департаментом и бюджетирование (4 кв. 2026)</t>
         </is>
       </c>
       <c r="U226" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-235</t>
+          <t>ADTHPL-242</t>
         </is>
       </c>
       <c r="V226" s="28" t="n">
@@ -23214,7 +23208,7 @@
     <row r="227">
       <c r="A227" s="8" t="inlineStr">
         <is>
-          <t>Бизнес</t>
+          <t>Аналитика</t>
         </is>
       </c>
       <c r="B227" s="8" t="inlineStr">
@@ -23224,90 +23218,100 @@
       </c>
       <c r="C227" s="8" t="inlineStr">
         <is>
-          <t>CN-0744573</t>
+          <t>CN-1090167</t>
         </is>
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>Ардаширов Денис Тимурович</t>
+          <t>Чижиков Никита Игоревич</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>Директор департамента</t>
+          <t>Специалист ML</t>
         </is>
       </c>
       <c r="F227" s="8" t="inlineStr">
         <is>
-          <t>8b6edcd4-c45f-11ef-ab50-f8f21e64b170</t>
+          <t>664a7fef-c2e6-11f1-86a6-3a68dd8b748f</t>
         </is>
       </c>
       <c r="G227" s="8" t="inlineStr">
         <is>
-          <t>8b6edd55-c45f-11ef-ab50-f8f21e64b170</t>
+          <t>fd95a41a-c2e6-11f1-86a6-3a68dd8b748f</t>
         </is>
       </c>
       <c r="H227" s="8" t="inlineStr">
         <is>
-          <t>ardashirov@magnit.ru</t>
+          <t>chizhikov_ni@magnit.ru</t>
         </is>
       </c>
       <c r="I227" s="8" t="inlineStr">
         <is>
-          <t>Департамент продуктов коммерции и механики рекламных технологий</t>
+          <t>Департамент по управлению данными и операционной аналитике цифровых платформ</t>
         </is>
       </c>
       <c r="J227" s="8" t="inlineStr">
         <is>
-          <t>Марлье Людмила Анатольевна</t>
+          <t>Соловьев Никита Александрович</t>
         </is>
       </c>
       <c r="K227" s="8" t="inlineStr">
         <is>
-          <t>Бизнес-формат Рекламные технологии</t>
+          <t>Команда машинного обучения в рекламных технологиях</t>
         </is>
       </c>
       <c r="L227" s="23" t="inlineStr">
         <is>
-          <t>да</t>
+          <t>нет</t>
         </is>
       </c>
       <c r="M227" s="23" t="n">
         <v>1</v>
       </c>
       <c r="N227" s="23" t="n">
-        <v>176</v>
-      </c>
-      <c r="O227" s="8" t="n"/>
-      <c r="P227" s="27" t="n"/>
-      <c r="Q227" s="27" t="n"/>
+        <v>88</v>
+      </c>
+      <c r="O227" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P227" s="27" t="n">
+        <v>46296</v>
+      </c>
+      <c r="Q227" s="27" t="n">
+        <v>46306</v>
+      </c>
       <c r="R227" s="8" t="inlineStr">
         <is>
-          <t>OPEX</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="S227" s="8" t="inlineStr">
         <is>
-          <t>Менеджмент/ Административные задачи</t>
+          <t>Разработка (кодирование) ПО</t>
         </is>
       </c>
       <c r="T227" s="8" t="inlineStr">
         <is>
-          <t>Стратегическое управление департаментом и бюджетирование (4 кв. 2026)</t>
+          <t>Дашборд эффективности кампаний в реальном времени: обучение и валидация модели</t>
         </is>
       </c>
       <c r="U227" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-242</t>
+          <t>ADTHPL-147</t>
         </is>
       </c>
       <c r="V227" s="28" t="n">
-        <v>46296</v>
+        <v>46307</v>
       </c>
       <c r="W227" s="28" t="n">
         <v>46326</v>
       </c>
-      <c r="X227" s="8" t="n"/>
+      <c r="X227" s="8" t="inlineStr">
+        <is>
+          <t>приступили к работе в октябре</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="8" t="inlineStr">
@@ -23374,7 +23378,7 @@
         <v>1</v>
       </c>
       <c r="N228" s="23" t="n">
-        <v>88</v>
+        <v>32</v>
       </c>
       <c r="O228" s="8" t="n">
         <v>7</v>
@@ -23397,16 +23401,16 @@
       </c>
       <c r="T228" s="8" t="inlineStr">
         <is>
-          <t>Дашборд эффективности кампаний в реальном времени: обучение и валидация модели</t>
+          <t>Отчет sales lift по рекламной кампании: обучение и валидация модели</t>
         </is>
       </c>
       <c r="U228" s="8" t="inlineStr">
         <is>
-          <t>ADTHPL-147</t>
+          <t>ADTHPL-290</t>
         </is>
       </c>
       <c r="V228" s="28" t="n">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="W228" s="28" t="n">
         <v>46326</v>
@@ -23417,116 +23421,8 @@
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="8" t="inlineStr">
-        <is>
-          <t>Аналитика</t>
-        </is>
-      </c>
-      <c r="B229" s="8" t="inlineStr">
-        <is>
-          <t>AdTech</t>
-        </is>
-      </c>
-      <c r="C229" s="8" t="inlineStr">
-        <is>
-          <t>CN-1090167</t>
-        </is>
-      </c>
-      <c r="D229" s="8" t="inlineStr">
-        <is>
-          <t>Чижиков Никита Игоревич</t>
-        </is>
-      </c>
-      <c r="E229" s="8" t="inlineStr">
-        <is>
-          <t>Специалист ML</t>
-        </is>
-      </c>
-      <c r="F229" s="8" t="inlineStr">
-        <is>
-          <t>664a7fef-c2e6-11f1-86a6-3a68dd8b748f</t>
-        </is>
-      </c>
-      <c r="G229" s="8" t="inlineStr">
-        <is>
-          <t>fd95a41a-c2e6-11f1-86a6-3a68dd8b748f</t>
-        </is>
-      </c>
-      <c r="H229" s="8" t="inlineStr">
-        <is>
-          <t>chizhikov_ni@magnit.ru</t>
-        </is>
-      </c>
-      <c r="I229" s="8" t="inlineStr">
-        <is>
-          <t>Департамент по управлению данными и операционной аналитике цифровых платформ</t>
-        </is>
-      </c>
-      <c r="J229" s="8" t="inlineStr">
-        <is>
-          <t>Соловьев Никита Александрович</t>
-        </is>
-      </c>
-      <c r="K229" s="8" t="inlineStr">
-        <is>
-          <t>Команда машинного обучения в рекламных технологиях</t>
-        </is>
-      </c>
-      <c r="L229" s="23" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="M229" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N229" s="23" t="n">
-        <v>32</v>
-      </c>
-      <c r="O229" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="P229" s="27" t="n">
-        <v>46296</v>
-      </c>
-      <c r="Q229" s="27" t="n">
-        <v>46306</v>
-      </c>
-      <c r="R229" s="8" t="inlineStr">
-        <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="S229" s="8" t="inlineStr">
-        <is>
-          <t>Разработка (кодирование) ПО</t>
-        </is>
-      </c>
-      <c r="T229" s="8" t="inlineStr">
-        <is>
-          <t>Отчет sales lift по рекламной кампании: обучение и валидация модели</t>
-        </is>
-      </c>
-      <c r="U229" s="8" t="inlineStr">
-        <is>
-          <t>ADTHPL-290</t>
-        </is>
-      </c>
-      <c r="V229" s="28" t="n">
-        <v>46314</v>
-      </c>
-      <c r="W229" s="28" t="n">
-        <v>46326</v>
-      </c>
-      <c r="X229" s="8" t="inlineStr">
-        <is>
-          <t>приступили к работе в октябре</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:X229"/>
+  <autoFilter ref="A1:X228"/>
   <conditionalFormatting sqref="D1:D105 D107:D1048576">
     <cfRule type="duplicateValues" priority="9" dxfId="0"/>
   </conditionalFormatting>
